--- a/output/yearly_surface_area_iteration_56_growth_param_0.5.xlsx
+++ b/output/yearly_surface_area_iteration_56_growth_param_0.5.xlsx
@@ -735,10 +735,10 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>10.84497626596947</v>
+        <v>10.84497626653378</v>
       </c>
       <c r="C21" t="n">
-        <v>37.78907171107824</v>
+        <v>37.78907171304459</v>
       </c>
       <c r="D21" t="n">
         <v>0</v>
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.381940914681015</v>
+        <v>5.114905539125882</v>
       </c>
       <c r="C2" t="n">
-        <v>9.794896845270427</v>
+        <v>12.67632635723482</v>
       </c>
       <c r="D2" t="n">
-        <v>25.70117314947725</v>
+        <v>18.80734077025615</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>18.00034415736527</v>
+        <v>15.66378462125786</v>
       </c>
       <c r="C3" t="n">
-        <v>22.88944772451438</v>
+        <v>22.29549036344507</v>
       </c>
       <c r="D3" t="n">
-        <v>85.9029241215959</v>
+        <v>56.6517512735622</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>37.27990557336413</v>
+        <v>33.59147944850886</v>
       </c>
       <c r="C4" t="n">
-        <v>54.61167954413732</v>
+        <v>49.02160811615598</v>
       </c>
       <c r="D4" t="n">
-        <v>110.0912240588288</v>
+        <v>78.22271183127312</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>47.22206457427158</v>
+        <v>42.65693774952392</v>
       </c>
       <c r="C5" t="n">
-        <v>87.47372044839082</v>
+        <v>89.82991493858316</v>
       </c>
       <c r="D5" t="n">
-        <v>83.12948685709868</v>
+        <v>62.24280444924779</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>45.80638438474769</v>
+        <v>40.37241084174159</v>
       </c>
       <c r="C6" t="n">
-        <v>103.1247423494935</v>
+        <v>124.1361067157837</v>
       </c>
       <c r="D6" t="n">
-        <v>54.46049039768332</v>
+        <v>46.69192081397831</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>31.73990327829938</v>
+        <v>27.60772719112455</v>
       </c>
       <c r="C7" t="n">
-        <v>89.47059527882881</v>
+        <v>126.7200666733613</v>
       </c>
       <c r="D7" t="n">
-        <v>41.62119392154352</v>
+        <v>39.40538935305847</v>
       </c>
     </row>
     <row r="8">
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>16.35591675275186</v>
+        <v>14.35315143608837</v>
       </c>
       <c r="C8" t="n">
-        <v>51.15396412978005</v>
+        <v>89.45685081096936</v>
       </c>
       <c r="D8" t="n">
-        <v>36.30012136452581</v>
+        <v>36.04977569994287</v>
       </c>
     </row>
     <row r="9">
@@ -878,13 +878,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>7.876561831172157</v>
+        <v>7.321874378272709</v>
       </c>
       <c r="C9" t="n">
-        <v>29.95312245657017</v>
+        <v>49.92187076095029</v>
       </c>
       <c r="D9" t="n">
-        <v>34.16874709860598</v>
+        <v>34.27968458918587</v>
       </c>
     </row>
     <row r="10">
@@ -895,10 +895,10 @@
         <v>5.409429850399925</v>
       </c>
       <c r="C10" t="n">
-        <v>28.61303684027329</v>
+        <v>32.31422568528377</v>
       </c>
       <c r="D10" t="n">
-        <v>34.59188035913637</v>
+        <v>34.44952694202058</v>
       </c>
     </row>
     <row r="11">
@@ -906,13 +906,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.620104696185489</v>
+        <v>4.797801030654161</v>
       </c>
       <c r="C11" t="n">
         <v>29.49759152179966</v>
       </c>
       <c r="D11" t="n">
-        <v>36.60544490054656</v>
+        <v>36.42774856607789</v>
       </c>
     </row>
     <row r="12">
@@ -926,7 +926,7 @@
         <v>27.98864530037232</v>
       </c>
       <c r="D12" t="n">
-        <v>34.71459882216721</v>
+        <v>34.28066633689012</v>
       </c>
     </row>
     <row r="13">
@@ -937,10 +937,10 @@
         <v>2.861794557879452</v>
       </c>
       <c r="C13" t="n">
-        <v>25.49598787928967</v>
+        <v>25.23582473766426</v>
       </c>
       <c r="D13" t="n">
-        <v>32.00006641992479</v>
+        <v>32.780555844801</v>
       </c>
     </row>
     <row r="14">
@@ -951,10 +951,10 @@
         <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
-        <v>23.04652735719387</v>
+        <v>23.35381438862312</v>
       </c>
       <c r="D14" t="n">
-        <v>30.72870314292517</v>
+        <v>31.03599017435442</v>
       </c>
     </row>
     <row r="15">
@@ -965,7 +965,7 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>21.50027472300514</v>
+        <v>21.14193681095506</v>
       </c>
       <c r="D15" t="n">
         <v>28.30869505195678</v>
@@ -982,7 +982,7 @@
         <v>19.01252604044373</v>
       </c>
       <c r="D16" t="n">
-        <v>26.86552592671396</v>
+        <v>27.27884171020187</v>
       </c>
     </row>
     <row r="17">
@@ -1007,7 +1007,7 @@
         <v>0.5350524988145117</v>
       </c>
       <c r="C18" t="n">
-        <v>17.65673246087889</v>
+        <v>18.1917849596934</v>
       </c>
       <c r="D18" t="n">
         <v>20.86704745376595</v>
@@ -1035,7 +1035,7 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>18.82992096745382</v>
       </c>
       <c r="D20" t="n">
         <v>10.75995483854504</v>
@@ -1046,13 +1046,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.689484803720585</v>
+        <v>7.684937796676213</v>
       </c>
       <c r="C21" t="n">
-        <v>94.19618884557715</v>
+        <v>93.17987078469908</v>
       </c>
       <c r="D21" t="n">
-        <v>8.650670404185657</v>
+        <v>7.684937796676213</v>
       </c>
     </row>
   </sheetData>
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7.196210672129119</v>
+        <v>6.638577976116932</v>
       </c>
       <c r="C2" t="n">
-        <v>11.32936850700819</v>
+        <v>18.62277220185775</v>
       </c>
       <c r="D2" t="n">
-        <v>34.48094286855648</v>
+        <v>16.22632605579128</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>17.93653055658923</v>
+        <v>16.33137306014569</v>
       </c>
       <c r="C3" t="n">
-        <v>30.7483380970101</v>
+        <v>36.34430001121692</v>
       </c>
       <c r="D3" t="n">
-        <v>85.92255907568085</v>
+        <v>57.92802328908305</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>35.48036203147973</v>
+        <v>31.44734246243383</v>
       </c>
       <c r="C4" t="n">
-        <v>55.87518883950297</v>
+        <v>52.37820351697583</v>
       </c>
       <c r="D4" t="n">
-        <v>124.1685043900238</v>
+        <v>86.36532729029615</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>51.63992924338224</v>
+        <v>46.19122948481243</v>
       </c>
       <c r="C5" t="n">
-        <v>93.04513866999146</v>
+        <v>89.16723523821656</v>
       </c>
       <c r="D5" t="n">
-        <v>101.5863436969387</v>
+        <v>74.73554398578845</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>54.13847715069036</v>
+        <v>48.94601354292898</v>
       </c>
       <c r="C6" t="n">
-        <v>120.6744643106095</v>
+        <v>133.5549941903276</v>
       </c>
       <c r="D6" t="n">
-        <v>65.77120569831082</v>
+        <v>54.09822549481625</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>42.39971985101125</v>
+        <v>37.12969817461437</v>
       </c>
       <c r="C7" t="n">
-        <v>117.3777555197486</v>
+        <v>151.5131231964102</v>
       </c>
       <c r="D7" t="n">
-        <v>47.37030847761284</v>
+        <v>43.71722527011047</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>24.78422079371073</v>
+        <v>21.61317570899353</v>
       </c>
       <c r="C8" t="n">
-        <v>83.53200341583985</v>
+        <v>127.7597374921587</v>
       </c>
       <c r="D8" t="n">
-        <v>38.7201294554942</v>
+        <v>38.05254101660637</v>
       </c>
     </row>
     <row r="9">
@@ -1189,10 +1189,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>11.98124898262807</v>
+        <v>10.76093658624928</v>
       </c>
       <c r="C9" t="n">
-        <v>45.5953086283346</v>
+        <v>78.4328058399819</v>
       </c>
       <c r="D9" t="n">
         <v>35.83280945730432</v>
@@ -1203,13 +1203,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>6.405903770210439</v>
+        <v>6.26355035309465</v>
       </c>
       <c r="C10" t="n">
-        <v>32.59893251951534</v>
+        <v>45.26838664282043</v>
       </c>
       <c r="D10" t="n">
-        <v>35.16129402759952</v>
+        <v>35.01894061048373</v>
       </c>
     </row>
     <row r="11">
@@ -1217,13 +1217,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.797801030654161</v>
+        <v>4.975497365122834</v>
       </c>
       <c r="C11" t="n">
-        <v>31.8076438698924</v>
+        <v>33.40691088011046</v>
       </c>
       <c r="D11" t="n">
-        <v>36.96083756948391</v>
+        <v>36.78314123501524</v>
       </c>
     </row>
     <row r="12">
@@ -1234,10 +1234,10 @@
         <v>3.905392367493811</v>
       </c>
       <c r="C12" t="n">
-        <v>30.59224021203486</v>
+        <v>31.02617269731195</v>
       </c>
       <c r="D12" t="n">
-        <v>35.58246379272139</v>
+        <v>35.1485313074443</v>
       </c>
     </row>
     <row r="13">
@@ -1248,10 +1248,10 @@
         <v>2.861794557879452</v>
       </c>
       <c r="C13" t="n">
-        <v>28.35778243716912</v>
+        <v>28.09761929554372</v>
       </c>
       <c r="D13" t="n">
-        <v>32.26022956155019</v>
+        <v>33.04071898642641</v>
       </c>
     </row>
     <row r="14">
@@ -1265,7 +1265,7 @@
         <v>25.19753657719863</v>
       </c>
       <c r="D14" t="n">
-        <v>31.03599017435442</v>
+        <v>31.34327720578367</v>
       </c>
     </row>
     <row r="15">
@@ -1293,7 +1293,7 @@
         <v>20.25247339090745</v>
       </c>
       <c r="D16" t="n">
-        <v>26.86552592671396</v>
+        <v>27.27884171020187</v>
       </c>
     </row>
     <row r="17">
@@ -1346,7 +1346,7 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>18.82992096745382</v>
       </c>
       <c r="D20" t="n">
         <v>10.75995483854504</v>
@@ -1357,13 +1357,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.872677956585943</v>
+        <v>7.868392550820402</v>
       </c>
       <c r="C21" t="n">
-        <v>103.3288981801905</v>
+        <v>101.3055540918127</v>
       </c>
       <c r="D21" t="n">
-        <v>9.840847445732429</v>
+        <v>8.851941619672953</v>
       </c>
     </row>
   </sheetData>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>8.455792976677778</v>
+        <v>9.062513057902306</v>
       </c>
       <c r="C2" t="n">
-        <v>10.03051629428966</v>
+        <v>18.59921025695582</v>
       </c>
       <c r="D2" t="n">
-        <v>34.83240854667683</v>
+        <v>18.88588058659589</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>20.700150344044</v>
+        <v>18.83973844449629</v>
       </c>
       <c r="C3" t="n">
-        <v>36.78117773960675</v>
+        <v>53.10273332270997</v>
       </c>
       <c r="D3" t="n">
-        <v>91.3516238801657</v>
+        <v>57.09353774047326</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>34.14027641518283</v>
+        <v>30.98788453684632</v>
       </c>
       <c r="C4" t="n">
-        <v>64.79633022799374</v>
+        <v>69.37814676371359</v>
       </c>
       <c r="D4" t="n">
-        <v>135.6294270894011</v>
+        <v>93.60178961829939</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>52.03262832508096</v>
+        <v>46.36303533305563</v>
       </c>
       <c r="C5" t="n">
-        <v>97.31574118346511</v>
+        <v>91.4497986505904</v>
       </c>
       <c r="D5" t="n">
-        <v>117.2697632722815</v>
+        <v>84.89663272474294</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>60.65924540229769</v>
+        <v>54.58124536530568</v>
       </c>
       <c r="C6" t="n">
-        <v>131.5424113966216</v>
+        <v>137.6606630894878</v>
       </c>
       <c r="D6" t="n">
-        <v>79.41651703963724</v>
+        <v>63.23535137824131</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>51.86180422454201</v>
+        <v>46.17257627843174</v>
       </c>
       <c r="C7" t="n">
-        <v>141.7516057730842</v>
+        <v>169.3593329642087</v>
       </c>
       <c r="D7" t="n">
-        <v>53.29908286355933</v>
+        <v>47.84940135728529</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>34.13045893814036</v>
+        <v>29.6242369756475</v>
       </c>
       <c r="C8" t="n">
-        <v>115.5762484824558</v>
+        <v>161.1391594365502</v>
       </c>
       <c r="D8" t="n">
-        <v>42.05807164993335</v>
+        <v>40.72289477215769</v>
       </c>
     </row>
     <row r="9">
@@ -1500,13 +1500,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>17.30624853046277</v>
+        <v>15.53124868118453</v>
       </c>
       <c r="C9" t="n">
-        <v>70.11249404649018</v>
+        <v>112.490615448008</v>
       </c>
       <c r="D9" t="n">
-        <v>37.05312185368311</v>
+        <v>36.94218436310322</v>
       </c>
     </row>
     <row r="10">
@@ -1514,13 +1514,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8.541205026947251</v>
+        <v>7.971791358484101</v>
       </c>
       <c r="C10" t="n">
-        <v>42.13661146627311</v>
+        <v>65.34021845614647</v>
       </c>
       <c r="D10" t="n">
-        <v>36.15776794741003</v>
+        <v>36.01541453029424</v>
       </c>
     </row>
     <row r="11">
@@ -1531,10 +1531,10 @@
         <v>5.330890034060179</v>
       </c>
       <c r="C11" t="n">
-        <v>34.47308888692249</v>
+        <v>41.75863860013807</v>
       </c>
       <c r="D11" t="n">
-        <v>36.96083756948391</v>
+        <v>36.78314123501524</v>
       </c>
     </row>
     <row r="12">
@@ -1545,10 +1545,10 @@
         <v>4.122358610132356</v>
       </c>
       <c r="C12" t="n">
-        <v>32.97886888105885</v>
+        <v>33.84673385161303</v>
       </c>
       <c r="D12" t="n">
-        <v>36.23336252063703</v>
+        <v>35.79943003535993</v>
       </c>
     </row>
     <row r="13">
@@ -1562,7 +1562,7 @@
         <v>30.95941385342317</v>
       </c>
       <c r="D13" t="n">
-        <v>32.5203927031756</v>
+        <v>33.30088212805181</v>
       </c>
     </row>
     <row r="14">
@@ -1576,7 +1576,7 @@
         <v>27.3485457972034</v>
       </c>
       <c r="D14" t="n">
-        <v>31.34327720578367</v>
+        <v>31.65056423721292</v>
       </c>
     </row>
     <row r="15">
@@ -1587,7 +1587,7 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>24.72531593145592</v>
+        <v>24.36697801940583</v>
       </c>
       <c r="D15" t="n">
         <v>28.30869505195678</v>
@@ -1601,10 +1601,10 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>21.49242074137117</v>
+        <v>21.90573652485908</v>
       </c>
       <c r="D16" t="n">
-        <v>26.86552592671396</v>
+        <v>27.27884171020187</v>
       </c>
     </row>
     <row r="17">
@@ -1657,7 +1657,7 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>18.82992096745382</v>
       </c>
       <c r="D20" t="n">
         <v>10.75995483854504</v>
@@ -1668,13 +1668,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8.040018527882253</v>
+        <v>8.036602421951322</v>
       </c>
       <c r="C21" t="n">
-        <v>111.5552570743663</v>
+        <v>109.4987079990867</v>
       </c>
       <c r="D21" t="n">
-        <v>11.0550254758381</v>
+        <v>10.04575302743915</v>
       </c>
     </row>
   </sheetData>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7.655668597716628</v>
+        <v>8.06113039957056</v>
       </c>
       <c r="C2" t="n">
-        <v>6.739697989654353</v>
+        <v>12.49863002276614</v>
       </c>
       <c r="D2" t="n">
-        <v>28.56689469817369</v>
+        <v>15.54695664445249</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>24.41115666609694</v>
+        <v>22.19240685449915</v>
       </c>
       <c r="C3" t="n">
-        <v>51.77737392197678</v>
+        <v>73.64089529555325</v>
       </c>
       <c r="D3" t="n">
-        <v>99.7112055818273</v>
+        <v>63.32763566244051</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>24.98940606389831</v>
+        <v>22.27094667083889</v>
       </c>
       <c r="C4" t="n">
-        <v>84.65512278949821</v>
+        <v>84.27224118484196</v>
       </c>
       <c r="D4" t="n">
-        <v>131.4049667180271</v>
+        <v>92.08302591982958</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>34.16482010778901</v>
+        <v>30.72870314292517</v>
       </c>
       <c r="C5" t="n">
-        <v>78.58890372495718</v>
+        <v>82.24591392327655</v>
       </c>
       <c r="D5" t="n">
-        <v>80.08606897393356</v>
+        <v>61.408318900638</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>32.20132469929539</v>
+        <v>28.6591789823729</v>
       </c>
       <c r="C6" t="n">
-        <v>93.34358997208251</v>
+        <v>111.5373384271844</v>
       </c>
       <c r="D6" t="n">
-        <v>35.09944392223197</v>
+        <v>31.51704654943536</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>22.57725195456389</v>
+        <v>19.64280806657018</v>
       </c>
       <c r="C7" t="n">
-        <v>81.26612971443822</v>
+        <v>113.3054660425329</v>
       </c>
       <c r="D7" t="n">
-        <v>29.52409870981433</v>
+        <v>28.62579956042849</v>
       </c>
     </row>
     <row r="8">
@@ -1797,13 +1797,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>12.01659189998096</v>
+        <v>10.76486357706628</v>
       </c>
       <c r="C8" t="n">
-        <v>51.65465545894592</v>
+        <v>82.86441497695203</v>
       </c>
       <c r="D8" t="n">
-        <v>27.28767743954009</v>
+        <v>27.20422888467911</v>
       </c>
     </row>
     <row r="9">
@@ -1811,13 +1811,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>6.101561981893925</v>
+        <v>5.657812019574366</v>
       </c>
       <c r="C9" t="n">
-        <v>32.17187226816797</v>
+        <v>49.81093327037041</v>
       </c>
       <c r="D9" t="n">
-        <v>27.5124976638126</v>
+        <v>27.40156017323271</v>
       </c>
     </row>
     <row r="10">
@@ -1828,10 +1828,10 @@
         <v>3.843542262126263</v>
       </c>
       <c r="C10" t="n">
-        <v>27.04714925199963</v>
+        <v>32.74128593663113</v>
       </c>
       <c r="D10" t="n">
-        <v>28.89774367450487</v>
+        <v>28.75539025738908</v>
       </c>
     </row>
     <row r="11">
@@ -1842,10 +1842,10 @@
         <v>3.020837685967435</v>
       </c>
       <c r="C11" t="n">
-        <v>26.29905750136355</v>
+        <v>27.00984283923824</v>
       </c>
       <c r="D11" t="n">
-        <v>28.96450251839364</v>
+        <v>28.60910984945629</v>
       </c>
     </row>
     <row r="12">
@@ -1859,7 +1859,7 @@
         <v>25.16808414607123</v>
       </c>
       <c r="D12" t="n">
-        <v>26.4698816019025</v>
+        <v>27.12078032981814</v>
       </c>
     </row>
     <row r="13">
@@ -1873,7 +1873,7 @@
         <v>22.63419332141022</v>
       </c>
       <c r="D13" t="n">
-        <v>25.75615102091507</v>
+        <v>26.01631416254048</v>
       </c>
     </row>
     <row r="14">
@@ -1884,7 +1884,7 @@
         <v>0.921861094287755</v>
       </c>
       <c r="C14" t="n">
-        <v>20.58823110575986</v>
+        <v>20.28094407433061</v>
       </c>
       <c r="D14" t="n">
         <v>23.66110142005238</v>
@@ -1898,10 +1898,10 @@
         <v>0.7166758241001715</v>
       </c>
       <c r="C15" t="n">
-        <v>17.91689560250429</v>
+        <v>18.27523351455437</v>
       </c>
       <c r="D15" t="n">
-        <v>22.57528845915541</v>
+        <v>22.93362637120549</v>
       </c>
     </row>
     <row r="16">
@@ -1954,7 +1954,7 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>16.85071759569225</v>
+        <v>16.24890625298896</v>
       </c>
       <c r="D19" t="n">
         <v>9.027170140549421</v>
@@ -1968,10 +1968,10 @@
         <v>5.37997741927252</v>
       </c>
       <c r="C20" t="n">
-        <v>74.64718669240621</v>
+        <v>73.30219233758808</v>
       </c>
       <c r="D20" t="n">
-        <v>7.397468951499714</v>
+        <v>6.724971774090649</v>
       </c>
     </row>
     <row r="21">
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.667228585989336</v>
+        <v>4.66919208139783</v>
       </c>
       <c r="C2" t="n">
-        <v>3.282964323001334</v>
+        <v>5.977861771158828</v>
       </c>
       <c r="D2" t="n">
-        <v>19.78712497909446</v>
+        <v>11.36569317206532</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>26.07031028627405</v>
+        <v>25.69724615866026</v>
       </c>
       <c r="C3" t="n">
-        <v>39.3680829402971</v>
+        <v>62.05136364691965</v>
       </c>
       <c r="D3" t="n">
-        <v>99.82901530633691</v>
+        <v>61.639029611136</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>34.89327690434013</v>
+        <v>30.93683365622549</v>
       </c>
       <c r="C4" t="n">
-        <v>109.6445288533965</v>
+        <v>136.1782240560751</v>
       </c>
       <c r="D4" t="n">
-        <v>149.5663174988888</v>
+        <v>102.1911002827547</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>37.38004383919731</v>
+        <v>33.52668410002858</v>
       </c>
       <c r="C5" t="n">
-        <v>115.4780737120311</v>
+        <v>117.4170254279185</v>
       </c>
       <c r="D5" t="n">
-        <v>100.7273144557228</v>
+        <v>75.15278676009335</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>38.52083467153211</v>
+        <v>34.3346624606237</v>
       </c>
       <c r="C6" t="n">
-        <v>110.3700404068349</v>
+        <v>125.3034047361332</v>
       </c>
       <c r="D6" t="n">
-        <v>44.92084795551706</v>
+        <v>38.68184129502858</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>21.13997331554657</v>
+        <v>18.50496247734813</v>
       </c>
       <c r="C7" t="n">
-        <v>104.2027013287564</v>
+        <v>137.6793162958684</v>
       </c>
       <c r="D7" t="n">
-        <v>32.45854259780804</v>
+        <v>31.26081039862693</v>
       </c>
     </row>
     <row r="8">
@@ -2108,13 +2108,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.01382658331747</v>
+        <v>9.095892479846697</v>
       </c>
       <c r="C8" t="n">
-        <v>69.09540342489051</v>
+        <v>106.814150222053</v>
       </c>
       <c r="D8" t="n">
-        <v>28.45595720759379</v>
+        <v>28.37250865273282</v>
       </c>
     </row>
     <row r="9">
@@ -2122,13 +2122,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>4.881249585515139</v>
+        <v>4.659374604355361</v>
       </c>
       <c r="C9" t="n">
-        <v>37.71874679716245</v>
+        <v>56.68905768632355</v>
       </c>
       <c r="D9" t="n">
-        <v>28.51093507903161</v>
+        <v>28.39999758845172</v>
       </c>
     </row>
     <row r="10">
@@ -2139,10 +2139,10 @@
         <v>2.135301256736813</v>
       </c>
       <c r="C10" t="n">
-        <v>30.32127784566274</v>
+        <v>34.73423377625215</v>
       </c>
       <c r="D10" t="n">
-        <v>30.17892442854695</v>
+        <v>30.03657101143117</v>
       </c>
     </row>
     <row r="11">
@@ -2153,10 +2153,10 @@
         <v>1.776963344686726</v>
       </c>
       <c r="C11" t="n">
+        <v>30.03068052520567</v>
+      </c>
+      <c r="D11" t="n">
         <v>29.67528785626833</v>
-      </c>
-      <c r="D11" t="n">
-        <v>29.49759152179966</v>
       </c>
     </row>
     <row r="12">
@@ -2170,7 +2170,7 @@
         <v>20.82875929330033</v>
       </c>
       <c r="D12" t="n">
-        <v>28.20561154301086</v>
+        <v>28.63954402828795</v>
       </c>
     </row>
     <row r="13">
@@ -2181,10 +2181,10 @@
         <v>0.5203262832508095</v>
       </c>
       <c r="C13" t="n">
-        <v>16.91060420565131</v>
+        <v>16.65044106402591</v>
       </c>
       <c r="D13" t="n">
-        <v>24.97566159603886</v>
+        <v>25.23582473766426</v>
       </c>
     </row>
     <row r="14">
@@ -2198,7 +2198,7 @@
         <v>15.05706454003333</v>
       </c>
       <c r="D14" t="n">
-        <v>18.74450891718435</v>
+        <v>19.0517959486136</v>
       </c>
     </row>
     <row r="15">
@@ -2251,7 +2251,7 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>14.44641746799181</v>
+        <v>13.9113649691773</v>
       </c>
       <c r="D18" t="n">
         <v>7.490734983403163</v>
@@ -2265,10 +2265,10 @@
         <v>4.212679398923063</v>
       </c>
       <c r="C19" t="n">
-        <v>64.99562501195582</v>
+        <v>63.79200232654924</v>
       </c>
       <c r="D19" t="n">
-        <v>6.018113427032947</v>
+        <v>5.416302084329653</v>
       </c>
     </row>
     <row r="20">
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.799764526062656</v>
+        <v>3.949571014184918</v>
       </c>
       <c r="C2" t="n">
-        <v>6.507023783747859</v>
+        <v>8.540223279243003</v>
       </c>
       <c r="D2" t="n">
-        <v>21.93224371287374</v>
+        <v>10.29755166984479</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>20.90631736193583</v>
+        <v>20.9455872701057</v>
       </c>
       <c r="C3" t="n">
-        <v>24.96584411899639</v>
+        <v>41.62119392154352</v>
       </c>
       <c r="D3" t="n">
-        <v>93.7863581866978</v>
+        <v>57.29479601984386</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>42.38499363544754</v>
+        <v>39.41127983928396</v>
       </c>
       <c r="C4" t="n">
-        <v>104.7691697541069</v>
+        <v>145.660925131395</v>
       </c>
       <c r="D4" t="n">
-        <v>162.9671736618578</v>
+        <v>108.5596976402038</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>44.39953992456201</v>
+        <v>39.58897617375263</v>
       </c>
       <c r="C5" t="n">
-        <v>157.9386619207056</v>
+        <v>182.924140993787</v>
       </c>
       <c r="D5" t="n">
-        <v>125.3937255249239</v>
+        <v>91.49888603580274</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>44.23656980565704</v>
+        <v>39.52712606838509</v>
       </c>
       <c r="C6" t="n">
-        <v>145.9927558554305</v>
+        <v>155.612901609345</v>
       </c>
       <c r="D6" t="n">
-        <v>63.1950997223672</v>
+        <v>50.31456984264904</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>31.32069700858599</v>
+        <v>27.66761380108361</v>
       </c>
       <c r="C7" t="n">
-        <v>130.0138302211093</v>
+        <v>159.9571352006371</v>
       </c>
       <c r="D7" t="n">
-        <v>36.83026512481909</v>
+        <v>34.49468733641593</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>14.77039421039326</v>
+        <v>13.18487166803466</v>
       </c>
       <c r="C8" t="n">
-        <v>101.0561999366454</v>
+        <v>141.9459918185251</v>
       </c>
       <c r="D8" t="n">
-        <v>30.29182541453534</v>
+        <v>29.95803119509142</v>
       </c>
     </row>
     <row r="9">
@@ -2433,13 +2433,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>6.656249434793372</v>
+        <v>6.212499472473814</v>
       </c>
       <c r="C9" t="n">
-        <v>59.12968247908112</v>
+        <v>88.97186744507141</v>
       </c>
       <c r="D9" t="n">
-        <v>29.28749751309084</v>
+        <v>29.17656002251095</v>
       </c>
     </row>
     <row r="10">
@@ -2447,13 +2447,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>2.847068342315751</v>
+        <v>2.704714925199962</v>
       </c>
       <c r="C10" t="n">
-        <v>36.72718161587318</v>
+        <v>48.40016181936776</v>
       </c>
       <c r="D10" t="n">
-        <v>30.7483380970101</v>
+        <v>30.60598467989432</v>
       </c>
     </row>
     <row r="11">
@@ -2464,10 +2464,10 @@
         <v>1.776963344686726</v>
       </c>
       <c r="C11" t="n">
-        <v>33.05151821117311</v>
+        <v>34.65078522139116</v>
       </c>
       <c r="D11" t="n">
-        <v>30.03068052520567</v>
+        <v>30.20837685967435</v>
       </c>
     </row>
     <row r="12">
@@ -2478,10 +2478,10 @@
         <v>0.8678649705541803</v>
       </c>
       <c r="C12" t="n">
-        <v>25.16808414607123</v>
+        <v>25.60201663134832</v>
       </c>
       <c r="D12" t="n">
-        <v>28.63954402828795</v>
+        <v>29.07347651356504</v>
       </c>
     </row>
     <row r="13">
@@ -2492,10 +2492,10 @@
         <v>0.2601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>19.25207248027995</v>
+        <v>18.73174619702914</v>
       </c>
       <c r="D13" t="n">
-        <v>25.75615102091507</v>
+        <v>26.01631416254048</v>
       </c>
     </row>
     <row r="14">
@@ -2506,10 +2506,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>16.59349969717959</v>
+        <v>16.28621266575034</v>
       </c>
       <c r="D14" t="n">
-        <v>19.0517959486136</v>
+        <v>19.35908298004286</v>
       </c>
     </row>
     <row r="15">
@@ -2551,7 +2551,7 @@
         <v>14.63884001802419</v>
       </c>
       <c r="D17" t="n">
-        <v>11.33329549782518</v>
+        <v>10.86107485208246</v>
       </c>
     </row>
     <row r="18">
@@ -2562,7 +2562,7 @@
         <v>3.21031499288707</v>
       </c>
       <c r="C18" t="n">
-        <v>34.77841242294325</v>
+        <v>33.70830742531424</v>
       </c>
       <c r="D18" t="n">
         <v>6.955682484588652</v>
@@ -2576,10 +2576,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>35.50686921949439</v>
+        <v>34.9050578767911</v>
       </c>
       <c r="D19" t="n">
-        <v>4.212679398923063</v>
+        <v>3.610868056219768</v>
       </c>
     </row>
     <row r="20">
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.860812810175206</v>
+        <v>2.34834050855837</v>
       </c>
       <c r="C2" t="n">
-        <v>3.037527396939631</v>
+        <v>3.996694903988765</v>
       </c>
       <c r="D2" t="n">
-        <v>15.29072049364407</v>
+        <v>7.188356690495145</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>20.88177366932966</v>
+        <v>20.10619298297468</v>
       </c>
       <c r="C3" t="n">
-        <v>26.50718801466388</v>
+        <v>40.71798603363646</v>
       </c>
       <c r="D3" t="n">
-        <v>93.33475424274427</v>
+        <v>55.40493168916875</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>46.85194568977053</v>
+        <v>43.40601124786423</v>
       </c>
       <c r="C4" t="n">
-        <v>100.251166819163</v>
+        <v>144.3846531158742</v>
       </c>
       <c r="D4" t="n">
-        <v>173.445366909284</v>
+        <v>114.4177861914445</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>46.75573441475435</v>
+        <v>41.72427743048944</v>
       </c>
       <c r="C5" t="n">
-        <v>189.4282195344221</v>
+        <v>231.5451960466103</v>
       </c>
       <c r="D5" t="n">
-        <v>132.3395905324701</v>
+        <v>96.26036240139979</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>37.43403996293088</v>
+        <v>33.24786775202249</v>
       </c>
       <c r="C6" t="n">
-        <v>178.2343322106</v>
+        <v>192.4834183900382</v>
       </c>
       <c r="D6" t="n">
-        <v>61.18251692866124</v>
+        <v>49.54978838104078</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.761517423326035</v>
+        <v>8.683558444063037</v>
       </c>
       <c r="C7" t="n">
-        <v>134.9245322377519</v>
+        <v>173.8508287111379</v>
       </c>
       <c r="D7" t="n">
-        <v>36.4110588551057</v>
+        <v>34.61446055633404</v>
       </c>
     </row>
     <row r="8">
@@ -2730,13 +2730,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>4.589670517353839</v>
+        <v>4.255876297909922</v>
       </c>
       <c r="C8" t="n">
-        <v>75.27059648460295</v>
+        <v>108.6500184289945</v>
       </c>
       <c r="D8" t="n">
-        <v>31.71045084717197</v>
+        <v>31.46010518258904</v>
       </c>
     </row>
     <row r="9">
@@ -2744,13 +2744,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.996874830438012</v>
+        <v>1.885937339858122</v>
       </c>
       <c r="C9" t="n">
-        <v>27.95624762613216</v>
+        <v>36.94218436310322</v>
       </c>
       <c r="D9" t="n">
-        <v>32.06093477758807</v>
+        <v>31.94999728700819</v>
       </c>
     </row>
     <row r="10">
@@ -2761,10 +2761,10 @@
         <v>1.281180754042088</v>
       </c>
       <c r="C10" t="n">
-        <v>25.90832191507333</v>
+        <v>27.18950266911542</v>
       </c>
       <c r="D10" t="n">
-        <v>23.48831382410494</v>
+        <v>23.63066724122073</v>
       </c>
     </row>
     <row r="11">
@@ -2775,10 +2775,10 @@
         <v>0.5330890034060179</v>
       </c>
       <c r="C11" t="n">
-        <v>20.07968579496001</v>
+        <v>20.43507846389736</v>
       </c>
       <c r="D11" t="n">
-        <v>22.92282714645877</v>
+        <v>23.27821981539612</v>
       </c>
     </row>
     <row r="12">
@@ -2789,10 +2789,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>15.62156946997525</v>
+        <v>15.18763698469816</v>
       </c>
       <c r="D12" t="n">
-        <v>21.04572553593887</v>
+        <v>21.26269177857742</v>
       </c>
     </row>
     <row r="13">
@@ -2803,10 +2803,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>13.52848336452105</v>
+        <v>13.26832022289564</v>
       </c>
       <c r="D13" t="n">
-        <v>15.60978849752428</v>
+        <v>15.86995163914969</v>
       </c>
     </row>
     <row r="14">
@@ -2848,7 +2848,7 @@
         <v>12.39947350463721</v>
       </c>
       <c r="D16" t="n">
-        <v>9.506263020221864</v>
+        <v>9.092947236733956</v>
       </c>
     </row>
     <row r="17">
@@ -2859,7 +2859,7 @@
         <v>2.361103228713579</v>
       </c>
       <c r="C17" t="n">
-        <v>29.7499006817911</v>
+        <v>28.80545939030567</v>
       </c>
       <c r="D17" t="n">
         <v>5.66664774891259</v>
@@ -2873,10 +2873,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>30.49799243242716</v>
+        <v>29.96293993361265</v>
       </c>
       <c r="D18" t="n">
-        <v>3.21031499288707</v>
+        <v>2.675262494072558</v>
       </c>
     </row>
     <row r="19">
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.180281724682919</v>
+        <v>2.610467145592269</v>
       </c>
       <c r="C2" t="n">
-        <v>3.033600406122644</v>
+        <v>6.465790380169493</v>
       </c>
       <c r="D2" t="n">
-        <v>15.66182112584936</v>
+        <v>12.13636511989907</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>15.54106615822701</v>
+        <v>14.29915531235479</v>
       </c>
       <c r="C3" t="n">
-        <v>19.05081420090935</v>
+        <v>27.92581344730052</v>
       </c>
       <c r="D3" t="n">
-        <v>84.76409678466962</v>
+        <v>49.56353284890022</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>43.58468933003715</v>
+        <v>41.40226418349649</v>
       </c>
       <c r="C4" t="n">
-        <v>83.41713893444297</v>
+        <v>124.6407250357666</v>
       </c>
       <c r="D4" t="n">
-        <v>181.1285244427195</v>
+        <v>115.489854684482</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>56.99045423152735</v>
+        <v>51.49266708774522</v>
       </c>
       <c r="C5" t="n">
-        <v>188.8146272192678</v>
+        <v>249.3148294934775</v>
       </c>
       <c r="D5" t="n">
-        <v>157.275982220339</v>
+        <v>111.133840120739</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>47.89947049020189</v>
+        <v>42.02272873258048</v>
       </c>
       <c r="C6" t="n">
-        <v>234.2646371873739</v>
+        <v>269.9276042918436</v>
       </c>
       <c r="D6" t="n">
-        <v>81.30834486572085</v>
+        <v>63.4366096576119</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>20.90042687571034</v>
+        <v>18.62473569726624</v>
       </c>
       <c r="C7" t="n">
-        <v>189.8405535702057</v>
+        <v>219.5443121098972</v>
       </c>
       <c r="D7" t="n">
-        <v>43.29801900039708</v>
+        <v>39.52516257297658</v>
       </c>
     </row>
     <row r="8">
@@ -3041,13 +3041,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>6.342090169434394</v>
+        <v>5.674501730546564</v>
       </c>
       <c r="C8" t="n">
-        <v>117.5790137991192</v>
+        <v>160.2212253330794</v>
       </c>
       <c r="D8" t="n">
-        <v>33.71321616383547</v>
+        <v>33.21252483466959</v>
       </c>
     </row>
     <row r="9">
@@ -3055,13 +3055,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>2.551562283337459</v>
+        <v>2.32968730217768</v>
       </c>
       <c r="C9" t="n">
-        <v>52.02968308196819</v>
+        <v>71.33280644286897</v>
       </c>
       <c r="D9" t="n">
-        <v>32.8374972116473</v>
+        <v>32.72655972106742</v>
       </c>
     </row>
     <row r="10">
@@ -3072,10 +3072,10 @@
         <v>1.281180754042088</v>
       </c>
       <c r="C10" t="n">
-        <v>29.60951076008381</v>
+        <v>33.73775985644164</v>
       </c>
       <c r="D10" t="n">
-        <v>24.62714116103124</v>
+        <v>24.91184799526281</v>
       </c>
     </row>
     <row r="11">
@@ -3086,7 +3086,7 @@
         <v>0.3553926689373453</v>
       </c>
       <c r="C11" t="n">
-        <v>23.63361248433346</v>
+        <v>24.16670148773948</v>
       </c>
       <c r="D11" t="n">
         <v>23.98900515327081</v>
@@ -3100,10 +3100,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>17.7912318963607</v>
+        <v>17.57426565372215</v>
       </c>
       <c r="D12" t="n">
-        <v>21.26269177857742</v>
+        <v>21.47965802121596</v>
       </c>
     </row>
     <row r="13">
@@ -3114,10 +3114,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>15.60978849752428</v>
+        <v>15.34962535589888</v>
       </c>
       <c r="D13" t="n">
-        <v>15.60978849752428</v>
+        <v>15.86995163914969</v>
       </c>
     </row>
     <row r="14">
@@ -3145,7 +3145,7 @@
         <v>13.61684065790326</v>
       </c>
       <c r="D15" t="n">
-        <v>12.18348900970292</v>
+        <v>11.82515109765283</v>
       </c>
     </row>
     <row r="16">
@@ -3156,7 +3156,7 @@
         <v>1.653263133951629</v>
       </c>
       <c r="C16" t="n">
-        <v>23.55899965881071</v>
+        <v>23.1456838753228</v>
       </c>
       <c r="D16" t="n">
         <v>8.266315669758143</v>
@@ -3170,10 +3170,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>34.94432778496098</v>
+        <v>33.99988649347554</v>
       </c>
       <c r="D17" t="n">
-        <v>4.722206457427158</v>
+        <v>4.249985811684442</v>
       </c>
     </row>
     <row r="18">
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.885356502781375</v>
+        <v>1.839795197758523</v>
       </c>
       <c r="C2" t="n">
-        <v>2.119593293468863</v>
+        <v>3.543127464626739</v>
       </c>
       <c r="D2" t="n">
-        <v>12.09611346402495</v>
+        <v>8.976119259928588</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>15.11891464540088</v>
+        <v>12.19821522526662</v>
       </c>
       <c r="C3" t="n">
-        <v>16.06630117999905</v>
+        <v>27.19441140763665</v>
       </c>
       <c r="D3" t="n">
-        <v>79.37430188835462</v>
+        <v>48.67505117655686</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>38.91353375323082</v>
+        <v>36.69282044622454</v>
       </c>
       <c r="C4" t="n">
-        <v>69.62063844666255</v>
+        <v>103.9523556641735</v>
       </c>
       <c r="D4" t="n">
-        <v>182.6345254210341</v>
+        <v>114.7496169154799</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>62.21826075664162</v>
+        <v>56.76956099807182</v>
       </c>
       <c r="C5" t="n">
-        <v>181.770587441297</v>
+        <v>250.2720335051182</v>
       </c>
       <c r="D5" t="n">
-        <v>177.4999849278233</v>
+        <v>120.5340743889022</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>56.07055663264809</v>
+        <v>49.22777513404782</v>
       </c>
       <c r="C6" t="n">
-        <v>267.2709950041517</v>
+        <v>322.6975251428138</v>
       </c>
       <c r="D6" t="n">
-        <v>97.16749728012383</v>
+        <v>74.78757661411353</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>19.52303484665207</v>
+        <v>16.64847756861741</v>
       </c>
       <c r="C7" t="n">
-        <v>241.6424711847887</v>
+        <v>277.3348907203857</v>
       </c>
       <c r="D7" t="n">
-        <v>49.82565948593412</v>
+        <v>43.6573386601514</v>
       </c>
     </row>
     <row r="8">
@@ -3352,13 +3352,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>5.17381040138069</v>
+        <v>4.589670517353839</v>
       </c>
       <c r="C8" t="n">
-        <v>152.4605097310084</v>
+        <v>198.2737663496858</v>
       </c>
       <c r="D8" t="n">
-        <v>34.79804737702819</v>
+        <v>34.21390749300134</v>
       </c>
     </row>
     <row r="9">
@@ -3366,13 +3366,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.885937339858122</v>
+        <v>1.774999849278233</v>
       </c>
       <c r="C9" t="n">
-        <v>61.57030727183869</v>
+        <v>80.31874317984003</v>
       </c>
       <c r="D9" t="n">
-        <v>32.61562223048752</v>
+        <v>32.50468473990763</v>
       </c>
     </row>
     <row r="10">
@@ -3383,10 +3383,10 @@
         <v>0.4270602513473625</v>
       </c>
       <c r="C10" t="n">
-        <v>30.7483380970101</v>
+        <v>34.30717352490479</v>
       </c>
       <c r="D10" t="n">
-        <v>25.19655482949439</v>
+        <v>25.33890824661018</v>
       </c>
     </row>
     <row r="11">
@@ -3397,7 +3397,7 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>23.27821981539612</v>
+        <v>23.45591614986479</v>
       </c>
       <c r="D11" t="n">
         <v>24.16670148773948</v>
@@ -3411,10 +3411,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>17.35729941108361</v>
+        <v>16.92336692580652</v>
       </c>
       <c r="D12" t="n">
-        <v>19.7439280801076</v>
+        <v>19.96089432274615</v>
       </c>
     </row>
     <row r="13">
@@ -3442,7 +3442,7 @@
         <v>11.36962016288231</v>
       </c>
       <c r="D14" t="n">
-        <v>11.36962016288231</v>
+        <v>11.06233313145306</v>
       </c>
     </row>
     <row r="15">
@@ -3453,7 +3453,7 @@
         <v>1.075013736150257</v>
       </c>
       <c r="C15" t="n">
-        <v>19.70858516275472</v>
+        <v>19.35024725070463</v>
       </c>
       <c r="D15" t="n">
         <v>6.808420328951629</v>
@@ -3467,10 +3467,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>29.75873641112932</v>
+        <v>28.9321048441535</v>
       </c>
       <c r="D16" t="n">
-        <v>3.719842051391165</v>
+        <v>3.306526267903257</v>
       </c>
     </row>
     <row r="17">
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.838052686528282</v>
+        <v>2.864739800992193</v>
       </c>
       <c r="C2" t="n">
-        <v>6.616979526623502</v>
+        <v>12.35234961483337</v>
       </c>
       <c r="D2" t="n">
-        <v>13.68458124949629</v>
+        <v>11.16836188351171</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>12.5123744906256</v>
+        <v>9.400234268163208</v>
       </c>
       <c r="C3" t="n">
-        <v>12.44856088984956</v>
+        <v>21.11248437982766</v>
       </c>
       <c r="D3" t="n">
-        <v>72.02592032206724</v>
+        <v>45.10148953309847</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>33.93607289269949</v>
+        <v>30.40079940970673</v>
       </c>
       <c r="C4" t="n">
-        <v>56.39846036586651</v>
+        <v>88.06276907093888</v>
       </c>
       <c r="D4" t="n">
-        <v>180.4903884349591</v>
+        <v>112.9500733735955</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>61.33468782281949</v>
+        <v>56.54866776461629</v>
       </c>
       <c r="C5" t="n">
-        <v>158.6749726988907</v>
+        <v>225.2374670468245</v>
       </c>
       <c r="D5" t="n">
-        <v>195.4414242229338</v>
+        <v>130.3270077387641</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>66.49573550404497</v>
+        <v>59.00892751145879</v>
       </c>
       <c r="C6" t="n">
-        <v>276.8508891021921</v>
+        <v>352.8862670484033</v>
       </c>
       <c r="D6" t="n">
-        <v>119.1449013873929</v>
+        <v>89.1574177611741</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>35.09355343600648</v>
+        <v>29.94330497952771</v>
       </c>
       <c r="C7" t="n">
-        <v>299.6127096251543</v>
+        <v>350.6959879202286</v>
       </c>
       <c r="D7" t="n">
-        <v>61.38377520803181</v>
+        <v>51.14316490503334</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>9.930378028456486</v>
+        <v>8.428304040958867</v>
       </c>
       <c r="C8" t="n">
-        <v>218.8855594003476</v>
+        <v>264.615367464164</v>
       </c>
       <c r="D8" t="n">
-        <v>38.80357801035517</v>
+        <v>36.71736413883071</v>
       </c>
     </row>
     <row r="9">
@@ -3677,13 +3677,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>2.773437264497239</v>
+        <v>2.440624792757569</v>
       </c>
       <c r="C9" t="n">
-        <v>107.7203033530728</v>
+        <v>137.6734258096429</v>
       </c>
       <c r="D9" t="n">
-        <v>33.61405964570653</v>
+        <v>33.39218466454675</v>
       </c>
     </row>
     <row r="10">
@@ -3691,13 +3691,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0.7117670855789376</v>
+        <v>0.5694136684631501</v>
       </c>
       <c r="C10" t="n">
-        <v>45.12603322570465</v>
+        <v>55.09077242380977</v>
       </c>
       <c r="D10" t="n">
-        <v>26.33538216642069</v>
+        <v>26.47773558353648</v>
       </c>
     </row>
     <row r="11">
@@ -3708,7 +3708,7 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>27.36523550817559</v>
+        <v>28.60910984945629</v>
       </c>
       <c r="D11" t="n">
         <v>24.6997904911455</v>
@@ -3722,10 +3722,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>20.17786056538469</v>
+        <v>19.7439280801076</v>
       </c>
       <c r="D12" t="n">
-        <v>19.96089432274615</v>
+        <v>20.39482680802324</v>
       </c>
     </row>
     <row r="13">
@@ -3736,7 +3736,7 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>13.78864650614645</v>
+        <v>13.52848336452105</v>
       </c>
       <c r="D13" t="n">
         <v>16.65044106402591</v>
@@ -3753,7 +3753,7 @@
         <v>11.98419422574081</v>
       </c>
       <c r="D14" t="n">
-        <v>11.67690719431156</v>
+        <v>11.06233313145306</v>
       </c>
     </row>
     <row r="15">
@@ -3764,7 +3764,7 @@
         <v>0.7166758241001715</v>
       </c>
       <c r="C15" t="n">
-        <v>20.78359889890498</v>
+        <v>20.42526098685489</v>
       </c>
       <c r="D15" t="n">
         <v>6.450082416901544</v>
@@ -3778,10 +3778,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>28.9321048441535</v>
+        <v>27.69215749368978</v>
       </c>
       <c r="D16" t="n">
-        <v>3.306526267903257</v>
+        <v>2.89321048441535</v>
       </c>
     </row>
     <row r="17">
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.074073046175016</v>
+        <v>4.737914420695106</v>
       </c>
       <c r="C2" t="n">
-        <v>1.789726064841935</v>
+        <v>10.28871594050657</v>
       </c>
       <c r="D2" t="n">
-        <v>22.10994004734242</v>
+        <v>10.75799134313655</v>
       </c>
     </row>
     <row r="3">
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.458697162061513</v>
+        <v>2.072469403665017</v>
       </c>
       <c r="C2" t="n">
-        <v>3.75813021185679</v>
+        <v>7.212900383101315</v>
       </c>
       <c r="D2" t="n">
-        <v>10.07174969786803</v>
+        <v>8.308530821040756</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>16.90078672860884</v>
+        <v>13.03760951239764</v>
       </c>
       <c r="C3" t="n">
-        <v>18.30959468420301</v>
+        <v>31.78408192499048</v>
       </c>
       <c r="D3" t="n">
-        <v>78.18638716621598</v>
+        <v>49.34263961544469</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>46.8008948091497</v>
+        <v>42.42328179591317</v>
       </c>
       <c r="C4" t="n">
-        <v>82.90663012823464</v>
+        <v>127.4995743505333</v>
       </c>
       <c r="D4" t="n">
-        <v>185.5316628962665</v>
+        <v>117.0979574240383</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>39.14718970684157</v>
+        <v>34.28753857081986</v>
       </c>
       <c r="C5" t="n">
-        <v>235.9139733305086</v>
+        <v>313.4965856586128</v>
       </c>
       <c r="D5" t="n">
-        <v>176.297343990121</v>
+        <v>121.0004045484194</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>21.77614582789851</v>
+        <v>18.59626501384309</v>
       </c>
       <c r="C6" t="n">
-        <v>251.6131008691193</v>
+        <v>296.6949554481329</v>
       </c>
       <c r="D6" t="n">
-        <v>93.5448482514531</v>
+        <v>72.09071567054754</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>6.527640485537042</v>
+        <v>5.569454726192155</v>
       </c>
       <c r="C7" t="n">
-        <v>153.9085875947725</v>
+        <v>186.0676971427852</v>
       </c>
       <c r="D7" t="n">
-        <v>35.09355343600648</v>
+        <v>32.27888276793088</v>
       </c>
     </row>
     <row r="8">
@@ -4285,13 +4285,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>1.919316761802514</v>
+        <v>1.668971097219577</v>
       </c>
       <c r="C8" t="n">
-        <v>79.35957567279091</v>
+        <v>101.4734427109503</v>
       </c>
       <c r="D8" t="n">
-        <v>24.70077223884975</v>
+        <v>24.53387512912779</v>
       </c>
     </row>
     <row r="9">
@@ -4299,13 +4299,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>0.4437499623195582</v>
+        <v>0.3328124717396686</v>
       </c>
       <c r="C9" t="n">
-        <v>34.39062207976576</v>
+        <v>42.04530892977813</v>
       </c>
       <c r="D9" t="n">
-        <v>20.07968579496001</v>
+        <v>20.1906232855399</v>
       </c>
     </row>
     <row r="10">
@@ -4316,7 +4316,7 @@
         <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>21.35301256736813</v>
+        <v>22.34948648717864</v>
       </c>
       <c r="D10" t="n">
         <v>19.3600647277471</v>
@@ -4330,10 +4330,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>16.17036643664921</v>
+        <v>15.81497376771187</v>
       </c>
       <c r="D11" t="n">
-        <v>15.99267010218054</v>
+        <v>16.34806277111788</v>
       </c>
     </row>
     <row r="12">
@@ -4344,7 +4344,7 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>11.0652783745658</v>
+        <v>10.84831213192725</v>
       </c>
       <c r="D12" t="n">
         <v>13.4519070435898</v>
@@ -4361,7 +4361,7 @@
         <v>9.886199381765381</v>
       </c>
       <c r="D13" t="n">
-        <v>9.626036240139976</v>
+        <v>9.105709956889166</v>
       </c>
     </row>
     <row r="14">
@@ -4372,7 +4372,7 @@
         <v>0.3072870314292517</v>
       </c>
       <c r="C14" t="n">
-        <v>17.20807376003809</v>
+        <v>16.90078672860884</v>
       </c>
       <c r="D14" t="n">
         <v>5.223879534297279</v>
@@ -4386,10 +4386,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>24.36697801940583</v>
+        <v>23.29196428325557</v>
       </c>
       <c r="D15" t="n">
-        <v>2.5083653843506</v>
+        <v>2.150027472300515</v>
       </c>
     </row>
     <row r="16">
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7.235480580298993</v>
+        <v>6.788785374866693</v>
       </c>
       <c r="C2" t="n">
-        <v>7.169703484114456</v>
+        <v>6.034803138005143</v>
       </c>
       <c r="D2" t="n">
-        <v>22.06870664376405</v>
+        <v>17.1452419069663</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>12.90016483380309</v>
+        <v>10.06782270705104</v>
       </c>
       <c r="C3" t="n">
-        <v>4.50622196249286</v>
+        <v>25.92304813063703</v>
       </c>
       <c r="D3" t="n">
-        <v>21.70644174089698</v>
+        <v>12.17367153266045</v>
       </c>
     </row>
     <row r="4">
@@ -4557,7 +4557,7 @@
         <v>4.736932672990861</v>
       </c>
       <c r="C5" t="n">
-        <v>9.449321653375552</v>
+        <v>9.35114688295087</v>
       </c>
       <c r="D5" t="n">
         <v>28.49522711576368</v>
@@ -4571,7 +4571,7 @@
         <v>8.050331174823848</v>
       </c>
       <c r="C6" t="n">
-        <v>18.27425176685013</v>
+        <v>18.47551004622073</v>
       </c>
       <c r="D6" t="n">
         <v>32.8453511932813</v>
@@ -4596,7 +4596,7 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>8.845546815263761</v>
+        <v>8.762098260402782</v>
       </c>
       <c r="C8" t="n">
         <v>21.69662426385451</v>
@@ -4610,7 +4610,7 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>8.764061755811273</v>
+        <v>8.874999246391162</v>
       </c>
       <c r="C9" t="n">
         <v>22.74218556887735</v>
@@ -4778,13 +4778,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>13.39685795644442</v>
+        <v>13.39757564524758</v>
       </c>
       <c r="C21" t="n">
-        <v>70.13649165432666</v>
+        <v>70.14024896629617</v>
       </c>
       <c r="D21" t="n">
-        <v>1.576100936052284</v>
+        <v>1.576185370029127</v>
       </c>
     </row>
   </sheetData>
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.458517235612265</v>
+        <v>5.176755644493432</v>
       </c>
       <c r="C2" t="n">
-        <v>6.969426952448107</v>
+        <v>5.491896657556658</v>
       </c>
       <c r="D2" t="n">
-        <v>22.15706393714626</v>
+        <v>17.77061519457152</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>20.14546289114455</v>
+        <v>18.04943154257761</v>
       </c>
       <c r="C3" t="n">
-        <v>19.17844140246144</v>
+        <v>24.42588288166064</v>
       </c>
       <c r="D3" t="n">
-        <v>34.99930565639879</v>
+        <v>23.63066724122073</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>15.00895890252524</v>
+        <v>11.80551614356789</v>
       </c>
       <c r="C4" t="n">
-        <v>7.440665850486576</v>
+        <v>40.04941584704438</v>
       </c>
       <c r="D4" t="n">
-        <v>26.44435616159208</v>
+        <v>21.45413258090555</v>
       </c>
     </row>
     <row r="5">
@@ -4868,7 +4868,7 @@
         <v>3.067961575771283</v>
       </c>
       <c r="C5" t="n">
-        <v>5.424156065963628</v>
+        <v>5.375068680751288</v>
       </c>
       <c r="D5" t="n">
         <v>29.40334374219198</v>
@@ -4896,7 +4896,7 @@
         <v>9.462084373530759</v>
       </c>
       <c r="C7" t="n">
-        <v>24.3139636433765</v>
+        <v>24.49362347325367</v>
       </c>
       <c r="D7" t="n">
         <v>34.97378021608837</v>
@@ -4907,7 +4907,7 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>9.680032363873551</v>
+        <v>9.596583809012571</v>
       </c>
       <c r="C8" t="n">
         <v>25.61870634232051</v>
@@ -5005,7 +5005,7 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>5.0167307687012</v>
+        <v>4.658392856651115</v>
       </c>
       <c r="C15" t="n">
         <v>26.51700549170635</v>
@@ -5025,7 +5025,7 @@
         <v>29.34542062764141</v>
       </c>
       <c r="D16" t="n">
-        <v>40.5049467818149</v>
+        <v>40.91826256530281</v>
       </c>
     </row>
     <row r="17">
@@ -5039,7 +5039,7 @@
         <v>31.63878326476196</v>
       </c>
       <c r="D17" t="n">
-        <v>36.83321036793183</v>
+        <v>36.36098972218912</v>
       </c>
     </row>
     <row r="18">
@@ -5089,13 +5089,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>15.43858054820122</v>
+        <v>15.43889398748856</v>
       </c>
       <c r="C21" t="n">
-        <v>86.13102832154364</v>
+        <v>86.13277698283092</v>
       </c>
       <c r="D21" t="n">
-        <v>3.250227483831835</v>
+        <v>3.250293471050223</v>
       </c>
     </row>
   </sheetData>
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.456553740203772</v>
+        <v>4.476769531365456</v>
       </c>
       <c r="C2" t="n">
-        <v>5.12177777305561</v>
+        <v>6.925248305757</v>
       </c>
       <c r="D2" t="n">
-        <v>23.85156047467626</v>
+        <v>19.16666043001048</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>19.44842202112931</v>
+        <v>17.98561794180156</v>
       </c>
       <c r="C3" t="n">
-        <v>23.99391389179205</v>
+        <v>22.57037972063417</v>
       </c>
       <c r="D3" t="n">
-        <v>44.6007982039326</v>
+        <v>32.3633130704961</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>28.63954402828795</v>
+        <v>24.91282974296706</v>
       </c>
       <c r="C4" t="n">
-        <v>31.30695254072654</v>
+        <v>52.4930679983727</v>
       </c>
       <c r="D4" t="n">
-        <v>38.03290606252143</v>
+        <v>28.47362866627024</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>13.08178815908875</v>
+        <v>10.60287520586555</v>
       </c>
       <c r="C5" t="n">
-        <v>10.16108873895449</v>
+        <v>44.44862730977434</v>
       </c>
       <c r="D5" t="n">
-        <v>32.12769362147687</v>
+        <v>30.38509144643879</v>
       </c>
     </row>
     <row r="6">
@@ -5193,7 +5193,7 @@
         <v>5.957245069369646</v>
       </c>
       <c r="C6" t="n">
-        <v>12.11574841810989</v>
+        <v>12.23650338573225</v>
       </c>
       <c r="D6" t="n">
         <v>36.54850353370026</v>
@@ -5207,10 +5207,10 @@
         <v>9.462084373530759</v>
       </c>
       <c r="C7" t="n">
-        <v>24.37385025333556</v>
+        <v>24.25407703341745</v>
       </c>
       <c r="D7" t="n">
-        <v>37.12969817461437</v>
+        <v>37.4890178343687</v>
       </c>
     </row>
     <row r="8">
@@ -5218,13 +5218,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.51451791248334</v>
+        <v>10.43106935762236</v>
       </c>
       <c r="C8" t="n">
-        <v>29.79113408536946</v>
+        <v>29.87458264023044</v>
       </c>
       <c r="D8" t="n">
-        <v>38.38633523605029</v>
+        <v>37.88564390688441</v>
       </c>
     </row>
     <row r="9">
@@ -5232,7 +5232,7 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>10.09531164276995</v>
+        <v>9.984374152190059</v>
       </c>
       <c r="C9" t="n">
         <v>29.7312474754104</v>
@@ -5249,7 +5249,7 @@
         <v>9.395325529641976</v>
       </c>
       <c r="C10" t="n">
-        <v>29.60951076008381</v>
+        <v>29.89421759431538</v>
       </c>
       <c r="D10" t="n">
         <v>49.25428232206248</v>
@@ -5263,7 +5263,7 @@
         <v>8.174031385558941</v>
       </c>
       <c r="C11" t="n">
-        <v>31.27455486648638</v>
+        <v>30.91916219754903</v>
       </c>
       <c r="D11" t="n">
         <v>49.75497365122833</v>
@@ -5305,7 +5305,7 @@
         <v>4.609305471438775</v>
       </c>
       <c r="C14" t="n">
-        <v>27.65583282863265</v>
+        <v>27.9631198600619</v>
       </c>
       <c r="D14" t="n">
         <v>45.47848065152925</v>
@@ -5316,10 +5316,10 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4.658392856651115</v>
+        <v>4.30005494460103</v>
       </c>
       <c r="C15" t="n">
-        <v>27.5920192278566</v>
+        <v>27.23368131580652</v>
       </c>
       <c r="D15" t="n">
         <v>43.00054944601029</v>
@@ -5336,7 +5336,7 @@
         <v>29.75873641112932</v>
       </c>
       <c r="D16" t="n">
-        <v>40.91826256530281</v>
+        <v>41.33157834879071</v>
       </c>
     </row>
     <row r="17">
@@ -5350,7 +5350,7 @@
         <v>32.11100391050468</v>
       </c>
       <c r="D17" t="n">
-        <v>37.30543101367455</v>
+        <v>36.83321036793183</v>
       </c>
     </row>
     <row r="18">
@@ -5400,13 +5400,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>16.73148758833716</v>
+        <v>16.72992187095895</v>
       </c>
       <c r="C21" t="n">
-        <v>102.0620742888567</v>
+        <v>102.0525234128496</v>
       </c>
       <c r="D21" t="n">
-        <v>5.019446276501148</v>
+        <v>4.182480467739737</v>
       </c>
     </row>
   </sheetData>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.848271074198249</v>
+        <v>5.428083056780614</v>
       </c>
       <c r="C2" t="n">
-        <v>4.792892292132928</v>
+        <v>4.715334223497431</v>
       </c>
       <c r="D2" t="n">
-        <v>27.98373656185109</v>
+        <v>20.03354365286041</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>19.03608798534566</v>
+        <v>16.50808764691012</v>
       </c>
       <c r="C3" t="n">
-        <v>21.60335823195106</v>
+        <v>25.04438393533613</v>
       </c>
       <c r="D3" t="n">
-        <v>52.80820901143593</v>
+        <v>39.73132959086842</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>33.66805576944012</v>
+        <v>29.99239236474006</v>
       </c>
       <c r="C4" t="n">
-        <v>47.36245449597887</v>
+        <v>54.7265440255342</v>
       </c>
       <c r="D4" t="n">
-        <v>51.08916878129977</v>
+        <v>37.75212621910685</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>27.88163480060942</v>
+        <v>23.83192552059133</v>
       </c>
       <c r="C5" t="n">
-        <v>35.78470381979624</v>
+        <v>72.796592269901</v>
       </c>
       <c r="D5" t="n">
-        <v>37.92000507653306</v>
+        <v>33.37942194439156</v>
       </c>
     </row>
     <row r="6">
@@ -5501,13 +5501,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>11.91449013873929</v>
+        <v>10.22392059202629</v>
       </c>
       <c r="C6" t="n">
-        <v>14.28933783531233</v>
+        <v>42.2642386678252</v>
       </c>
       <c r="D6" t="n">
-        <v>38.80259626265094</v>
+        <v>38.31957639216151</v>
       </c>
     </row>
     <row r="7">
@@ -5518,10 +5518,10 @@
         <v>8.563785224144926</v>
       </c>
       <c r="C7" t="n">
-        <v>21.13997331554657</v>
+        <v>21.19985992550562</v>
       </c>
       <c r="D7" t="n">
-        <v>39.22572952318131</v>
+        <v>39.52516257297658</v>
       </c>
     </row>
     <row r="8">
@@ -5532,10 +5532,10 @@
         <v>10.84831213192725</v>
       </c>
       <c r="C8" t="n">
-        <v>31.46010518258904</v>
+        <v>31.71045084717197</v>
       </c>
       <c r="D8" t="n">
-        <v>40.13875488813084</v>
+        <v>39.8884092235479</v>
       </c>
     </row>
     <row r="9">
@@ -5543,13 +5543,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>10.76093658624928</v>
+        <v>10.6499990956694</v>
       </c>
       <c r="C9" t="n">
-        <v>34.27968458918587</v>
+        <v>33.9468721174462</v>
       </c>
       <c r="D9" t="n">
-        <v>41.82343394861835</v>
+        <v>42.15624642035802</v>
       </c>
     </row>
     <row r="10">
@@ -5560,10 +5560,10 @@
         <v>9.964739198105127</v>
       </c>
       <c r="C10" t="n">
-        <v>33.31069960509428</v>
+        <v>33.59540643932586</v>
       </c>
       <c r="D10" t="n">
-        <v>49.25428232206248</v>
+        <v>48.68486865359933</v>
       </c>
     </row>
     <row r="11">
@@ -5574,7 +5574,7 @@
         <v>8.707120388964958</v>
       </c>
       <c r="C11" t="n">
-        <v>33.40691088011046</v>
+        <v>33.58460721457913</v>
       </c>
       <c r="D11" t="n">
         <v>50.82115165804038</v>
@@ -5585,10 +5585,10 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>7.159886007071988</v>
+        <v>7.376852249710534</v>
       </c>
       <c r="C12" t="n">
-        <v>34.49763257952867</v>
+        <v>33.84673385161303</v>
       </c>
       <c r="D12" t="n">
         <v>47.08167465256428</v>
@@ -5616,7 +5616,7 @@
         <v>4.609305471438775</v>
       </c>
       <c r="C14" t="n">
-        <v>30.42141611149592</v>
+        <v>30.72870314292517</v>
       </c>
       <c r="D14" t="n">
         <v>45.47848065152925</v>
@@ -5630,7 +5630,7 @@
         <v>4.30005494460103</v>
       </c>
       <c r="C15" t="n">
-        <v>29.02537087605695</v>
+        <v>28.66703296400686</v>
       </c>
       <c r="D15" t="n">
         <v>43.71722527011046</v>
@@ -5647,7 +5647,7 @@
         <v>30.17205219461722</v>
       </c>
       <c r="D16" t="n">
-        <v>41.33157834879071</v>
+        <v>41.74489413227862</v>
       </c>
     </row>
     <row r="17">
@@ -5658,10 +5658,10 @@
         <v>4.722206457427158</v>
       </c>
       <c r="C17" t="n">
-        <v>32.11100391050468</v>
+        <v>32.58322455624739</v>
       </c>
       <c r="D17" t="n">
-        <v>37.30543101367455</v>
+        <v>36.83321036793183</v>
       </c>
     </row>
     <row r="18">
@@ -5711,13 +5711,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>18.05735109409622</v>
+        <v>18.05216934936604</v>
       </c>
       <c r="C21" t="n">
-        <v>117.8027190424372</v>
+        <v>117.7689143268165</v>
       </c>
       <c r="D21" t="n">
-        <v>6.878990892989035</v>
+        <v>6.017389783122013</v>
       </c>
     </row>
   </sheetData>
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.228207435741766</v>
+        <v>5.877723505325654</v>
       </c>
       <c r="C2" t="n">
-        <v>6.753442457513809</v>
+        <v>5.4172838320339</v>
       </c>
       <c r="D2" t="n">
-        <v>29.61441949860503</v>
+        <v>19.0999015861217</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>17.44074796594459</v>
+        <v>15.73741569907637</v>
       </c>
       <c r="C3" t="n">
-        <v>18.6826588118168</v>
+        <v>19.90002596508285</v>
       </c>
       <c r="D3" t="n">
-        <v>58.63979037466198</v>
+        <v>43.38833978918779</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>25.64030479181395</v>
+        <v>22.65382827549515</v>
       </c>
       <c r="C4" t="n">
-        <v>42.41051907575796</v>
+        <v>49.50659148205391</v>
       </c>
       <c r="D4" t="n">
-        <v>56.90896917207485</v>
+        <v>42.34670547498192</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>24.22462460229005</v>
+        <v>20.93576979306323</v>
       </c>
       <c r="C5" t="n">
-        <v>47.61476365597031</v>
+        <v>64.86897955810801</v>
       </c>
       <c r="D5" t="n">
-        <v>37.92000507653306</v>
+        <v>31.44047022850411</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>13.48430471782994</v>
+        <v>11.55222523587222</v>
       </c>
       <c r="C6" t="n">
-        <v>24.67426505083509</v>
+        <v>54.66174867705392</v>
       </c>
       <c r="D6" t="n">
-        <v>32.56358960216246</v>
+        <v>31.27553661419064</v>
       </c>
     </row>
     <row r="7">
@@ -5826,13 +5826,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>5.689227946110266</v>
+        <v>5.270021676396877</v>
       </c>
       <c r="C7" t="n">
-        <v>13.41460063082842</v>
+        <v>26.52976821186155</v>
       </c>
       <c r="D7" t="n">
-        <v>30.66194429903638</v>
+        <v>30.78171751895449</v>
       </c>
     </row>
     <row r="8">
@@ -5843,10 +5843,10 @@
         <v>4.840016181936775</v>
       </c>
       <c r="C8" t="n">
-        <v>18.60902773399829</v>
+        <v>18.52557917913731</v>
       </c>
       <c r="D8" t="n">
-        <v>30.12492830481337</v>
+        <v>30.0414797499524</v>
       </c>
     </row>
     <row r="9">
@@ -5857,10 +5857,10 @@
         <v>4.881249585515139</v>
       </c>
       <c r="C9" t="n">
-        <v>21.85468564423824</v>
+        <v>22.07656062539802</v>
       </c>
       <c r="D9" t="n">
-        <v>29.84218496599028</v>
+        <v>29.95312245657017</v>
       </c>
     </row>
     <row r="10">
@@ -5868,13 +5868,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4.270602513473626</v>
+        <v>4.412955930589413</v>
       </c>
       <c r="C10" t="n">
-        <v>21.49536598448391</v>
+        <v>21.35301256736813</v>
       </c>
       <c r="D10" t="n">
-        <v>33.73775985644164</v>
+        <v>33.45305302221006</v>
       </c>
     </row>
     <row r="11">
@@ -5885,10 +5885,10 @@
         <v>3.731623023842126</v>
       </c>
       <c r="C11" t="n">
-        <v>20.25738212942868</v>
+        <v>20.43507846389736</v>
       </c>
       <c r="D11" t="n">
-        <v>34.47308888692249</v>
+        <v>34.29539255245382</v>
       </c>
     </row>
     <row r="12">
@@ -5896,7 +5896,7 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>2.820561154301086</v>
+        <v>3.037527396939631</v>
       </c>
       <c r="C12" t="n">
         <v>19.7439280801076</v>
@@ -5913,10 +5913,10 @@
         <v>2.341468274628643</v>
       </c>
       <c r="C13" t="n">
-        <v>19.25207248027995</v>
+        <v>18.99190933865455</v>
       </c>
       <c r="D13" t="n">
-        <v>30.17892442854696</v>
+        <v>30.43908757017236</v>
       </c>
     </row>
     <row r="14">
@@ -5930,7 +5930,7 @@
         <v>17.51536079146734</v>
       </c>
       <c r="D14" t="n">
-        <v>29.80684204863741</v>
+        <v>29.49955501720816</v>
       </c>
     </row>
     <row r="15">
@@ -5941,7 +5941,7 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>16.12520604225386</v>
+        <v>15.76686813020377</v>
       </c>
       <c r="D15" t="n">
         <v>28.30869505195678</v>
@@ -5958,7 +5958,7 @@
         <v>15.70599977254047</v>
       </c>
       <c r="D16" t="n">
-        <v>26.03889435973815</v>
+        <v>26.45221014322606</v>
       </c>
     </row>
     <row r="17">
@@ -5969,7 +5969,7 @@
         <v>1.416661937228147</v>
       </c>
       <c r="C17" t="n">
-        <v>16.05550195525234</v>
+        <v>16.52772260099505</v>
       </c>
       <c r="D17" t="n">
         <v>23.61103228713579</v>
@@ -5980,7 +5980,7 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1.605157496443535</v>
+        <v>1.070104997629023</v>
       </c>
       <c r="C18" t="n">
         <v>17.65673246087889</v>
@@ -6011,7 +6011,7 @@
         <v>1.34499435481813</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>18.82992096745382</v>
       </c>
       <c r="D20" t="n">
         <v>10.08745766113597</v>
@@ -6022,13 +6022,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.057936138682341</v>
+        <v>7.054188382822082</v>
       </c>
       <c r="C21" t="n">
-        <v>66.16815130014695</v>
+        <v>66.13301608895702</v>
       </c>
       <c r="D21" t="n">
-        <v>5.293452104011755</v>
+        <v>4.408867739263802</v>
       </c>
     </row>
   </sheetData>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.659775514982861</v>
+        <v>4.844924920458009</v>
       </c>
       <c r="C2" t="n">
-        <v>5.424156065963627</v>
+        <v>4.565126824747668</v>
       </c>
       <c r="D2" t="n">
-        <v>30.23881103850601</v>
+        <v>20.03550714826891</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>20.18473279931442</v>
+        <v>18.76119862815655</v>
       </c>
       <c r="C3" t="n">
-        <v>23.74356822720911</v>
+        <v>20.71978529812893</v>
       </c>
       <c r="D3" t="n">
-        <v>70.52875507309086</v>
+        <v>48.94503179522474</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>31.17932533917445</v>
+        <v>27.92483169959628</v>
       </c>
       <c r="C4" t="n">
-        <v>45.30765655099029</v>
+        <v>49.82565948593412</v>
       </c>
       <c r="D4" t="n">
-        <v>73.89614969865741</v>
+        <v>54.85417122708628</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>32.59402378099411</v>
+        <v>28.59340188618836</v>
       </c>
       <c r="C5" t="n">
-        <v>66.80793127399546</v>
+        <v>80.65057390387548</v>
       </c>
       <c r="D5" t="n">
-        <v>51.17359908386501</v>
+        <v>40.54618018539328</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>24.79502001845745</v>
+        <v>21.37362926915731</v>
       </c>
       <c r="C6" t="n">
-        <v>55.10451689166923</v>
+        <v>83.76369587404213</v>
       </c>
       <c r="D6" t="n">
-        <v>37.43403996293088</v>
+        <v>34.41516577237194</v>
       </c>
     </row>
     <row r="7">
@@ -6137,13 +6137,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>11.67788894201581</v>
+        <v>10.24061030299848</v>
       </c>
       <c r="C7" t="n">
-        <v>26.64954143177966</v>
+        <v>57.61091878061132</v>
       </c>
       <c r="D7" t="n">
-        <v>33.77604801690726</v>
+        <v>33.53650157707104</v>
       </c>
     </row>
     <row r="8">
@@ -6151,10 +6151,10 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>5.757950285407543</v>
+        <v>5.507604620824606</v>
       </c>
       <c r="C8" t="n">
-        <v>18.60902773399829</v>
+        <v>28.62285431731576</v>
       </c>
       <c r="D8" t="n">
         <v>32.12769362147687</v>
@@ -6168,10 +6168,10 @@
         <v>5.214062057254808</v>
       </c>
       <c r="C9" t="n">
-        <v>23.2968730217768</v>
+        <v>23.40781051235669</v>
       </c>
       <c r="D9" t="n">
-        <v>30.95155987178918</v>
+        <v>31.06249736236907</v>
       </c>
     </row>
     <row r="10">
@@ -6179,13 +6179,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4.697662764820988</v>
+        <v>4.840016181936776</v>
       </c>
       <c r="C10" t="n">
         <v>24.76949457814703</v>
       </c>
       <c r="D10" t="n">
-        <v>34.16482010778901</v>
+        <v>33.88011327355743</v>
       </c>
     </row>
     <row r="11">
@@ -6199,7 +6199,7 @@
         <v>23.45591614986479</v>
       </c>
       <c r="D11" t="n">
-        <v>35.36157055926586</v>
+        <v>35.18387422479719</v>
       </c>
     </row>
     <row r="12">
@@ -6210,7 +6210,7 @@
         <v>3.254493639578176</v>
       </c>
       <c r="C12" t="n">
-        <v>21.69662426385451</v>
+        <v>22.1305567491316</v>
       </c>
       <c r="D12" t="n">
         <v>32.97886888105885</v>
@@ -6221,13 +6221,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.341468274628643</v>
+        <v>2.601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>21.07321447165778</v>
+        <v>20.81305133003238</v>
       </c>
       <c r="D13" t="n">
-        <v>30.95941385342317</v>
+        <v>31.21957699504857</v>
       </c>
     </row>
     <row r="14">
@@ -6252,7 +6252,7 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>17.91689560250429</v>
+        <v>17.5585576904542</v>
       </c>
       <c r="D15" t="n">
         <v>28.30869505195678</v>
@@ -6269,7 +6269,7 @@
         <v>16.53263133951629</v>
       </c>
       <c r="D16" t="n">
-        <v>26.45221014322606</v>
+        <v>26.86552592671396</v>
       </c>
     </row>
     <row r="17">
@@ -6280,7 +6280,7 @@
         <v>0.9444412914854317</v>
       </c>
       <c r="C17" t="n">
-        <v>16.52772260099505</v>
+        <v>16.99994324673777</v>
       </c>
       <c r="D17" t="n">
         <v>24.0832529328785</v>
@@ -6305,7 +6305,7 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1.203622685406589</v>
+        <v>0.6018113427032947</v>
       </c>
       <c r="C19" t="n">
         <v>18.65615162380213</v>
@@ -6322,7 +6322,7 @@
         <v>0.672497177409065</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>18.82992096745382</v>
       </c>
       <c r="D20" t="n">
         <v>10.75995483854504</v>
@@ -6333,13 +6333,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.281053169084593</v>
+        <v>7.276588728012793</v>
       </c>
       <c r="C21" t="n">
-        <v>75.54092662925267</v>
+        <v>75.49460805313272</v>
       </c>
       <c r="D21" t="n">
-        <v>6.370921522949019</v>
+        <v>5.457441546009594</v>
       </c>
     </row>
   </sheetData>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.818417732443345</v>
+        <v>4.101741908343174</v>
       </c>
       <c r="C2" t="n">
-        <v>6.058365082907066</v>
+        <v>6.417684742661399</v>
       </c>
       <c r="D2" t="n">
-        <v>32.86694964277471</v>
+        <v>19.68207797474005</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>19.86075605691298</v>
+        <v>17.64691498383642</v>
       </c>
       <c r="C3" t="n">
-        <v>22.14331946928681</v>
+        <v>18.9280957378785</v>
       </c>
       <c r="D3" t="n">
-        <v>78.35328427593794</v>
+        <v>53.61815086743955</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>35.72285371442869</v>
+        <v>32.72361447795468</v>
       </c>
       <c r="C4" t="n">
-        <v>53.66723825265188</v>
+        <v>51.07640606114455</v>
       </c>
       <c r="D4" t="n">
-        <v>92.65734832681397</v>
+        <v>67.08085713577607</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>40.76707341884881</v>
+        <v>36.22649028670731</v>
       </c>
       <c r="C5" t="n">
-        <v>75.88909753827845</v>
+        <v>86.49197274414401</v>
       </c>
       <c r="D5" t="n">
-        <v>65.7034651067178</v>
+        <v>50.75635630956011</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>35.30070220160257</v>
+        <v>30.79251674370121</v>
       </c>
       <c r="C6" t="n">
-        <v>83.723444218168</v>
+        <v>108.8404774836184</v>
       </c>
       <c r="D6" t="n">
-        <v>45.36361617013237</v>
+        <v>39.7686360036298</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>21.43940636534185</v>
+        <v>18.56484908730718</v>
       </c>
       <c r="C7" t="n">
-        <v>55.87420709179872</v>
+        <v>93.00390526641308</v>
       </c>
       <c r="D7" t="n">
-        <v>36.9500383447372</v>
+        <v>35.93196597543326</v>
       </c>
     </row>
     <row r="8">
@@ -6462,13 +6462,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>9.513135254151592</v>
+        <v>8.595201150680824</v>
       </c>
       <c r="C8" t="n">
-        <v>28.03871443328891</v>
+        <v>54.9091490985241</v>
       </c>
       <c r="D8" t="n">
-        <v>34.38080460272329</v>
+        <v>34.29735604786232</v>
       </c>
     </row>
     <row r="9">
@@ -6476,13 +6476,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.768749510154256</v>
+        <v>5.657812019574366</v>
       </c>
       <c r="C9" t="n">
-        <v>23.74062298409636</v>
+        <v>30.28593492830985</v>
       </c>
       <c r="D9" t="n">
-        <v>32.50468473990763</v>
+        <v>32.61562223048752</v>
       </c>
     </row>
     <row r="10">
@@ -6490,13 +6490,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4.982369599052563</v>
+        <v>5.124723016168351</v>
       </c>
       <c r="C10" t="n">
         <v>27.18950266911542</v>
       </c>
       <c r="D10" t="n">
-        <v>34.30717352490479</v>
+        <v>34.02246669067321</v>
       </c>
     </row>
     <row r="11">
@@ -6510,7 +6510,7 @@
         <v>26.83214650476957</v>
       </c>
       <c r="D11" t="n">
-        <v>36.07235589714055</v>
+        <v>35.89465956267188</v>
       </c>
     </row>
     <row r="12">
@@ -6521,7 +6521,7 @@
         <v>3.471459882216721</v>
       </c>
       <c r="C12" t="n">
-        <v>24.73415166079414</v>
+        <v>24.95111790343269</v>
       </c>
       <c r="D12" t="n">
         <v>33.62976760897449</v>
@@ -6538,7 +6538,7 @@
         <v>22.89435646303562</v>
       </c>
       <c r="D13" t="n">
-        <v>31.73990327829938</v>
+        <v>32.00006641992479</v>
       </c>
     </row>
     <row r="14">
@@ -6546,13 +6546,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.536435157146258</v>
+        <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
         <v>21.51009220004762</v>
       </c>
       <c r="D14" t="n">
-        <v>30.42141611149592</v>
+        <v>30.72870314292517</v>
       </c>
     </row>
     <row r="15">
@@ -6563,7 +6563,7 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>19.70858516275472</v>
+        <v>19.35024725070463</v>
       </c>
       <c r="D15" t="n">
         <v>28.30869505195678</v>
@@ -6580,7 +6580,7 @@
         <v>17.77257868998001</v>
       </c>
       <c r="D16" t="n">
-        <v>26.86552592671396</v>
+        <v>27.27884171020187</v>
       </c>
     </row>
     <row r="17">
@@ -6591,7 +6591,7 @@
         <v>0.9444412914854317</v>
       </c>
       <c r="C17" t="n">
-        <v>16.99994324673777</v>
+        <v>17.47216389248049</v>
       </c>
       <c r="D17" t="n">
         <v>24.55547357862122</v>
@@ -6630,10 +6630,10 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>0.672497177409065</v>
+        <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>18.82992096745382</v>
       </c>
       <c r="D20" t="n">
         <v>10.75995483854504</v>
@@ -6644,13 +6644,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.492094194490036</v>
+        <v>7.487216044833052</v>
       </c>
       <c r="C21" t="n">
-        <v>85.22257146232417</v>
+        <v>84.23118050437184</v>
       </c>
       <c r="D21" t="n">
-        <v>7.492094194490036</v>
+        <v>6.55131403922892</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_surface_area_iteration_56_growth_param_0.5.xlsx
+++ b/output/yearly_surface_area_iteration_56_growth_param_0.5.xlsx
@@ -735,10 +735,10 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>10.84497626653378</v>
+        <v>10.84497630196448</v>
       </c>
       <c r="C21" t="n">
-        <v>37.78907171304459</v>
+        <v>37.78907183650206</v>
       </c>
       <c r="D21" t="n">
         <v>0</v>
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.114905539125882</v>
+        <v>4.233296100712247</v>
       </c>
       <c r="C2" t="n">
-        <v>12.67632635723482</v>
+        <v>7.675303551801563</v>
       </c>
       <c r="D2" t="n">
-        <v>18.80734077025615</v>
+        <v>17.99641716654828</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>15.66378462125786</v>
+        <v>16.09084487260522</v>
       </c>
       <c r="C3" t="n">
-        <v>22.29549036344507</v>
+        <v>41.14504628498383</v>
       </c>
       <c r="D3" t="n">
-        <v>56.6517512735622</v>
+        <v>66.90610604442013</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>33.59147944850886</v>
+        <v>31.48563062289946</v>
       </c>
       <c r="C4" t="n">
-        <v>49.02160811615598</v>
+        <v>70.48850341721673</v>
       </c>
       <c r="D4" t="n">
-        <v>78.22271183127312</v>
+        <v>97.2008767020682</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>42.65693774952392</v>
+        <v>36.52101459798135</v>
       </c>
       <c r="C5" t="n">
-        <v>89.82991493858316</v>
+        <v>112.0419567471673</v>
       </c>
       <c r="D5" t="n">
-        <v>62.24280444924779</v>
+        <v>74.66191290796993</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>40.37241084174159</v>
+        <v>33.52962934314132</v>
       </c>
       <c r="C6" t="n">
-        <v>124.1361067157837</v>
+        <v>141.0820538387879</v>
       </c>
       <c r="D6" t="n">
-        <v>46.69192081397831</v>
+        <v>50.27431818677493</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>27.60772719112455</v>
+        <v>23.89475737366311</v>
       </c>
       <c r="C7" t="n">
-        <v>126.7200666733613</v>
+        <v>129.4748507314779</v>
       </c>
       <c r="D7" t="n">
-        <v>39.40538935305847</v>
+        <v>39.70482240285375</v>
       </c>
     </row>
     <row r="8">
@@ -864,10 +864,10 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>14.35315143608837</v>
+        <v>12.93452600345173</v>
       </c>
       <c r="C8" t="n">
-        <v>89.45685081096936</v>
+        <v>84.11614329986671</v>
       </c>
       <c r="D8" t="n">
         <v>36.04977569994287</v>
@@ -878,13 +878,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>7.321874378272709</v>
+        <v>7.09999939711293</v>
       </c>
       <c r="C9" t="n">
-        <v>49.92187076095029</v>
+        <v>45.26249615659493</v>
       </c>
       <c r="D9" t="n">
-        <v>34.27968458918587</v>
+        <v>33.9468721174462</v>
       </c>
     </row>
     <row r="10">
@@ -892,13 +892,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>5.409429850399925</v>
+        <v>5.267076433284139</v>
       </c>
       <c r="C10" t="n">
-        <v>32.31422568528377</v>
+        <v>31.03304493124168</v>
       </c>
       <c r="D10" t="n">
-        <v>34.44952694202058</v>
+        <v>34.73423377625215</v>
       </c>
     </row>
     <row r="11">
@@ -906,13 +906,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.797801030654161</v>
+        <v>4.620104696185489</v>
       </c>
       <c r="C11" t="n">
-        <v>29.49759152179966</v>
+        <v>28.96450251839364</v>
       </c>
       <c r="D11" t="n">
-        <v>36.42774856607789</v>
+        <v>35.89465956267188</v>
       </c>
     </row>
     <row r="12">
@@ -923,10 +923,10 @@
         <v>3.688426124855267</v>
       </c>
       <c r="C12" t="n">
-        <v>27.98864530037232</v>
+        <v>27.55471281509523</v>
       </c>
       <c r="D12" t="n">
-        <v>34.28066633689012</v>
+        <v>35.1485313074443</v>
       </c>
     </row>
     <row r="13">
@@ -937,10 +937,10 @@
         <v>2.861794557879452</v>
       </c>
       <c r="C13" t="n">
-        <v>25.23582473766426</v>
+        <v>25.49598787928967</v>
       </c>
       <c r="D13" t="n">
-        <v>32.780555844801</v>
+        <v>32.00006641992479</v>
       </c>
     </row>
     <row r="14">
@@ -948,13 +948,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.84372218857551</v>
+        <v>2.151009220004762</v>
       </c>
       <c r="C14" t="n">
         <v>23.35381438862312</v>
       </c>
       <c r="D14" t="n">
-        <v>31.03599017435442</v>
+        <v>30.72870314292517</v>
       </c>
     </row>
     <row r="15">
@@ -968,7 +968,7 @@
         <v>21.14193681095506</v>
       </c>
       <c r="D15" t="n">
-        <v>28.30869505195678</v>
+        <v>29.38370878810703</v>
       </c>
     </row>
     <row r="16">
@@ -979,10 +979,10 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>19.01252604044373</v>
+        <v>18.59921025695582</v>
       </c>
       <c r="D16" t="n">
-        <v>27.27884171020187</v>
+        <v>26.03889435973815</v>
       </c>
     </row>
     <row r="17">
@@ -996,7 +996,7 @@
         <v>17.9443845382232</v>
       </c>
       <c r="D17" t="n">
-        <v>24.55547357862122</v>
+        <v>24.0832529328785</v>
       </c>
     </row>
     <row r="18">
@@ -1035,7 +1035,7 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>18.82992096745382</v>
+        <v>19.50241814486288</v>
       </c>
       <c r="D20" t="n">
         <v>10.75995483854504</v>
@@ -1046,13 +1046,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.684937796676213</v>
+        <v>7.669499982965761</v>
       </c>
       <c r="C21" t="n">
-        <v>93.17987078469908</v>
+        <v>94.91006228920131</v>
       </c>
       <c r="D21" t="n">
-        <v>7.684937796676213</v>
+        <v>7.669499982965761</v>
       </c>
     </row>
   </sheetData>
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.638577976116932</v>
+        <v>5.970989537229101</v>
       </c>
       <c r="C2" t="n">
-        <v>18.62277220185775</v>
+        <v>13.43914432343459</v>
       </c>
       <c r="D2" t="n">
-        <v>16.22632605579128</v>
+        <v>19.75374555715007</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>16.33137306014569</v>
+        <v>15.03055735201867</v>
       </c>
       <c r="C3" t="n">
-        <v>36.34430001121692</v>
+        <v>35.18583772020568</v>
       </c>
       <c r="D3" t="n">
-        <v>57.92802328908305</v>
+        <v>65.54638547403829</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>31.44734246243383</v>
+        <v>30.70710469343173</v>
       </c>
       <c r="C4" t="n">
-        <v>52.37820351697583</v>
+        <v>85.49746231974197</v>
       </c>
       <c r="D4" t="n">
-        <v>86.36532729029615</v>
+        <v>106.7601540983194</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>46.19122948481243</v>
+        <v>41.55247158224626</v>
       </c>
       <c r="C5" t="n">
-        <v>89.16723523821656</v>
+        <v>120.5340743889022</v>
       </c>
       <c r="D5" t="n">
-        <v>74.73554398578845</v>
+        <v>88.89725461954869</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>48.94601354292898</v>
+        <v>40.53341746523807</v>
       </c>
       <c r="C6" t="n">
-        <v>133.5549941903276</v>
+        <v>157.1827161884356</v>
       </c>
       <c r="D6" t="n">
-        <v>54.09822549481625</v>
+        <v>60.65924540229769</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>37.12969817461437</v>
+        <v>31.14103717870882</v>
       </c>
       <c r="C7" t="n">
-        <v>151.5131231964102</v>
+        <v>164.8678372172796</v>
       </c>
       <c r="D7" t="n">
-        <v>43.71722527011047</v>
+        <v>44.01665831990574</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>21.61317570899353</v>
+        <v>18.94282195344221</v>
       </c>
       <c r="C8" t="n">
-        <v>127.7597374921587</v>
+        <v>123.8376554136927</v>
       </c>
       <c r="D8" t="n">
-        <v>38.05254101660637</v>
+        <v>38.46978379091126</v>
       </c>
     </row>
     <row r="9">
@@ -1189,13 +1189,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>10.76093658624928</v>
+        <v>9.762499171030278</v>
       </c>
       <c r="C9" t="n">
-        <v>78.4328058399819</v>
+        <v>72.55311883924776</v>
       </c>
       <c r="D9" t="n">
-        <v>35.83280945730432</v>
+        <v>35.16718451382499</v>
       </c>
     </row>
     <row r="10">
@@ -1203,13 +1203,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>6.26355035309465</v>
+        <v>5.978843518863076</v>
       </c>
       <c r="C10" t="n">
-        <v>45.26838664282043</v>
+        <v>41.28249096357838</v>
       </c>
       <c r="D10" t="n">
-        <v>35.01894061048373</v>
+        <v>35.58835427894688</v>
       </c>
     </row>
     <row r="11">
@@ -1217,13 +1217,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.975497365122834</v>
+        <v>4.797801030654161</v>
       </c>
       <c r="C11" t="n">
-        <v>33.40691088011046</v>
+        <v>32.51842920776709</v>
       </c>
       <c r="D11" t="n">
-        <v>36.78314123501524</v>
+        <v>36.07235589714055</v>
       </c>
     </row>
     <row r="12">
@@ -1234,10 +1234,10 @@
         <v>3.905392367493811</v>
       </c>
       <c r="C12" t="n">
-        <v>31.02617269731195</v>
+        <v>29.94134148411922</v>
       </c>
       <c r="D12" t="n">
-        <v>35.1485313074443</v>
+        <v>35.79943003535993</v>
       </c>
     </row>
     <row r="13">
@@ -1251,7 +1251,7 @@
         <v>28.09761929554372</v>
       </c>
       <c r="D13" t="n">
-        <v>33.04071898642641</v>
+        <v>32.5203927031756</v>
       </c>
     </row>
     <row r="14">
@@ -1259,13 +1259,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.84372218857551</v>
+        <v>2.151009220004762</v>
       </c>
       <c r="C14" t="n">
         <v>25.19753657719863</v>
       </c>
       <c r="D14" t="n">
-        <v>31.34327720578367</v>
+        <v>31.03599017435442</v>
       </c>
     </row>
     <row r="15">
@@ -1279,7 +1279,7 @@
         <v>22.93362637120549</v>
       </c>
       <c r="D15" t="n">
-        <v>28.30869505195678</v>
+        <v>29.74204670015712</v>
       </c>
     </row>
     <row r="16">
@@ -1290,10 +1290,10 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>20.25247339090745</v>
+        <v>19.83915760741954</v>
       </c>
       <c r="D16" t="n">
-        <v>27.27884171020187</v>
+        <v>26.03889435973815</v>
       </c>
     </row>
     <row r="17">
@@ -1307,7 +1307,7 @@
         <v>18.88882582970863</v>
       </c>
       <c r="D17" t="n">
-        <v>24.55547357862122</v>
+        <v>24.0832529328785</v>
       </c>
     </row>
     <row r="18">
@@ -1346,7 +1346,7 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>18.82992096745382</v>
+        <v>19.50241814486288</v>
       </c>
       <c r="D20" t="n">
         <v>10.75995483854504</v>
@@ -1357,13 +1357,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.868392550820402</v>
+        <v>7.845700542175535</v>
       </c>
       <c r="C21" t="n">
-        <v>101.3055540918127</v>
+        <v>102.9748196160539</v>
       </c>
       <c r="D21" t="n">
-        <v>8.851941619672953</v>
+        <v>8.826413109947476</v>
       </c>
     </row>
   </sheetData>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>9.062513057902306</v>
+        <v>6.117269945161876</v>
       </c>
       <c r="C2" t="n">
-        <v>18.59921025695582</v>
+        <v>12.02935462013617</v>
       </c>
       <c r="D2" t="n">
-        <v>18.88588058659589</v>
+        <v>22.88748422910589</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>18.83973844449629</v>
+        <v>16.90078672860884</v>
       </c>
       <c r="C3" t="n">
-        <v>53.10273332270997</v>
+        <v>43.10363295495621</v>
       </c>
       <c r="D3" t="n">
-        <v>57.09353774047326</v>
+        <v>65.33530971762524</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>30.98788453684632</v>
+        <v>29.06071379340984</v>
       </c>
       <c r="C4" t="n">
-        <v>69.37814676371359</v>
+        <v>85.42088599881073</v>
       </c>
       <c r="D4" t="n">
-        <v>93.60178961829939</v>
+        <v>111.6482759177643</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>46.36303533305563</v>
+        <v>43.04963683122264</v>
       </c>
       <c r="C5" t="n">
-        <v>91.4497986505904</v>
+        <v>134.9657656413303</v>
       </c>
       <c r="D5" t="n">
-        <v>84.89663272474294</v>
+        <v>102.9362467902781</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>54.58124536530568</v>
+        <v>46.73217246985243</v>
       </c>
       <c r="C6" t="n">
-        <v>137.6606630894878</v>
+        <v>172.1160805177338</v>
       </c>
       <c r="D6" t="n">
-        <v>63.23535137824131</v>
+        <v>70.68190771495337</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>46.17257627843174</v>
+        <v>38.50709020367265</v>
       </c>
       <c r="C7" t="n">
-        <v>169.3593329642087</v>
+        <v>190.19987322996</v>
       </c>
       <c r="D7" t="n">
-        <v>47.84940135728529</v>
+        <v>49.88554609589318</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>29.6242369756475</v>
+        <v>24.86766934857171</v>
       </c>
       <c r="C8" t="n">
-        <v>161.1391594365502</v>
+        <v>162.9750276434918</v>
       </c>
       <c r="D8" t="n">
-        <v>40.72289477215769</v>
+        <v>40.55599766243574</v>
       </c>
     </row>
     <row r="9">
@@ -1500,13 +1500,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>15.53124868118453</v>
+        <v>13.42343636016663</v>
       </c>
       <c r="C9" t="n">
-        <v>112.490615448008</v>
+        <v>106.7218659378537</v>
       </c>
       <c r="D9" t="n">
-        <v>36.94218436310322</v>
+        <v>36.83124687252333</v>
       </c>
     </row>
     <row r="10">
@@ -1514,13 +1514,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>7.971791358484101</v>
+        <v>7.260024272905163</v>
       </c>
       <c r="C10" t="n">
-        <v>65.34021845614647</v>
+        <v>59.07666810305182</v>
       </c>
       <c r="D10" t="n">
-        <v>36.01541453029424</v>
+        <v>35.87306111317846</v>
       </c>
     </row>
     <row r="11">
@@ -1528,13 +1528,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>5.330890034060179</v>
+        <v>5.153193699591506</v>
       </c>
       <c r="C11" t="n">
-        <v>41.75863860013807</v>
+        <v>38.56010457970196</v>
       </c>
       <c r="D11" t="n">
-        <v>36.78314123501524</v>
+        <v>36.60544490054656</v>
       </c>
     </row>
     <row r="12">
@@ -1545,7 +1545,7 @@
         <v>4.122358610132356</v>
       </c>
       <c r="C12" t="n">
-        <v>33.84673385161303</v>
+        <v>32.97886888105885</v>
       </c>
       <c r="D12" t="n">
         <v>35.79943003535993</v>
@@ -1556,10 +1556,10 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>3.121957699504857</v>
+        <v>2.861794557879452</v>
       </c>
       <c r="C13" t="n">
-        <v>30.95941385342317</v>
+        <v>30.17892442854696</v>
       </c>
       <c r="D13" t="n">
         <v>33.30088212805181</v>
@@ -1570,13 +1570,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.84372218857551</v>
+        <v>2.151009220004762</v>
       </c>
       <c r="C14" t="n">
         <v>27.3485457972034</v>
       </c>
       <c r="D14" t="n">
-        <v>31.65056423721292</v>
+        <v>31.03599017435442</v>
       </c>
     </row>
     <row r="15">
@@ -1587,10 +1587,10 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>24.36697801940583</v>
+        <v>24.72531593145592</v>
       </c>
       <c r="D15" t="n">
-        <v>28.30869505195678</v>
+        <v>29.74204670015712</v>
       </c>
     </row>
     <row r="16">
@@ -1601,10 +1601,10 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>21.90573652485908</v>
+        <v>21.07910495788326</v>
       </c>
       <c r="D16" t="n">
-        <v>27.27884171020187</v>
+        <v>26.45221014322606</v>
       </c>
     </row>
     <row r="17">
@@ -1615,10 +1615,10 @@
         <v>0.9444412914854317</v>
       </c>
       <c r="C17" t="n">
-        <v>19.83326712119407</v>
+        <v>19.36104647545135</v>
       </c>
       <c r="D17" t="n">
-        <v>24.55547357862122</v>
+        <v>24.0832529328785</v>
       </c>
     </row>
     <row r="18">
@@ -1657,7 +1657,7 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>18.82992096745382</v>
+        <v>19.50241814486288</v>
       </c>
       <c r="D20" t="n">
         <v>10.75995483854504</v>
@@ -1668,13 +1668,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8.036602421951322</v>
+        <v>8.005568980755079</v>
       </c>
       <c r="C21" t="n">
-        <v>109.4987079990867</v>
+        <v>111.0772696079767</v>
       </c>
       <c r="D21" t="n">
-        <v>10.04575302743915</v>
+        <v>10.00696122594385</v>
       </c>
     </row>
   </sheetData>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>8.06113039957056</v>
+        <v>5.648976290236146</v>
       </c>
       <c r="C2" t="n">
-        <v>12.49863002276614</v>
+        <v>8.276133146800611</v>
       </c>
       <c r="D2" t="n">
-        <v>15.54695664445249</v>
+        <v>18.93693146721673</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>22.19240685449915</v>
+        <v>20.17491532227195</v>
       </c>
       <c r="C3" t="n">
-        <v>73.64089529555325</v>
+        <v>61.99245878466484</v>
       </c>
       <c r="D3" t="n">
-        <v>63.32763566244051</v>
+        <v>72.77695731581605</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>22.27094667083889</v>
+        <v>20.67560665143782</v>
       </c>
       <c r="C4" t="n">
-        <v>84.27224118484196</v>
+        <v>113.2946668177862</v>
       </c>
       <c r="D4" t="n">
-        <v>92.08302591982958</v>
+        <v>109.8742578161903</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>30.72870314292517</v>
+        <v>26.31083847381452</v>
       </c>
       <c r="C5" t="n">
-        <v>82.24591392327655</v>
+        <v>102.8380720198534</v>
       </c>
       <c r="D5" t="n">
-        <v>61.408318900638</v>
+        <v>69.90043654237292</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>28.6591789823729</v>
+        <v>23.90948358922682</v>
       </c>
       <c r="C6" t="n">
-        <v>111.5373384271844</v>
+        <v>125.2631530802591</v>
       </c>
       <c r="D6" t="n">
-        <v>31.51704654943536</v>
+        <v>32.8453511932813</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>19.64280806657018</v>
+        <v>16.46881773874025</v>
       </c>
       <c r="C7" t="n">
-        <v>113.3054660425329</v>
+        <v>114.563084851673</v>
       </c>
       <c r="D7" t="n">
-        <v>28.62579956042849</v>
+        <v>28.50602634051038</v>
       </c>
     </row>
     <row r="8">
@@ -1797,13 +1797,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.76486357706628</v>
+        <v>9.262789589568655</v>
       </c>
       <c r="C8" t="n">
-        <v>82.86441497695203</v>
+        <v>78.60853867904211</v>
       </c>
       <c r="D8" t="n">
-        <v>27.20422888467911</v>
+        <v>27.12078032981814</v>
       </c>
     </row>
     <row r="9">
@@ -1811,13 +1811,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.657812019574366</v>
+        <v>5.214062057254808</v>
       </c>
       <c r="C9" t="n">
-        <v>49.81093327037041</v>
+        <v>45.04062117543515</v>
       </c>
       <c r="D9" t="n">
-        <v>27.40156017323271</v>
+        <v>27.29062268265283</v>
       </c>
     </row>
     <row r="10">
@@ -1825,13 +1825,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>3.843542262126263</v>
+        <v>3.701188845010476</v>
       </c>
       <c r="C10" t="n">
-        <v>32.74128593663113</v>
+        <v>30.17892442854695</v>
       </c>
       <c r="D10" t="n">
-        <v>28.75539025738908</v>
+        <v>28.61303684027329</v>
       </c>
     </row>
     <row r="11">
@@ -1842,7 +1842,7 @@
         <v>3.020837685967435</v>
       </c>
       <c r="C11" t="n">
-        <v>27.00984283923824</v>
+        <v>26.29905750136355</v>
       </c>
       <c r="D11" t="n">
         <v>28.60910984945629</v>
@@ -1853,10 +1853,10 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>2.386628669023996</v>
+        <v>2.169662426385451</v>
       </c>
       <c r="C12" t="n">
-        <v>25.16808414607123</v>
+        <v>24.5171854181556</v>
       </c>
       <c r="D12" t="n">
         <v>27.12078032981814</v>
@@ -1867,13 +1867,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>1.300815708127024</v>
+        <v>1.560978849752429</v>
       </c>
       <c r="C13" t="n">
         <v>22.63419332141022</v>
       </c>
       <c r="D13" t="n">
-        <v>26.01631416254048</v>
+        <v>25.49598787928967</v>
       </c>
     </row>
     <row r="14">
@@ -1884,10 +1884,10 @@
         <v>0.921861094287755</v>
       </c>
       <c r="C14" t="n">
-        <v>20.28094407433061</v>
+        <v>20.58823110575986</v>
       </c>
       <c r="D14" t="n">
-        <v>23.66110142005238</v>
+        <v>24.89024954576939</v>
       </c>
     </row>
     <row r="15">
@@ -1898,10 +1898,10 @@
         <v>0.7166758241001715</v>
       </c>
       <c r="C15" t="n">
-        <v>18.27523351455437</v>
+        <v>17.5585576904542</v>
       </c>
       <c r="D15" t="n">
-        <v>22.93362637120549</v>
+        <v>22.21695054710532</v>
       </c>
     </row>
     <row r="16">
@@ -1912,10 +1912,10 @@
         <v>0.4133157834879072</v>
       </c>
       <c r="C16" t="n">
-        <v>16.94594712300419</v>
+        <v>16.53263133951629</v>
       </c>
       <c r="D16" t="n">
-        <v>20.66578917439536</v>
+        <v>20.25247339090745</v>
       </c>
     </row>
     <row r="17">
@@ -1954,7 +1954,7 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>16.24890625298896</v>
+        <v>16.85071759569225</v>
       </c>
       <c r="D19" t="n">
         <v>9.027170140549421</v>
@@ -1968,7 +1968,7 @@
         <v>5.37997741927252</v>
       </c>
       <c r="C20" t="n">
-        <v>73.30219233758808</v>
+        <v>74.64718669240621</v>
       </c>
       <c r="D20" t="n">
         <v>6.724971774090649</v>
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.66919208139783</v>
+        <v>3.395865308989717</v>
       </c>
       <c r="C2" t="n">
-        <v>5.977861771158828</v>
+        <v>3.492076584005904</v>
       </c>
       <c r="D2" t="n">
-        <v>11.36569317206532</v>
+        <v>13.28500993386784</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>25.69724615866026</v>
+        <v>20.38108234016379</v>
       </c>
       <c r="C3" t="n">
-        <v>62.05136364691965</v>
+        <v>47.82583941238337</v>
       </c>
       <c r="D3" t="n">
-        <v>61.639029611136</v>
+        <v>72.26153977108648</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>30.93683365622549</v>
+        <v>28.57573042751191</v>
       </c>
       <c r="C4" t="n">
-        <v>136.1782240560751</v>
+        <v>137.3523943103543</v>
       </c>
       <c r="D4" t="n">
-        <v>102.1911002827547</v>
+        <v>119.0123654473196</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>33.52668410002858</v>
+        <v>29.28062527916113</v>
       </c>
       <c r="C5" t="n">
-        <v>117.4170254279185</v>
+        <v>151.9990883100124</v>
       </c>
       <c r="D5" t="n">
-        <v>75.15278676009335</v>
+        <v>86.76195336281188</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>34.3346624606237</v>
+        <v>28.49817235887642</v>
       </c>
       <c r="C6" t="n">
-        <v>125.3034047361332</v>
+        <v>146.2745174465493</v>
       </c>
       <c r="D6" t="n">
-        <v>38.68184129502858</v>
+        <v>41.25794727097221</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>18.50496247734813</v>
+        <v>15.4507453694363</v>
       </c>
       <c r="C7" t="n">
-        <v>137.6793162958684</v>
+        <v>143.6080906818149</v>
       </c>
       <c r="D7" t="n">
-        <v>31.26081039862693</v>
+        <v>31.56024344842221</v>
       </c>
     </row>
     <row r="8">
@@ -2108,13 +2108,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>9.095892479846697</v>
+        <v>7.927612711792993</v>
       </c>
       <c r="C8" t="n">
-        <v>106.814150222053</v>
+        <v>102.3913768144211</v>
       </c>
       <c r="D8" t="n">
-        <v>28.37250865273282</v>
+        <v>27.87181732356695</v>
       </c>
     </row>
     <row r="9">
@@ -2122,13 +2122,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>4.659374604355361</v>
+        <v>4.437499623195581</v>
       </c>
       <c r="C9" t="n">
-        <v>56.68905768632355</v>
+        <v>50.25468323268996</v>
       </c>
       <c r="D9" t="n">
-        <v>28.39999758845172</v>
+        <v>28.28906009787183</v>
       </c>
     </row>
     <row r="10">
@@ -2139,10 +2139,10 @@
         <v>2.135301256736813</v>
       </c>
       <c r="C10" t="n">
-        <v>34.73423377625215</v>
+        <v>32.45657910239955</v>
       </c>
       <c r="D10" t="n">
-        <v>30.03657101143117</v>
+        <v>29.89421759431538</v>
       </c>
     </row>
     <row r="11">
@@ -2150,10 +2150,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>1.776963344686726</v>
+        <v>1.599267010218054</v>
       </c>
       <c r="C11" t="n">
-        <v>30.03068052520567</v>
+        <v>29.14219885286231</v>
       </c>
       <c r="D11" t="n">
         <v>29.67528785626833</v>
@@ -2164,13 +2164,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>0.8678649705541803</v>
+        <v>1.084831213192725</v>
       </c>
       <c r="C12" t="n">
-        <v>20.82875929330033</v>
+        <v>20.61179305066178</v>
       </c>
       <c r="D12" t="n">
-        <v>28.63954402828795</v>
+        <v>28.42257778564941</v>
       </c>
     </row>
     <row r="13">
@@ -2181,10 +2181,10 @@
         <v>0.5203262832508095</v>
       </c>
       <c r="C13" t="n">
-        <v>16.65044106402591</v>
+        <v>16.91060420565131</v>
       </c>
       <c r="D13" t="n">
-        <v>25.23582473766426</v>
+        <v>26.01631416254048</v>
       </c>
     </row>
     <row r="14">
@@ -2195,10 +2195,10 @@
         <v>0.3072870314292517</v>
       </c>
       <c r="C14" t="n">
-        <v>15.05706454003333</v>
+        <v>14.74977750860408</v>
       </c>
       <c r="D14" t="n">
-        <v>19.0517959486136</v>
+        <v>18.4372218857551</v>
       </c>
     </row>
     <row r="15">
@@ -2209,10 +2209,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>14.33351648200343</v>
+        <v>13.97517856995334</v>
       </c>
       <c r="D15" t="n">
-        <v>17.5585576904542</v>
+        <v>17.20021977840412</v>
       </c>
     </row>
     <row r="16">
@@ -2251,7 +2251,7 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>13.9113649691773</v>
+        <v>14.44641746799181</v>
       </c>
       <c r="D18" t="n">
         <v>7.490734983403163</v>
@@ -2265,7 +2265,7 @@
         <v>4.212679398923063</v>
       </c>
       <c r="C19" t="n">
-        <v>63.79200232654924</v>
+        <v>64.99562501195582</v>
       </c>
       <c r="D19" t="n">
         <v>5.416302084329653</v>
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.949571014184918</v>
+        <v>4.263730279543897</v>
       </c>
       <c r="C2" t="n">
-        <v>8.540223279243003</v>
+        <v>10.30344215607028</v>
       </c>
       <c r="D2" t="n">
-        <v>10.29755166984479</v>
+        <v>17.60764507566654</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>20.9455872701057</v>
+        <v>15.94849145548944</v>
       </c>
       <c r="C3" t="n">
-        <v>41.62119392154352</v>
+        <v>30.07584091960103</v>
       </c>
       <c r="D3" t="n">
-        <v>57.29479601984386</v>
+        <v>66.61158173314608</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>39.41127983928396</v>
+        <v>33.60424216866407</v>
       </c>
       <c r="C4" t="n">
-        <v>145.660925131395</v>
+        <v>128.2525748396906</v>
       </c>
       <c r="D4" t="n">
-        <v>108.5596976402038</v>
+        <v>126.6317093799791</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>39.58897617375263</v>
+        <v>35.36746104549135</v>
       </c>
       <c r="C5" t="n">
-        <v>182.924140993787</v>
+        <v>200.4974248998049</v>
       </c>
       <c r="D5" t="n">
-        <v>91.49888603580274</v>
+        <v>105.9305772882309</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>39.52712606838509</v>
+        <v>33.40887437551896</v>
       </c>
       <c r="C6" t="n">
-        <v>155.612901609345</v>
+        <v>191.758888584304</v>
       </c>
       <c r="D6" t="n">
-        <v>50.31456984264904</v>
+        <v>55.2252718592916</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>27.66761380108361</v>
+        <v>22.75691178444107</v>
       </c>
       <c r="C7" t="n">
-        <v>159.9571352006371</v>
+        <v>176.126519889582</v>
       </c>
       <c r="D7" t="n">
-        <v>34.49468733641593</v>
+        <v>35.27321326588365</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>13.18487166803466</v>
+        <v>11.09865779651019</v>
       </c>
       <c r="C8" t="n">
-        <v>141.9459918185251</v>
+        <v>141.6121975990812</v>
       </c>
       <c r="D8" t="n">
-        <v>29.95803119509142</v>
+        <v>29.6242369756475</v>
       </c>
     </row>
     <row r="9">
@@ -2433,13 +2433,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>6.212499472473814</v>
+        <v>5.657812019574366</v>
       </c>
       <c r="C9" t="n">
-        <v>88.97186744507141</v>
+        <v>81.7609305573786</v>
       </c>
       <c r="D9" t="n">
-        <v>29.17656002251095</v>
+        <v>29.28749751309084</v>
       </c>
     </row>
     <row r="10">
@@ -2450,10 +2450,10 @@
         <v>2.704714925199962</v>
       </c>
       <c r="C10" t="n">
-        <v>48.40016181936776</v>
+        <v>43.70249905454677</v>
       </c>
       <c r="D10" t="n">
-        <v>30.60598467989432</v>
+        <v>30.17892442854695</v>
       </c>
     </row>
     <row r="11">
@@ -2461,10 +2461,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>1.776963344686726</v>
+        <v>1.599267010218054</v>
       </c>
       <c r="C11" t="n">
-        <v>34.65078522139116</v>
+        <v>32.87382187670443</v>
       </c>
       <c r="D11" t="n">
         <v>30.20837685967435</v>
@@ -2475,13 +2475,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>0.8678649705541803</v>
+        <v>1.084831213192725</v>
       </c>
       <c r="C12" t="n">
-        <v>25.60201663134832</v>
+        <v>24.95111790343269</v>
       </c>
       <c r="D12" t="n">
-        <v>29.07347651356504</v>
+        <v>28.8565102709265</v>
       </c>
     </row>
     <row r="13">
@@ -2492,10 +2492,10 @@
         <v>0.2601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>18.73174619702914</v>
+        <v>18.99190933865455</v>
       </c>
       <c r="D13" t="n">
-        <v>26.01631416254048</v>
+        <v>26.79680358741669</v>
       </c>
     </row>
     <row r="14">
@@ -2506,10 +2506,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>16.28621266575034</v>
+        <v>15.97892563432109</v>
       </c>
       <c r="D14" t="n">
-        <v>19.35908298004286</v>
+        <v>19.0517959486136</v>
       </c>
     </row>
     <row r="15">
@@ -2520,7 +2520,7 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>15.76686813020377</v>
+        <v>15.40853021815369</v>
       </c>
       <c r="D15" t="n">
         <v>17.20021977840412</v>
@@ -2534,7 +2534,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>14.87936820556466</v>
+        <v>14.46605242207675</v>
       </c>
       <c r="D16" t="n">
         <v>14.87936820556466</v>
@@ -2562,7 +2562,7 @@
         <v>3.21031499288707</v>
       </c>
       <c r="C18" t="n">
-        <v>33.70830742531424</v>
+        <v>35.31346492175777</v>
       </c>
       <c r="D18" t="n">
         <v>6.955682484588652</v>
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.34834050855837</v>
+        <v>2.528000338435537</v>
       </c>
       <c r="C2" t="n">
-        <v>3.996694903988765</v>
+        <v>4.890085314853362</v>
       </c>
       <c r="D2" t="n">
-        <v>7.188356690495145</v>
+        <v>12.30326222962103</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>20.10619298297468</v>
+        <v>16.59644494029233</v>
       </c>
       <c r="C3" t="n">
-        <v>40.71798603363646</v>
+        <v>36.24121650227101</v>
       </c>
       <c r="D3" t="n">
-        <v>55.40493168916875</v>
+        <v>67.34298377280996</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>43.40601124786423</v>
+        <v>36.782159487311</v>
       </c>
       <c r="C4" t="n">
-        <v>144.3846531158742</v>
+        <v>122.037130124104</v>
       </c>
       <c r="D4" t="n">
-        <v>114.4177861914445</v>
+        <v>133.4087137823948</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>41.72427743048944</v>
+        <v>36.54555829058752</v>
       </c>
       <c r="C5" t="n">
-        <v>231.5451960466103</v>
+        <v>242.5162266415684</v>
       </c>
       <c r="D5" t="n">
-        <v>96.26036240139979</v>
+        <v>111.3056459689821</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>33.24786775202249</v>
+        <v>27.37112599440108</v>
       </c>
       <c r="C6" t="n">
-        <v>192.4834183900382</v>
+        <v>225.6507828303124</v>
       </c>
       <c r="D6" t="n">
-        <v>49.54978838104078</v>
+        <v>53.93721887131977</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>8.683558444063037</v>
+        <v>7.306166415004762</v>
       </c>
       <c r="C7" t="n">
-        <v>173.8508287111379</v>
+        <v>185.3490578232766</v>
       </c>
       <c r="D7" t="n">
-        <v>34.61446055633404</v>
+        <v>35.03366682604743</v>
       </c>
     </row>
     <row r="8">
@@ -2730,13 +2730,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>4.255876297909922</v>
+        <v>3.922082078466008</v>
       </c>
       <c r="C8" t="n">
-        <v>108.6500184289945</v>
+        <v>101.8906854852552</v>
       </c>
       <c r="D8" t="n">
-        <v>31.46010518258904</v>
+        <v>31.29320807286708</v>
       </c>
     </row>
     <row r="9">
@@ -2747,10 +2747,10 @@
         <v>1.885937339858122</v>
       </c>
       <c r="C9" t="n">
-        <v>36.94218436310322</v>
+        <v>33.28124717396686</v>
       </c>
       <c r="D9" t="n">
-        <v>31.94999728700819</v>
+        <v>31.61718481526852</v>
       </c>
     </row>
     <row r="10">
@@ -2758,10 +2758,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.281180754042088</v>
+        <v>1.1388273369263</v>
       </c>
       <c r="C10" t="n">
-        <v>27.18950266911542</v>
+        <v>25.76596849795754</v>
       </c>
       <c r="D10" t="n">
         <v>23.63066724122073</v>
@@ -2772,13 +2772,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>0.5330890034060179</v>
+        <v>0.7107853378746906</v>
       </c>
       <c r="C11" t="n">
-        <v>20.43507846389736</v>
+        <v>19.90198946049134</v>
       </c>
       <c r="D11" t="n">
-        <v>23.27821981539612</v>
+        <v>23.10052348092744</v>
       </c>
     </row>
     <row r="12">
@@ -2789,10 +2789,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>15.18763698469816</v>
+        <v>15.4046032273367</v>
       </c>
       <c r="D12" t="n">
-        <v>21.26269177857742</v>
+        <v>21.69662426385451</v>
       </c>
     </row>
     <row r="13">
@@ -2803,10 +2803,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>13.26832022289564</v>
+        <v>13.00815708127024</v>
       </c>
       <c r="D13" t="n">
-        <v>15.86995163914969</v>
+        <v>15.60978849752428</v>
       </c>
     </row>
     <row r="14">
@@ -2817,7 +2817,7 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>13.21334235145782</v>
+        <v>12.90605532002857</v>
       </c>
       <c r="D14" t="n">
         <v>14.44249047717483</v>
@@ -2831,7 +2831,7 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>12.541826921753</v>
+        <v>12.18348900970292</v>
       </c>
       <c r="D15" t="n">
         <v>12.541826921753</v>
@@ -2859,7 +2859,7 @@
         <v>2.361103228713579</v>
       </c>
       <c r="C17" t="n">
-        <v>28.80545939030567</v>
+        <v>30.22212132753381</v>
       </c>
       <c r="D17" t="n">
         <v>5.66664774891259</v>
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.610467145592269</v>
+        <v>3.291800052339555</v>
       </c>
       <c r="C2" t="n">
-        <v>6.465790380169493</v>
+        <v>9.229410167624264</v>
       </c>
       <c r="D2" t="n">
-        <v>12.13636511989907</v>
+        <v>14.01346673041897</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>14.29915531235479</v>
+        <v>12.80689880189964</v>
       </c>
       <c r="C3" t="n">
-        <v>27.92581344730052</v>
+        <v>27.67546778271759</v>
       </c>
       <c r="D3" t="n">
-        <v>49.56353284890022</v>
+        <v>62.17899084847173</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>41.40226418349649</v>
+        <v>34.33171721751096</v>
       </c>
       <c r="C4" t="n">
-        <v>124.6407250357666</v>
+        <v>107.8449853115121</v>
       </c>
       <c r="D4" t="n">
-        <v>115.489854684482</v>
+        <v>135.744291570798</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>51.49266708774522</v>
+        <v>44.37499623195583</v>
       </c>
       <c r="C5" t="n">
-        <v>249.3148294934775</v>
+        <v>234.0731963850458</v>
       </c>
       <c r="D5" t="n">
-        <v>111.133840120739</v>
+        <v>128.8298424897877</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>42.02272873258048</v>
+        <v>35.86422538384024</v>
       </c>
       <c r="C6" t="n">
-        <v>269.9276042918436</v>
+        <v>299.0698031447059</v>
       </c>
       <c r="D6" t="n">
-        <v>63.4366096576119</v>
+        <v>71.04417261782045</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>18.62473569726624</v>
+        <v>15.15131231964102</v>
       </c>
       <c r="C7" t="n">
-        <v>219.5443121098972</v>
+        <v>244.5170284628233</v>
       </c>
       <c r="D7" t="n">
-        <v>39.52516257297658</v>
+        <v>39.94436884268997</v>
       </c>
     </row>
     <row r="8">
@@ -3041,13 +3041,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>5.674501730546564</v>
+        <v>4.923464736797754</v>
       </c>
       <c r="C8" t="n">
-        <v>160.2212253330794</v>
+        <v>158.9694970101648</v>
       </c>
       <c r="D8" t="n">
-        <v>33.21252483466959</v>
+        <v>33.12907627980861</v>
       </c>
     </row>
     <row r="9">
@@ -3055,13 +3055,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>2.32968730217768</v>
+        <v>2.218749811597791</v>
       </c>
       <c r="C9" t="n">
-        <v>71.33280644286897</v>
+        <v>66.22968187619405</v>
       </c>
       <c r="D9" t="n">
-        <v>32.72655972106742</v>
+        <v>32.39374724932775</v>
       </c>
     </row>
     <row r="10">
@@ -3069,10 +3069,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.281180754042088</v>
+        <v>1.1388273369263</v>
       </c>
       <c r="C10" t="n">
-        <v>33.73775985644164</v>
+        <v>31.17539834835747</v>
       </c>
       <c r="D10" t="n">
         <v>24.91184799526281</v>
@@ -3083,13 +3083,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>0.3553926689373453</v>
+        <v>0.5330890034060179</v>
       </c>
       <c r="C11" t="n">
-        <v>24.16670148773948</v>
+        <v>23.27821981539612</v>
       </c>
       <c r="D11" t="n">
-        <v>23.98900515327081</v>
+        <v>23.81130881880213</v>
       </c>
     </row>
     <row r="12">
@@ -3103,7 +3103,7 @@
         <v>17.57426565372215</v>
       </c>
       <c r="D12" t="n">
-        <v>21.47965802121596</v>
+        <v>21.91359050649305</v>
       </c>
     </row>
     <row r="13">
@@ -3114,10 +3114,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>15.34962535589888</v>
+        <v>15.08946221427348</v>
       </c>
       <c r="D13" t="n">
-        <v>15.86995163914969</v>
+        <v>15.60978849752428</v>
       </c>
     </row>
     <row r="14">
@@ -3128,10 +3128,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
+        <v>13.52062938288707</v>
+      </c>
+      <c r="D14" t="n">
         <v>14.13520344574558</v>
-      </c>
-      <c r="D14" t="n">
-        <v>14.44249047717483</v>
       </c>
     </row>
     <row r="15">
@@ -3142,7 +3142,7 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>13.61684065790326</v>
+        <v>13.25850274585317</v>
       </c>
       <c r="D15" t="n">
         <v>11.82515109765283</v>
@@ -3156,7 +3156,7 @@
         <v>1.653263133951629</v>
       </c>
       <c r="C16" t="n">
-        <v>23.1456838753228</v>
+        <v>23.97231544229862</v>
       </c>
       <c r="D16" t="n">
         <v>8.266315669758143</v>
@@ -3170,7 +3170,7 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>33.99988649347554</v>
+        <v>34.47210713921825</v>
       </c>
       <c r="D17" t="n">
         <v>4.249985811684442</v>
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>1.839795197758523</v>
+        <v>2.219731559302038</v>
       </c>
       <c r="C2" t="n">
-        <v>3.543127464626739</v>
+        <v>6.31558298141973</v>
       </c>
       <c r="D2" t="n">
-        <v>8.976119259928588</v>
+        <v>10.71773968726243</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>12.19821522526662</v>
+        <v>12.22275891787279</v>
       </c>
       <c r="C3" t="n">
-        <v>27.19441140763665</v>
+        <v>31.54846247597125</v>
       </c>
       <c r="D3" t="n">
-        <v>48.67505117655686</v>
+        <v>59.77861771158828</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>36.69282044622454</v>
+        <v>31.33247798103695</v>
       </c>
       <c r="C4" t="n">
-        <v>103.9523556641735</v>
+        <v>94.57175635009524</v>
       </c>
       <c r="D4" t="n">
-        <v>114.7496169154799</v>
+        <v>136.1526986157647</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>56.76956099807182</v>
+        <v>48.30198704894308</v>
       </c>
       <c r="C5" t="n">
-        <v>250.2720335051182</v>
+        <v>228.9681083229624</v>
       </c>
       <c r="D5" t="n">
-        <v>120.5340743889022</v>
+        <v>141.3471257189345</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>49.22777513404782</v>
+        <v>41.37870223859457</v>
       </c>
       <c r="C6" t="n">
-        <v>322.6975251428138</v>
+        <v>336.222081516518</v>
       </c>
       <c r="D6" t="n">
-        <v>74.78757661411353</v>
+        <v>82.35488791844796</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>16.64847756861741</v>
+        <v>13.59426046070558</v>
       </c>
       <c r="C7" t="n">
-        <v>277.3348907203857</v>
+        <v>306.3200099405685</v>
       </c>
       <c r="D7" t="n">
-        <v>43.6573386601514</v>
+        <v>44.6155244194963</v>
       </c>
     </row>
     <row r="8">
@@ -3352,13 +3352,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>4.589670517353839</v>
+        <v>4.005530633326986</v>
       </c>
       <c r="C8" t="n">
-        <v>198.2737663496858</v>
+        <v>200.7772229955152</v>
       </c>
       <c r="D8" t="n">
-        <v>34.21390749300134</v>
+        <v>34.38080460272329</v>
       </c>
     </row>
     <row r="9">
@@ -3366,13 +3366,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.774999849278233</v>
+        <v>1.664062358698343</v>
       </c>
       <c r="C9" t="n">
-        <v>80.31874317984003</v>
+        <v>72.66405632982764</v>
       </c>
       <c r="D9" t="n">
-        <v>32.50468473990763</v>
+        <v>31.94999728700819</v>
       </c>
     </row>
     <row r="10">
@@ -3380,13 +3380,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0.4270602513473625</v>
+        <v>0.5694136684631501</v>
       </c>
       <c r="C10" t="n">
-        <v>34.30717352490479</v>
+        <v>31.8871654339364</v>
       </c>
       <c r="D10" t="n">
-        <v>25.33890824661018</v>
+        <v>25.62361508084176</v>
       </c>
     </row>
     <row r="11">
@@ -3397,7 +3397,7 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>23.45591614986479</v>
+        <v>22.7451308119901</v>
       </c>
       <c r="D11" t="n">
         <v>24.16670148773948</v>
@@ -3411,7 +3411,7 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>16.92336692580652</v>
+        <v>16.48943444052943</v>
       </c>
       <c r="D12" t="n">
         <v>19.96089432274615</v>
@@ -3425,10 +3425,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>11.70734137314322</v>
+        <v>11.18701508989241</v>
       </c>
       <c r="D13" t="n">
-        <v>16.3902779224005</v>
+        <v>16.1301147807751</v>
       </c>
     </row>
     <row r="14">
@@ -3439,7 +3439,7 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>11.36962016288231</v>
+        <v>11.06233313145306</v>
       </c>
       <c r="D14" t="n">
         <v>11.06233313145306</v>
@@ -3453,7 +3453,7 @@
         <v>1.075013736150257</v>
       </c>
       <c r="C15" t="n">
-        <v>19.35024725070463</v>
+        <v>20.0669230748048</v>
       </c>
       <c r="D15" t="n">
         <v>6.808420328951629</v>
@@ -3467,7 +3467,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>28.9321048441535</v>
+        <v>29.34542062764141</v>
       </c>
       <c r="D16" t="n">
         <v>3.306526267903257</v>
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.864739800992193</v>
+        <v>2.353249247079604</v>
       </c>
       <c r="C2" t="n">
-        <v>12.35234961483337</v>
+        <v>9.94510424402019</v>
       </c>
       <c r="D2" t="n">
-        <v>11.16836188351171</v>
+        <v>17.57622914913065</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>9.400234268163208</v>
+        <v>9.979465413668827</v>
       </c>
       <c r="C3" t="n">
-        <v>21.11248437982766</v>
+        <v>28.4265047764664</v>
       </c>
       <c r="D3" t="n">
-        <v>45.10148953309847</v>
+        <v>55.78290455530377</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>30.40079940970673</v>
+        <v>27.35050929261189</v>
       </c>
       <c r="C4" t="n">
-        <v>88.06276907093888</v>
+        <v>87.53949754457535</v>
       </c>
       <c r="D4" t="n">
-        <v>112.9500733735955</v>
+        <v>133.2938493009979</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>56.54866776461629</v>
+        <v>47.66385104118265</v>
       </c>
       <c r="C5" t="n">
-        <v>225.2374670468245</v>
+        <v>206.1179305066179</v>
       </c>
       <c r="D5" t="n">
-        <v>130.3270077387641</v>
+        <v>153.226272940321</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>59.00892751145879</v>
+        <v>49.83154997215961</v>
       </c>
       <c r="C6" t="n">
-        <v>352.8862670484033</v>
+        <v>347.8548100641384</v>
       </c>
       <c r="D6" t="n">
-        <v>89.1574177611741</v>
+        <v>99.94486153543805</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>29.94330497952771</v>
+        <v>24.852943133008</v>
       </c>
       <c r="C7" t="n">
-        <v>350.6959879202286</v>
+        <v>374.5907452938917</v>
       </c>
       <c r="D7" t="n">
-        <v>51.14316490503334</v>
+        <v>53.29908286355933</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>8.428304040958867</v>
+        <v>7.093127163183205</v>
       </c>
       <c r="C8" t="n">
-        <v>264.615367464164</v>
+        <v>275.9643709252571</v>
       </c>
       <c r="D8" t="n">
-        <v>36.71736413883071</v>
+        <v>36.96770980341364</v>
       </c>
     </row>
     <row r="9">
@@ -3677,13 +3677,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>2.440624792757569</v>
+        <v>2.218749811597791</v>
       </c>
       <c r="C9" t="n">
-        <v>137.6734258096429</v>
+        <v>134.2343636016663</v>
       </c>
       <c r="D9" t="n">
-        <v>33.39218466454675</v>
+        <v>32.9484347022272</v>
       </c>
     </row>
     <row r="10">
@@ -3691,13 +3691,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0.5694136684631501</v>
+        <v>0.7117670855789376</v>
       </c>
       <c r="C10" t="n">
-        <v>55.09077242380977</v>
+        <v>49.53898915629405</v>
       </c>
       <c r="D10" t="n">
-        <v>26.47773558353648</v>
+        <v>26.90479583488384</v>
       </c>
     </row>
     <row r="11">
@@ -3708,10 +3708,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>28.60910984945629</v>
+        <v>27.36523550817559</v>
       </c>
       <c r="D11" t="n">
-        <v>24.6997904911455</v>
+        <v>24.34439782220815</v>
       </c>
     </row>
     <row r="12">
@@ -3722,7 +3722,7 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>19.7439280801076</v>
+        <v>19.09302935219197</v>
       </c>
       <c r="D12" t="n">
         <v>20.39482680802324</v>
@@ -3736,10 +3736,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>13.52848336452105</v>
+        <v>12.74799393964483</v>
       </c>
       <c r="D13" t="n">
-        <v>16.65044106402591</v>
+        <v>16.3902779224005</v>
       </c>
     </row>
     <row r="14">
@@ -3750,7 +3750,7 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>11.98419422574081</v>
+        <v>11.67690719431156</v>
       </c>
       <c r="D14" t="n">
         <v>11.06233313145306</v>
@@ -3764,7 +3764,7 @@
         <v>0.7166758241001715</v>
       </c>
       <c r="C15" t="n">
-        <v>20.42526098685489</v>
+        <v>21.14193681095506</v>
       </c>
       <c r="D15" t="n">
         <v>6.450082416901544</v>
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.737914420695106</v>
+        <v>4.625013434706723</v>
       </c>
       <c r="C2" t="n">
-        <v>10.28871594050657</v>
+        <v>8.541205026947251</v>
       </c>
       <c r="D2" t="n">
-        <v>10.75799134313655</v>
+        <v>15.27108553955914</v>
       </c>
     </row>
     <row r="3">
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.072469403665017</v>
+        <v>1.720021977840412</v>
       </c>
       <c r="C2" t="n">
-        <v>7.212900383101315</v>
+        <v>5.886559234663874</v>
       </c>
       <c r="D2" t="n">
-        <v>8.308530821040756</v>
+        <v>13.07589767286327</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>13.03760951239764</v>
+        <v>12.84125997154828</v>
       </c>
       <c r="C3" t="n">
-        <v>31.78408192499048</v>
+        <v>35.76997760423254</v>
       </c>
       <c r="D3" t="n">
-        <v>49.34263961544469</v>
+        <v>62.40970155896974</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>42.42328179591317</v>
+        <v>36.88426124855267</v>
       </c>
       <c r="C4" t="n">
-        <v>127.4995743505333</v>
+        <v>123.8494363861436</v>
       </c>
       <c r="D4" t="n">
-        <v>117.0979574240383</v>
+        <v>136.8418855041459</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>34.28753857081986</v>
+        <v>28.49522711576368</v>
       </c>
       <c r="C5" t="n">
-        <v>313.4965856586128</v>
+        <v>301.0283898146783</v>
       </c>
       <c r="D5" t="n">
-        <v>121.0004045484194</v>
+        <v>140.7580770963865</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>18.59626501384309</v>
+        <v>15.41638419978766</v>
       </c>
       <c r="C6" t="n">
-        <v>296.6949554481329</v>
+        <v>308.0861740605086</v>
       </c>
       <c r="D6" t="n">
-        <v>72.09071567054754</v>
+        <v>78.85299385739957</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>5.569454726192155</v>
+        <v>4.671155576806323</v>
       </c>
       <c r="C7" t="n">
-        <v>186.0676971427852</v>
+        <v>194.0326162673396</v>
       </c>
       <c r="D7" t="n">
-        <v>32.27888276793088</v>
+        <v>32.21899615797182</v>
       </c>
     </row>
     <row r="8">
@@ -4285,13 +4285,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>1.668971097219577</v>
+        <v>1.50207398749762</v>
       </c>
       <c r="C8" t="n">
-        <v>101.4734427109503</v>
+        <v>98.88653751025997</v>
       </c>
       <c r="D8" t="n">
-        <v>24.53387512912779</v>
+        <v>24.28352946454485</v>
       </c>
     </row>
     <row r="9">
@@ -4299,13 +4299,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>0.3328124717396686</v>
+        <v>0.4437499623195582</v>
       </c>
       <c r="C9" t="n">
-        <v>42.04530892977813</v>
+        <v>37.82968428774233</v>
       </c>
       <c r="D9" t="n">
-        <v>20.1906232855399</v>
+        <v>20.52343575727956</v>
       </c>
     </row>
     <row r="10">
@@ -4316,10 +4316,10 @@
         <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>22.34948648717864</v>
+        <v>21.35301256736813</v>
       </c>
       <c r="D10" t="n">
-        <v>19.3600647277471</v>
+        <v>19.07535789351553</v>
       </c>
     </row>
     <row r="11">
@@ -4330,7 +4330,7 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>15.81497376771187</v>
+        <v>15.28188476430585</v>
       </c>
       <c r="D11" t="n">
         <v>16.34806277111788</v>
@@ -4344,10 +4344,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>10.84831213192725</v>
+        <v>10.41437964665016</v>
       </c>
       <c r="D12" t="n">
-        <v>13.4519070435898</v>
+        <v>13.23494080095125</v>
       </c>
     </row>
     <row r="13">
@@ -4358,7 +4358,7 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>9.886199381765381</v>
+        <v>9.626036240139976</v>
       </c>
       <c r="D13" t="n">
         <v>9.105709956889166</v>
@@ -4372,7 +4372,7 @@
         <v>0.3072870314292517</v>
       </c>
       <c r="C14" t="n">
-        <v>16.90078672860884</v>
+        <v>17.51536079146734</v>
       </c>
       <c r="D14" t="n">
         <v>5.223879534297279</v>
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.788785374866693</v>
+        <v>5.884595739255381</v>
       </c>
       <c r="C2" t="n">
-        <v>6.034803138005143</v>
+        <v>7.638978886744431</v>
       </c>
       <c r="D2" t="n">
-        <v>17.1452419069663</v>
+        <v>15.79828405673967</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>10.06782270705104</v>
+        <v>9.832203258031806</v>
       </c>
       <c r="C3" t="n">
-        <v>25.92304813063703</v>
+        <v>21.51990967709008</v>
       </c>
       <c r="D3" t="n">
-        <v>12.17367153266045</v>
+        <v>15.96321767105314</v>
       </c>
     </row>
     <row r="4">
@@ -4557,7 +4557,7 @@
         <v>4.736932672990861</v>
       </c>
       <c r="C5" t="n">
-        <v>9.35114688295087</v>
+        <v>9.449321653375552</v>
       </c>
       <c r="D5" t="n">
         <v>28.49522711576368</v>
@@ -4571,7 +4571,7 @@
         <v>8.050331174823848</v>
       </c>
       <c r="C6" t="n">
-        <v>18.47551004622073</v>
+        <v>18.27425176685013</v>
       </c>
       <c r="D6" t="n">
         <v>32.8453511932813</v>
@@ -4778,13 +4778,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>13.39757564524758</v>
+        <v>13.39712103272468</v>
       </c>
       <c r="C21" t="n">
-        <v>70.14024896629617</v>
+        <v>70.13786893602918</v>
       </c>
       <c r="D21" t="n">
-        <v>1.576185370029127</v>
+        <v>1.576131886202903</v>
       </c>
     </row>
   </sheetData>
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.176755644493432</v>
+        <v>3.888702656521616</v>
       </c>
       <c r="C2" t="n">
-        <v>5.491896657556658</v>
+        <v>6.696501090667494</v>
       </c>
       <c r="D2" t="n">
-        <v>17.77061519457152</v>
+        <v>24.78618428911922</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>18.04943154257761</v>
+        <v>16.10557108816893</v>
       </c>
       <c r="C3" t="n">
-        <v>24.42588288166064</v>
+        <v>26.69372007847078</v>
       </c>
       <c r="D3" t="n">
-        <v>23.63066724122073</v>
+        <v>25.37326941625881</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>11.80551614356789</v>
+        <v>11.53749902030852</v>
       </c>
       <c r="C4" t="n">
-        <v>40.04941584704438</v>
+        <v>33.3489877655599</v>
       </c>
       <c r="D4" t="n">
-        <v>21.45413258090555</v>
+        <v>23.43235420496287</v>
       </c>
     </row>
     <row r="5">
@@ -4868,7 +4868,7 @@
         <v>3.067961575771283</v>
       </c>
       <c r="C5" t="n">
-        <v>5.375068680751288</v>
+        <v>5.424156065963628</v>
       </c>
       <c r="D5" t="n">
         <v>29.40334374219198</v>
@@ -4896,7 +4896,7 @@
         <v>9.462084373530759</v>
       </c>
       <c r="C7" t="n">
-        <v>24.49362347325367</v>
+        <v>24.3139636433765</v>
       </c>
       <c r="D7" t="n">
         <v>34.97378021608837</v>
@@ -5005,7 +5005,7 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4.658392856651115</v>
+        <v>5.0167307687012</v>
       </c>
       <c r="C15" t="n">
         <v>26.51700549170635</v>
@@ -5025,7 +5025,7 @@
         <v>29.34542062764141</v>
       </c>
       <c r="D16" t="n">
-        <v>40.91826256530281</v>
+        <v>40.5049467818149</v>
       </c>
     </row>
     <row r="17">
@@ -5039,7 +5039,7 @@
         <v>31.63878326476196</v>
       </c>
       <c r="D17" t="n">
-        <v>36.36098972218912</v>
+        <v>36.83321036793183</v>
       </c>
     </row>
     <row r="18">
@@ -5089,13 +5089,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>15.43889398748856</v>
+        <v>15.43867705097228</v>
       </c>
       <c r="C21" t="n">
-        <v>86.13277698283092</v>
+        <v>86.13156670542429</v>
       </c>
       <c r="D21" t="n">
-        <v>3.250293471050223</v>
+        <v>3.25024780020469</v>
       </c>
     </row>
   </sheetData>
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.476769531365456</v>
+        <v>3.771874679716245</v>
       </c>
       <c r="C2" t="n">
-        <v>6.925248305757</v>
+        <v>7.639960634448678</v>
       </c>
       <c r="D2" t="n">
-        <v>19.16666043001048</v>
+        <v>22.00194779987526</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>17.98561794180156</v>
+        <v>14.61822331623501</v>
       </c>
       <c r="C3" t="n">
-        <v>22.57037972063417</v>
+        <v>26.56609287691869</v>
       </c>
       <c r="D3" t="n">
-        <v>32.3633130704961</v>
+        <v>39.31408681656352</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>24.91282974296706</v>
+        <v>22.67935371580556</v>
       </c>
       <c r="C4" t="n">
-        <v>52.4930679983727</v>
+        <v>52.40372895728624</v>
       </c>
       <c r="D4" t="n">
-        <v>28.47362866627024</v>
+        <v>30.88578277560466</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>10.60287520586555</v>
+        <v>10.40652566501619</v>
       </c>
       <c r="C5" t="n">
-        <v>44.44862730977434</v>
+        <v>37.42913122440965</v>
       </c>
       <c r="D5" t="n">
-        <v>30.38509144643879</v>
+        <v>31.07231483941155</v>
       </c>
     </row>
     <row r="6">
@@ -5193,7 +5193,7 @@
         <v>5.957245069369646</v>
       </c>
       <c r="C6" t="n">
-        <v>12.23650338573225</v>
+        <v>12.27675504160637</v>
       </c>
       <c r="D6" t="n">
         <v>36.54850353370026</v>
@@ -5207,7 +5207,7 @@
         <v>9.462084373530759</v>
       </c>
       <c r="C7" t="n">
-        <v>24.25407703341745</v>
+        <v>24.13430381349934</v>
       </c>
       <c r="D7" t="n">
         <v>37.4890178343687</v>
@@ -5221,7 +5221,7 @@
         <v>10.43106935762236</v>
       </c>
       <c r="C8" t="n">
-        <v>29.87458264023044</v>
+        <v>29.79113408536946</v>
       </c>
       <c r="D8" t="n">
         <v>37.88564390688441</v>
@@ -5316,7 +5316,7 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4.30005494460103</v>
+        <v>4.658392856651115</v>
       </c>
       <c r="C15" t="n">
         <v>27.23368131580652</v>
@@ -5336,7 +5336,7 @@
         <v>29.75873641112932</v>
       </c>
       <c r="D16" t="n">
-        <v>41.33157834879071</v>
+        <v>40.91826256530281</v>
       </c>
     </row>
     <row r="17">
@@ -5350,7 +5350,7 @@
         <v>32.11100391050468</v>
       </c>
       <c r="D17" t="n">
-        <v>36.83321036793183</v>
+        <v>37.30543101367455</v>
       </c>
     </row>
     <row r="18">
@@ -5375,7 +5375,7 @@
         <v>6.018113427032947</v>
       </c>
       <c r="C19" t="n">
-        <v>36.71049190490098</v>
+        <v>37.31230324760427</v>
       </c>
       <c r="D19" t="n">
         <v>24.67426505083508</v>
@@ -5400,13 +5400,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>16.72992187095895</v>
+        <v>16.72884648477939</v>
       </c>
       <c r="C21" t="n">
-        <v>102.0525234128496</v>
+        <v>102.0459635571543</v>
       </c>
       <c r="D21" t="n">
-        <v>4.182480467739737</v>
+        <v>4.182211621194847</v>
       </c>
     </row>
   </sheetData>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.428083056780614</v>
+        <v>4.180281724682919</v>
       </c>
       <c r="C2" t="n">
-        <v>4.715334223497431</v>
+        <v>8.259443435828414</v>
       </c>
       <c r="D2" t="n">
-        <v>20.03354365286041</v>
+        <v>30.6413275972472</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>16.50808764691012</v>
+        <v>13.66101930459437</v>
       </c>
       <c r="C3" t="n">
-        <v>25.04438393533613</v>
+        <v>28.33323874456295</v>
       </c>
       <c r="D3" t="n">
-        <v>39.73132959086842</v>
+        <v>47.29078691356886</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>29.99239236474006</v>
+        <v>25.51267759026186</v>
       </c>
       <c r="C4" t="n">
-        <v>54.7265440255342</v>
+        <v>60.2655645728947</v>
       </c>
       <c r="D4" t="n">
-        <v>37.75212621910685</v>
+        <v>42.94655332227672</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>23.83192552059133</v>
+        <v>22.18749811597792</v>
       </c>
       <c r="C5" t="n">
-        <v>72.796592269901</v>
+        <v>69.48319376806802</v>
       </c>
       <c r="D5" t="n">
-        <v>33.37942194439156</v>
+        <v>34.70478134512475</v>
       </c>
     </row>
     <row r="6">
@@ -5501,13 +5501,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>10.22392059202629</v>
+        <v>9.94215900090745</v>
       </c>
       <c r="C6" t="n">
-        <v>42.2642386678252</v>
+        <v>36.50825187782615</v>
       </c>
       <c r="D6" t="n">
-        <v>38.31957639216151</v>
+        <v>38.52083467153211</v>
       </c>
     </row>
     <row r="7">
@@ -5518,7 +5518,7 @@
         <v>8.563785224144926</v>
       </c>
       <c r="C7" t="n">
-        <v>21.19985992550562</v>
+        <v>21.13997331554657</v>
       </c>
       <c r="D7" t="n">
         <v>39.52516257297658</v>
@@ -5532,7 +5532,7 @@
         <v>10.84831213192725</v>
       </c>
       <c r="C8" t="n">
-        <v>31.71045084717197</v>
+        <v>31.54355373745002</v>
       </c>
       <c r="D8" t="n">
         <v>39.8884092235479</v>
@@ -5647,7 +5647,7 @@
         <v>30.17205219461722</v>
       </c>
       <c r="D16" t="n">
-        <v>41.74489413227862</v>
+        <v>41.33157834879071</v>
       </c>
     </row>
     <row r="17">
@@ -5661,7 +5661,7 @@
         <v>32.58322455624739</v>
       </c>
       <c r="D17" t="n">
-        <v>36.83321036793183</v>
+        <v>37.30543101367455</v>
       </c>
     </row>
     <row r="18">
@@ -5700,7 +5700,7 @@
         <v>4.707480241863455</v>
       </c>
       <c r="C20" t="n">
-        <v>39.00483628972577</v>
+        <v>39.67733346713483</v>
       </c>
       <c r="D20" t="n">
         <v>16.13993225781756</v>
@@ -5711,13 +5711,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>18.05216934936604</v>
+        <v>18.05004382956612</v>
       </c>
       <c r="C21" t="n">
-        <v>117.7689143268165</v>
+        <v>117.7550478405028</v>
       </c>
       <c r="D21" t="n">
-        <v>6.017389783122013</v>
+        <v>6.016681276522039</v>
       </c>
     </row>
   </sheetData>
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.877723505325654</v>
+        <v>6.253732876052181</v>
       </c>
       <c r="C2" t="n">
-        <v>5.4172838320339</v>
+        <v>5.891467973185108</v>
       </c>
       <c r="D2" t="n">
-        <v>19.0999015861217</v>
+        <v>27.57238427377167</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>15.73741569907637</v>
+        <v>12.48783079801943</v>
       </c>
       <c r="C3" t="n">
-        <v>19.90002596508285</v>
+        <v>28.54922323949725</v>
       </c>
       <c r="D3" t="n">
-        <v>43.38833978918779</v>
+        <v>56.49958037940394</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>22.65382827549515</v>
+        <v>18.96540215063988</v>
       </c>
       <c r="C4" t="n">
-        <v>49.50659148205391</v>
+        <v>54.77759490615503</v>
       </c>
       <c r="D4" t="n">
-        <v>42.34670547498192</v>
+        <v>49.05989627662161</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>20.93576979306323</v>
+        <v>18.4077694546277</v>
       </c>
       <c r="C5" t="n">
-        <v>64.86897955810801</v>
+        <v>68.30509652297184</v>
       </c>
       <c r="D5" t="n">
-        <v>31.44047022850411</v>
+        <v>33.67394625566561</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>11.55222523587222</v>
+        <v>10.90819874188631</v>
       </c>
       <c r="C6" t="n">
-        <v>54.66174867705392</v>
+        <v>50.11331156327844</v>
       </c>
       <c r="D6" t="n">
-        <v>31.27553661419064</v>
+        <v>31.67805317293184</v>
       </c>
     </row>
     <row r="7">
@@ -5826,10 +5826,10 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>5.270021676396877</v>
+        <v>5.090361846519712</v>
       </c>
       <c r="C7" t="n">
-        <v>26.52976821186155</v>
+        <v>23.83487076370406</v>
       </c>
       <c r="D7" t="n">
         <v>30.78171751895449</v>
@@ -5843,7 +5843,7 @@
         <v>4.840016181936775</v>
       </c>
       <c r="C8" t="n">
-        <v>18.52557917913731</v>
+        <v>18.60902773399829</v>
       </c>
       <c r="D8" t="n">
         <v>30.0414797499524</v>
@@ -5857,7 +5857,7 @@
         <v>4.881249585515139</v>
       </c>
       <c r="C9" t="n">
-        <v>22.07656062539802</v>
+        <v>21.74374815365835</v>
       </c>
       <c r="D9" t="n">
         <v>29.95312245657017</v>
@@ -5868,10 +5868,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4.412955930589413</v>
+        <v>4.270602513473626</v>
       </c>
       <c r="C10" t="n">
-        <v>21.35301256736813</v>
+        <v>21.49536598448391</v>
       </c>
       <c r="D10" t="n">
         <v>33.45305302221006</v>
@@ -5885,10 +5885,10 @@
         <v>3.731623023842126</v>
       </c>
       <c r="C11" t="n">
-        <v>20.43507846389736</v>
+        <v>20.25738212942868</v>
       </c>
       <c r="D11" t="n">
-        <v>34.29539255245382</v>
+        <v>34.65078522139116</v>
       </c>
     </row>
     <row r="12">
@@ -5902,7 +5902,7 @@
         <v>19.7439280801076</v>
       </c>
       <c r="D12" t="n">
-        <v>32.11100391050467</v>
+        <v>31.89403766786613</v>
       </c>
     </row>
     <row r="13">
@@ -5941,7 +5941,7 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>15.76686813020377</v>
+        <v>16.12520604225386</v>
       </c>
       <c r="D15" t="n">
         <v>28.30869505195678</v>
@@ -5958,7 +5958,7 @@
         <v>15.70599977254047</v>
       </c>
       <c r="D16" t="n">
-        <v>26.45221014322606</v>
+        <v>26.03889435973815</v>
       </c>
     </row>
     <row r="17">
@@ -5983,7 +5983,7 @@
         <v>1.070104997629023</v>
       </c>
       <c r="C18" t="n">
-        <v>17.65673246087889</v>
+        <v>17.12167996206437</v>
       </c>
       <c r="D18" t="n">
         <v>20.33199495495144</v>
@@ -6011,7 +6011,7 @@
         <v>1.34499435481813</v>
       </c>
       <c r="C20" t="n">
-        <v>18.82992096745382</v>
+        <v>19.50241814486288</v>
       </c>
       <c r="D20" t="n">
         <v>10.08745766113597</v>
@@ -6022,13 +6022,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.054188382822082</v>
+        <v>7.052007904454229</v>
       </c>
       <c r="C21" t="n">
-        <v>66.13301608895702</v>
+        <v>66.99407509231517</v>
       </c>
       <c r="D21" t="n">
-        <v>4.408867739263802</v>
+        <v>4.407504940283893</v>
       </c>
     </row>
   </sheetData>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.844924920458009</v>
+        <v>4.738896168399354</v>
       </c>
       <c r="C2" t="n">
-        <v>4.565126824747668</v>
+        <v>9.049750337747097</v>
       </c>
       <c r="D2" t="n">
-        <v>20.03550714826891</v>
+        <v>21.15764477422301</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>18.76119862815655</v>
+        <v>18.11324514335365</v>
       </c>
       <c r="C3" t="n">
-        <v>20.71978529812893</v>
+        <v>24.98547907308132</v>
       </c>
       <c r="D3" t="n">
-        <v>48.94503179522474</v>
+        <v>66.00780689503431</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>27.92483169959628</v>
+        <v>22.29647211114931</v>
       </c>
       <c r="C4" t="n">
-        <v>49.82565948593412</v>
+        <v>65.39617807528853</v>
       </c>
       <c r="D4" t="n">
-        <v>54.85417122708628</v>
+        <v>66.81284001251667</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>28.59340188618836</v>
+        <v>24.51914891356409</v>
       </c>
       <c r="C5" t="n">
-        <v>80.65057390387548</v>
+        <v>88.55364292306231</v>
       </c>
       <c r="D5" t="n">
-        <v>40.54618018539328</v>
+        <v>44.86587008407924</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>21.37362926915731</v>
+        <v>18.99878157258428</v>
       </c>
       <c r="C6" t="n">
-        <v>83.76369587404213</v>
+        <v>84.52847733565039</v>
       </c>
       <c r="D6" t="n">
-        <v>34.41516577237194</v>
+        <v>35.74347041621788</v>
       </c>
     </row>
     <row r="7">
@@ -6137,13 +6137,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>10.24061030299848</v>
+        <v>9.581857593448868</v>
       </c>
       <c r="C7" t="n">
-        <v>57.61091878061132</v>
+        <v>52.10135066437822</v>
       </c>
       <c r="D7" t="n">
-        <v>33.53650157707104</v>
+        <v>33.17718191731671</v>
       </c>
     </row>
     <row r="8">
@@ -6154,7 +6154,7 @@
         <v>5.507604620824606</v>
       </c>
       <c r="C8" t="n">
-        <v>28.62285431731576</v>
+        <v>26.45319189093031</v>
       </c>
       <c r="D8" t="n">
         <v>32.12769362147687</v>
@@ -6168,10 +6168,10 @@
         <v>5.214062057254808</v>
       </c>
       <c r="C9" t="n">
-        <v>23.40781051235669</v>
+        <v>23.18593553119691</v>
       </c>
       <c r="D9" t="n">
-        <v>31.06249736236907</v>
+        <v>31.39530983410874</v>
       </c>
     </row>
     <row r="10">
@@ -6179,13 +6179,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4.840016181936776</v>
+        <v>4.697662764820988</v>
       </c>
       <c r="C10" t="n">
-        <v>24.76949457814703</v>
+        <v>24.34243432679967</v>
       </c>
       <c r="D10" t="n">
-        <v>33.88011327355743</v>
+        <v>33.59540643932586</v>
       </c>
     </row>
     <row r="11">
@@ -6199,7 +6199,7 @@
         <v>23.45591614986479</v>
       </c>
       <c r="D11" t="n">
-        <v>35.18387422479719</v>
+        <v>35.36157055926586</v>
       </c>
     </row>
     <row r="12">
@@ -6210,10 +6210,10 @@
         <v>3.254493639578176</v>
       </c>
       <c r="C12" t="n">
-        <v>22.1305567491316</v>
+        <v>21.91359050649305</v>
       </c>
       <c r="D12" t="n">
-        <v>32.97886888105885</v>
+        <v>33.1958351236974</v>
       </c>
     </row>
     <row r="13">
@@ -6224,10 +6224,10 @@
         <v>2.601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>20.81305133003238</v>
+        <v>21.07321447165778</v>
       </c>
       <c r="D13" t="n">
-        <v>31.21957699504857</v>
+        <v>30.95941385342317</v>
       </c>
     </row>
     <row r="14">
@@ -6235,10 +6235,10 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.536435157146258</v>
+        <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
-        <v>19.66637001147211</v>
+        <v>19.35908298004286</v>
       </c>
       <c r="D14" t="n">
         <v>30.11412908006666</v>
@@ -6255,7 +6255,7 @@
         <v>17.5585576904542</v>
       </c>
       <c r="D15" t="n">
-        <v>28.30869505195678</v>
+        <v>28.66703296400686</v>
       </c>
     </row>
     <row r="16">
@@ -6269,7 +6269,7 @@
         <v>16.53263133951629</v>
       </c>
       <c r="D16" t="n">
-        <v>26.86552592671396</v>
+        <v>26.03889435973815</v>
       </c>
     </row>
     <row r="17">
@@ -6294,10 +6294,10 @@
         <v>1.070104997629023</v>
       </c>
       <c r="C18" t="n">
-        <v>17.65673246087889</v>
+        <v>17.12167996206437</v>
       </c>
       <c r="D18" t="n">
-        <v>20.33199495495144</v>
+        <v>20.86704745376595</v>
       </c>
     </row>
     <row r="19">
@@ -6311,7 +6311,7 @@
         <v>18.65615162380213</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>15.64709491028566</v>
       </c>
     </row>
     <row r="20">
@@ -6322,7 +6322,7 @@
         <v>0.672497177409065</v>
       </c>
       <c r="C20" t="n">
-        <v>18.82992096745382</v>
+        <v>19.50241814486288</v>
       </c>
       <c r="D20" t="n">
         <v>10.75995483854504</v>
@@ -6333,13 +6333,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.276588728012793</v>
+        <v>7.27142879644605</v>
       </c>
       <c r="C21" t="n">
-        <v>75.49460805313272</v>
+        <v>76.35000236268353</v>
       </c>
       <c r="D21" t="n">
-        <v>5.457441546009594</v>
+        <v>5.453571597334538</v>
       </c>
     </row>
   </sheetData>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.101741908343174</v>
+        <v>4.432590884674349</v>
       </c>
       <c r="C2" t="n">
-        <v>6.417684742661399</v>
+        <v>12.55949838042945</v>
       </c>
       <c r="D2" t="n">
-        <v>19.68207797474005</v>
+        <v>19.00172681569702</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>17.64691498383642</v>
+        <v>17.3131207643925</v>
       </c>
       <c r="C3" t="n">
-        <v>18.9280957378785</v>
+        <v>31.06740610089032</v>
       </c>
       <c r="D3" t="n">
-        <v>53.61815086743955</v>
+        <v>67.61787312999907</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>32.72361447795468</v>
+        <v>29.31596819651401</v>
       </c>
       <c r="C4" t="n">
-        <v>51.07640606114455</v>
+        <v>63.78807533573226</v>
       </c>
       <c r="D4" t="n">
-        <v>67.08085713577607</v>
+        <v>84.89761447244717</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>36.22649028670731</v>
+        <v>29.62423697564751</v>
       </c>
       <c r="C5" t="n">
-        <v>86.49197274414401</v>
+        <v>105.8569462104124</v>
       </c>
       <c r="D5" t="n">
-        <v>50.75635630956011</v>
+        <v>58.31581363226055</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>30.79251674370121</v>
+        <v>26.52584122104457</v>
       </c>
       <c r="C6" t="n">
-        <v>108.8404774836184</v>
+        <v>115.6027556704704</v>
       </c>
       <c r="D6" t="n">
-        <v>39.7686360036298</v>
+        <v>42.14348370020284</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>18.56484908730718</v>
+        <v>16.58859095865835</v>
       </c>
       <c r="C7" t="n">
-        <v>93.00390526641308</v>
+        <v>90.30900781825558</v>
       </c>
       <c r="D7" t="n">
-        <v>35.93196597543326</v>
+        <v>36.35117224514665</v>
       </c>
     </row>
     <row r="8">
@@ -6462,13 +6462,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>8.595201150680824</v>
+        <v>8.17795837637593</v>
       </c>
       <c r="C8" t="n">
-        <v>54.9091490985241</v>
+        <v>49.48499303256047</v>
       </c>
       <c r="D8" t="n">
-        <v>34.29735604786232</v>
+        <v>33.79666471869644</v>
       </c>
     </row>
     <row r="9">
@@ -6479,10 +6479,10 @@
         <v>5.657812019574366</v>
       </c>
       <c r="C9" t="n">
-        <v>30.28593492830985</v>
+        <v>28.6218725696115</v>
       </c>
       <c r="D9" t="n">
-        <v>32.61562223048752</v>
+        <v>32.9484347022272</v>
       </c>
     </row>
     <row r="10">
@@ -6490,13 +6490,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>5.124723016168351</v>
+        <v>4.982369599052563</v>
       </c>
       <c r="C10" t="n">
-        <v>27.18950266911542</v>
+        <v>26.76244241776806</v>
       </c>
       <c r="D10" t="n">
-        <v>34.02246669067321</v>
+        <v>33.88011327355743</v>
       </c>
     </row>
     <row r="11">
@@ -6507,7 +6507,7 @@
         <v>4.442408361716816</v>
       </c>
       <c r="C11" t="n">
-        <v>26.83214650476957</v>
+        <v>26.47675383583222</v>
       </c>
       <c r="D11" t="n">
         <v>35.89465956267188</v>
@@ -6521,10 +6521,10 @@
         <v>3.471459882216721</v>
       </c>
       <c r="C12" t="n">
-        <v>24.95111790343269</v>
+        <v>24.5171854181556</v>
       </c>
       <c r="D12" t="n">
-        <v>33.62976760897449</v>
+        <v>34.28066633689012</v>
       </c>
     </row>
     <row r="13">
@@ -6532,13 +6532,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.601631416254048</v>
+        <v>2.861794557879452</v>
       </c>
       <c r="C13" t="n">
-        <v>22.89435646303562</v>
+        <v>23.15451960466103</v>
       </c>
       <c r="D13" t="n">
-        <v>32.00006641992479</v>
+        <v>31.47974013667398</v>
       </c>
     </row>
     <row r="14">
@@ -6552,7 +6552,7 @@
         <v>21.51009220004762</v>
       </c>
       <c r="D14" t="n">
-        <v>30.72870314292517</v>
+        <v>30.42141611149592</v>
       </c>
     </row>
     <row r="15">
@@ -6566,7 +6566,7 @@
         <v>19.35024725070463</v>
       </c>
       <c r="D15" t="n">
-        <v>28.30869505195678</v>
+        <v>29.02537087605695</v>
       </c>
     </row>
     <row r="16">
@@ -6577,10 +6577,10 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>17.77257868998001</v>
+        <v>17.3592629064921</v>
       </c>
       <c r="D16" t="n">
-        <v>27.27884171020187</v>
+        <v>26.03889435973815</v>
       </c>
     </row>
     <row r="17">
@@ -6594,7 +6594,7 @@
         <v>17.47216389248049</v>
       </c>
       <c r="D17" t="n">
-        <v>24.55547357862122</v>
+        <v>24.0832529328785</v>
       </c>
     </row>
     <row r="18">
@@ -6608,7 +6608,7 @@
         <v>17.65673246087889</v>
       </c>
       <c r="D18" t="n">
-        <v>20.33199495495144</v>
+        <v>20.86704745376595</v>
       </c>
     </row>
     <row r="19">
@@ -6633,7 +6633,7 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>18.82992096745382</v>
+        <v>19.50241814486288</v>
       </c>
       <c r="D20" t="n">
         <v>10.75995483854504</v>
@@ -6644,13 +6644,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.487216044833052</v>
+        <v>7.477884807051963</v>
       </c>
       <c r="C21" t="n">
-        <v>84.23118050437184</v>
+        <v>85.99567528109758</v>
       </c>
       <c r="D21" t="n">
-        <v>6.55131403922892</v>
+        <v>6.543149206170468</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_surface_area_iteration_56_growth_param_0.5.xlsx
+++ b/output/yearly_surface_area_iteration_56_growth_param_0.5.xlsx
@@ -735,10 +735,10 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>10.84497630196448</v>
+        <v>10.84497655533858</v>
       </c>
       <c r="C21" t="n">
-        <v>37.78907183650206</v>
+        <v>37.78907271937829</v>
       </c>
       <c r="D21" t="n">
         <v>0</v>
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.233296100712247</v>
+        <v>1.124101121362598</v>
       </c>
       <c r="C2" t="n">
-        <v>7.675303551801563</v>
+        <v>3.29965403397353</v>
       </c>
       <c r="D2" t="n">
-        <v>17.99641716654828</v>
+        <v>17.67833091037232</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>16.09084487260522</v>
+        <v>9.036987617591889</v>
       </c>
       <c r="C3" t="n">
-        <v>41.14504628498383</v>
+        <v>30.46363126277852</v>
       </c>
       <c r="D3" t="n">
-        <v>66.90610604442013</v>
+        <v>99.03379966589699</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>31.48563062289946</v>
+        <v>14.28148385367835</v>
       </c>
       <c r="C4" t="n">
-        <v>70.48850341721673</v>
+        <v>82.91939284838985</v>
       </c>
       <c r="D4" t="n">
-        <v>97.2008767020682</v>
+        <v>121.3224177954123</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>36.52101459798135</v>
+        <v>12.10004045484194</v>
       </c>
       <c r="C5" t="n">
-        <v>112.0419567471673</v>
+        <v>91.25344910974104</v>
       </c>
       <c r="D5" t="n">
-        <v>74.66191290796993</v>
+        <v>66.09616418841652</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>33.52962934314132</v>
+        <v>8.171086142446205</v>
       </c>
       <c r="C6" t="n">
-        <v>141.0820538387879</v>
+        <v>50.03280825153021</v>
       </c>
       <c r="D6" t="n">
-        <v>50.27431818677493</v>
+        <v>31.43654323768712</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>23.89475737366311</v>
+        <v>5.689227946110266</v>
       </c>
       <c r="C7" t="n">
-        <v>129.4748507314779</v>
+        <v>30.12296480940488</v>
       </c>
       <c r="D7" t="n">
-        <v>39.70482240285375</v>
+        <v>29.46421209985527</v>
       </c>
     </row>
     <row r="8">
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>12.93452600345173</v>
+        <v>6.091744504851458</v>
       </c>
       <c r="C8" t="n">
-        <v>84.11614329986671</v>
+        <v>27.78836876870596</v>
       </c>
       <c r="D8" t="n">
-        <v>36.04977569994287</v>
+        <v>31.12631096314512</v>
       </c>
     </row>
     <row r="9">
@@ -878,13 +878,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>7.09999939711293</v>
+        <v>5.879687000734146</v>
       </c>
       <c r="C9" t="n">
-        <v>45.26249615659493</v>
+        <v>31.8390597964283</v>
       </c>
       <c r="D9" t="n">
-        <v>33.9468721174462</v>
+        <v>34.94530953266521</v>
       </c>
     </row>
     <row r="10">
@@ -892,13 +892,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>5.267076433284139</v>
+        <v>3.4164820107789</v>
       </c>
       <c r="C10" t="n">
-        <v>31.03304493124168</v>
+        <v>30.17892442854695</v>
       </c>
       <c r="D10" t="n">
-        <v>34.73423377625215</v>
+        <v>38.29306920414684</v>
       </c>
     </row>
     <row r="11">
@@ -906,13 +906,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.620104696185489</v>
+        <v>2.665445017030089</v>
       </c>
       <c r="C11" t="n">
-        <v>28.96450251839364</v>
+        <v>31.45225120095506</v>
       </c>
       <c r="D11" t="n">
-        <v>35.89465956267188</v>
+        <v>37.6716229073586</v>
       </c>
     </row>
     <row r="12">
@@ -920,13 +920,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.688426124855267</v>
+        <v>2.169662426385451</v>
       </c>
       <c r="C12" t="n">
-        <v>27.55471281509523</v>
+        <v>24.0832529328785</v>
       </c>
       <c r="D12" t="n">
-        <v>35.1485313074443</v>
+        <v>37.96909246174538</v>
       </c>
     </row>
     <row r="13">
@@ -934,13 +934,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.861794557879452</v>
+        <v>1.821141991377834</v>
       </c>
       <c r="C13" t="n">
-        <v>25.49598787928967</v>
+        <v>20.03256190515617</v>
       </c>
       <c r="D13" t="n">
-        <v>32.00006641992479</v>
+        <v>35.90251354430586</v>
       </c>
     </row>
     <row r="14">
@@ -948,13 +948,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>2.151009220004762</v>
+        <v>1.536435157146258</v>
       </c>
       <c r="C14" t="n">
-        <v>23.35381438862312</v>
+        <v>19.97365704290136</v>
       </c>
       <c r="D14" t="n">
-        <v>30.72870314292517</v>
+        <v>27.3485457972034</v>
       </c>
     </row>
     <row r="15">
@@ -968,7 +968,7 @@
         <v>21.14193681095506</v>
       </c>
       <c r="D15" t="n">
-        <v>29.38370878810703</v>
+        <v>25.80032966760617</v>
       </c>
     </row>
     <row r="16">
@@ -976,13 +976,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.239947350463722</v>
+        <v>1.653263133951629</v>
       </c>
       <c r="C16" t="n">
-        <v>18.59921025695582</v>
+        <v>22.7323680918349</v>
       </c>
       <c r="D16" t="n">
-        <v>26.03889435973815</v>
+        <v>21.90573652485908</v>
       </c>
     </row>
     <row r="17">
@@ -990,13 +990,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0.9444412914854317</v>
+        <v>1.416661937228147</v>
       </c>
       <c r="C17" t="n">
-        <v>17.9443845382232</v>
+        <v>24.55547357862122</v>
       </c>
       <c r="D17" t="n">
-        <v>24.0832529328785</v>
+        <v>18.41660518396592</v>
       </c>
     </row>
     <row r="18">
@@ -1004,13 +1004,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>0.5350524988145117</v>
+        <v>1.605157496443535</v>
       </c>
       <c r="C18" t="n">
-        <v>18.1917849596934</v>
+        <v>26.21757244191107</v>
       </c>
       <c r="D18" t="n">
-        <v>20.86704745376595</v>
+        <v>11.23610247510475</v>
       </c>
     </row>
     <row r="19">
@@ -1018,13 +1018,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>0</v>
+        <v>11.4344155113626</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>84.85539932116455</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>3.009056713516474</v>
       </c>
     </row>
     <row r="20">
@@ -1035,10 +1035,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>10.75995483854504</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1046,13 +1046,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.669499982965761</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>94.91006228920131</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>7.669499982965761</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.970989537229101</v>
+        <v>0.8659014751456867</v>
       </c>
       <c r="C2" t="n">
-        <v>13.43914432343459</v>
+        <v>10.84045815029328</v>
       </c>
       <c r="D2" t="n">
-        <v>19.75374555715007</v>
+        <v>17.12757044828985</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>15.03055735201867</v>
+        <v>6.312637738306991</v>
       </c>
       <c r="C3" t="n">
-        <v>35.18583772020568</v>
+        <v>20.22891144600553</v>
       </c>
       <c r="D3" t="n">
-        <v>65.54638547403829</v>
+        <v>90.44350725373741</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>30.70710469343173</v>
+        <v>16.13207827618359</v>
       </c>
       <c r="C4" t="n">
-        <v>85.49746231974197</v>
+        <v>79.15439040260334</v>
       </c>
       <c r="D4" t="n">
-        <v>106.7601540983194</v>
+        <v>142.4702450925929</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>41.55247158224626</v>
+        <v>16.76334205001429</v>
       </c>
       <c r="C5" t="n">
-        <v>120.5340743889022</v>
+        <v>126.2282110735337</v>
       </c>
       <c r="D5" t="n">
-        <v>88.89725461954869</v>
+        <v>92.97150759217296</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>40.53341746523807</v>
+        <v>12.07549676223577</v>
       </c>
       <c r="C6" t="n">
-        <v>157.1827161884356</v>
+        <v>99.70335160019334</v>
       </c>
       <c r="D6" t="n">
-        <v>60.65924540229769</v>
+        <v>43.55229165579701</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>31.14103717870882</v>
+        <v>7.665486074759095</v>
       </c>
       <c r="C7" t="n">
-        <v>164.8678372172796</v>
+        <v>51.68214439466484</v>
       </c>
       <c r="D7" t="n">
-        <v>44.01665831990574</v>
+        <v>31.85967649821749</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>18.94282195344221</v>
+        <v>6.425538724295373</v>
       </c>
       <c r="C8" t="n">
-        <v>123.8376554136927</v>
+        <v>34.38080460272329</v>
       </c>
       <c r="D8" t="n">
-        <v>38.46978379091126</v>
+        <v>32.54493639578176</v>
       </c>
     </row>
     <row r="9">
@@ -1189,13 +1189,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>9.762499171030278</v>
+        <v>6.212499472473814</v>
       </c>
       <c r="C9" t="n">
-        <v>72.55311883924776</v>
+        <v>34.50155957034565</v>
       </c>
       <c r="D9" t="n">
-        <v>35.16718451382499</v>
+        <v>35.38905949498476</v>
       </c>
     </row>
     <row r="10">
@@ -1203,13 +1203,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>5.978843518863076</v>
+        <v>4.128249096357838</v>
       </c>
       <c r="C10" t="n">
-        <v>41.28249096357838</v>
+        <v>34.73423377625215</v>
       </c>
       <c r="D10" t="n">
-        <v>35.58835427894688</v>
+        <v>39.00483628972578</v>
       </c>
     </row>
     <row r="11">
@@ -1217,13 +1217,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.797801030654161</v>
+        <v>2.843141351498762</v>
       </c>
       <c r="C11" t="n">
-        <v>32.51842920776709</v>
+        <v>34.47308888692249</v>
       </c>
       <c r="D11" t="n">
-        <v>36.07235589714055</v>
+        <v>38.56010457970196</v>
       </c>
     </row>
     <row r="12">
@@ -1231,13 +1231,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.905392367493811</v>
+        <v>2.169662426385451</v>
       </c>
       <c r="C12" t="n">
-        <v>29.94134148411922</v>
+        <v>28.8565102709265</v>
       </c>
       <c r="D12" t="n">
-        <v>35.79943003535993</v>
+        <v>38.40302494702248</v>
       </c>
     </row>
     <row r="13">
@@ -1245,13 +1245,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.861794557879452</v>
+        <v>1.821141991377834</v>
       </c>
       <c r="C13" t="n">
-        <v>28.09761929554372</v>
+        <v>22.89435646303562</v>
       </c>
       <c r="D13" t="n">
-        <v>32.5203927031756</v>
+        <v>36.68300296918207</v>
       </c>
     </row>
     <row r="14">
@@ -1259,13 +1259,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>2.151009220004762</v>
+        <v>1.229148125717007</v>
       </c>
       <c r="C14" t="n">
-        <v>25.19753657719863</v>
+        <v>21.20280516861837</v>
       </c>
       <c r="D14" t="n">
-        <v>31.03599017435442</v>
+        <v>28.88498095434966</v>
       </c>
     </row>
     <row r="15">
@@ -1279,7 +1279,7 @@
         <v>22.93362637120549</v>
       </c>
       <c r="D15" t="n">
-        <v>29.74204670015712</v>
+        <v>25.44199175555609</v>
       </c>
     </row>
     <row r="16">
@@ -1290,10 +1290,10 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>19.83915760741954</v>
+        <v>25.62557857625024</v>
       </c>
       <c r="D16" t="n">
-        <v>26.03889435973815</v>
+        <v>21.49242074137117</v>
       </c>
     </row>
     <row r="17">
@@ -1301,13 +1301,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0.9444412914854317</v>
+        <v>1.416661937228147</v>
       </c>
       <c r="C17" t="n">
-        <v>18.88882582970863</v>
+        <v>26.44435616159209</v>
       </c>
       <c r="D17" t="n">
-        <v>24.0832529328785</v>
+        <v>17.47216389248049</v>
       </c>
     </row>
     <row r="18">
@@ -1315,13 +1315,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>0.5350524988145117</v>
+        <v>9.095892479846698</v>
       </c>
       <c r="C18" t="n">
-        <v>18.1917849596934</v>
+        <v>50.82998738737861</v>
       </c>
       <c r="D18" t="n">
-        <v>20.86704745376595</v>
+        <v>9.095892479846698</v>
       </c>
     </row>
     <row r="19">
@@ -1332,10 +1332,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>46.33947338815369</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>1.805434028109884</v>
       </c>
     </row>
     <row r="20">
@@ -1346,10 +1346,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>10.75995483854504</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1357,13 +1357,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.845700542175535</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>102.9748196160539</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>8.826413109947476</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.117269945161876</v>
+        <v>0.4614214209960009</v>
       </c>
       <c r="C2" t="n">
-        <v>12.02935462013617</v>
+        <v>4.480696522182442</v>
       </c>
       <c r="D2" t="n">
-        <v>22.88748422910589</v>
+        <v>11.543389506534</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>16.90078672860884</v>
+        <v>5.532148313430777</v>
       </c>
       <c r="C3" t="n">
-        <v>43.10363295495621</v>
+        <v>32.70201602846125</v>
       </c>
       <c r="D3" t="n">
-        <v>65.33530971762524</v>
+        <v>87.36572820092366</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>29.06071379340984</v>
+        <v>17.59979109403257</v>
       </c>
       <c r="C4" t="n">
-        <v>85.42088599881073</v>
+        <v>75.40215067697201</v>
       </c>
       <c r="D4" t="n">
-        <v>111.6482759177643</v>
+        <v>157.0197460695306</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>43.04963683122264</v>
+        <v>16.61607989437727</v>
       </c>
       <c r="C5" t="n">
-        <v>134.9657656413303</v>
+        <v>147.5321362556895</v>
       </c>
       <c r="D5" t="n">
-        <v>102.9362467902781</v>
+        <v>104.7279363505285</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>46.73217246985243</v>
+        <v>10.22392059202629</v>
       </c>
       <c r="C6" t="n">
-        <v>172.1160805177338</v>
+        <v>130.7373782791393</v>
       </c>
       <c r="D6" t="n">
-        <v>70.68190771495337</v>
+        <v>43.63279496754524</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>38.50709020367265</v>
+        <v>4.251949307092936</v>
       </c>
       <c r="C7" t="n">
-        <v>190.19987322996</v>
+        <v>52.4007837141735</v>
       </c>
       <c r="D7" t="n">
-        <v>49.88554609589318</v>
+        <v>33.59638818703009</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>24.86766934857171</v>
+        <v>4.255876297909922</v>
       </c>
       <c r="C8" t="n">
-        <v>162.9750276434918</v>
+        <v>37.55184968744049</v>
       </c>
       <c r="D8" t="n">
-        <v>40.55599766243574</v>
+        <v>36.21667280966483</v>
       </c>
     </row>
     <row r="9">
@@ -1500,13 +1500,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>13.42343636016663</v>
+        <v>2.884374755077128</v>
       </c>
       <c r="C9" t="n">
-        <v>106.7218659378537</v>
+        <v>26.5140602485936</v>
       </c>
       <c r="D9" t="n">
-        <v>36.83124687252333</v>
+        <v>40.82499653339935</v>
       </c>
     </row>
     <row r="10">
@@ -1514,13 +1514,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>7.260024272905163</v>
+        <v>1.992947839621025</v>
       </c>
       <c r="C10" t="n">
-        <v>59.07666810305182</v>
+        <v>27.04714925199963</v>
       </c>
       <c r="D10" t="n">
-        <v>35.87306111317846</v>
+        <v>30.17892442854695</v>
       </c>
     </row>
     <row r="11">
@@ -1528,13 +1528,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>5.153193699591506</v>
+        <v>1.599267010218054</v>
       </c>
       <c r="C11" t="n">
-        <v>38.56010457970196</v>
+        <v>23.10052348092744</v>
       </c>
       <c r="D11" t="n">
-        <v>36.60544490054656</v>
+        <v>30.74146586308036</v>
       </c>
     </row>
     <row r="12">
@@ -1542,13 +1542,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>4.122358610132356</v>
+        <v>1.301797455831271</v>
       </c>
       <c r="C12" t="n">
-        <v>32.97886888105885</v>
+        <v>18.65909686691488</v>
       </c>
       <c r="D12" t="n">
-        <v>35.79943003535993</v>
+        <v>29.94134148411922</v>
       </c>
     </row>
     <row r="13">
@@ -1556,13 +1556,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.861794557879452</v>
+        <v>0.7804894248762143</v>
       </c>
       <c r="C13" t="n">
-        <v>30.17892442854696</v>
+        <v>17.43093048890212</v>
       </c>
       <c r="D13" t="n">
-        <v>33.30088212805181</v>
+        <v>23.93500902953724</v>
       </c>
     </row>
     <row r="14">
@@ -1570,13 +1570,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>2.151009220004762</v>
+        <v>0.921861094287755</v>
       </c>
       <c r="C14" t="n">
-        <v>27.3485457972034</v>
+        <v>19.0517959486136</v>
       </c>
       <c r="D14" t="n">
-        <v>31.03599017435442</v>
+        <v>21.20280516861837</v>
       </c>
     </row>
     <row r="15">
@@ -1584,13 +1584,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.433351648200343</v>
+        <v>0.7166758241001715</v>
       </c>
       <c r="C15" t="n">
-        <v>24.72531593145592</v>
+        <v>21.50027472300514</v>
       </c>
       <c r="D15" t="n">
-        <v>29.74204670015712</v>
+        <v>17.91689560250429</v>
       </c>
     </row>
     <row r="16">
@@ -1598,13 +1598,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.239947350463722</v>
+        <v>0.8266315669758143</v>
       </c>
       <c r="C16" t="n">
-        <v>21.07910495788326</v>
+        <v>22.31905230834699</v>
       </c>
       <c r="D16" t="n">
-        <v>26.45221014322606</v>
+        <v>14.87936820556466</v>
       </c>
     </row>
     <row r="17">
@@ -1612,13 +1612,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0.9444412914854317</v>
+        <v>7.083309686140737</v>
       </c>
       <c r="C17" t="n">
-        <v>19.36104647545135</v>
+        <v>43.91652005407257</v>
       </c>
       <c r="D17" t="n">
-        <v>24.0832529328785</v>
+        <v>7.555530331883453</v>
       </c>
     </row>
     <row r="18">
@@ -1626,13 +1626,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>0.5350524988145117</v>
+        <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>18.72683745850791</v>
+        <v>40.12893741108837</v>
       </c>
       <c r="D18" t="n">
-        <v>20.86704745376595</v>
+        <v>1.070104997629023</v>
       </c>
     </row>
     <row r="19">
@@ -1643,10 +1643,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1657,10 +1657,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>10.75995483854504</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1668,13 +1668,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8.005568980755079</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>111.0772696079767</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>10.00696122594385</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.648976290236146</v>
+        <v>0.5056000676871074</v>
       </c>
       <c r="C2" t="n">
-        <v>8.276133146800611</v>
+        <v>5.560618996853934</v>
       </c>
       <c r="D2" t="n">
-        <v>18.93693146721673</v>
+        <v>12.9737959116216</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>20.17491532227195</v>
+        <v>3.485204350076177</v>
       </c>
       <c r="C3" t="n">
-        <v>61.99245878466484</v>
+        <v>24.16081100151401</v>
       </c>
       <c r="D3" t="n">
-        <v>72.77695731581605</v>
+        <v>77.54334241993432</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>20.67560665143782</v>
+        <v>14.38358561492002</v>
       </c>
       <c r="C4" t="n">
-        <v>113.2946668177862</v>
+        <v>79.62661104834605</v>
       </c>
       <c r="D4" t="n">
-        <v>109.8742578161903</v>
+        <v>164.3583101587755</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>26.31083847381452</v>
+        <v>21.35301256736813</v>
       </c>
       <c r="C5" t="n">
-        <v>102.8380720198534</v>
+        <v>144.6114368355552</v>
       </c>
       <c r="D5" t="n">
-        <v>69.90043654237292</v>
+        <v>133.7140373184156</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>23.90948358922682</v>
+        <v>15.57739082328414</v>
       </c>
       <c r="C6" t="n">
-        <v>125.2631530802591</v>
+        <v>184.2720805917178</v>
       </c>
       <c r="D6" t="n">
-        <v>32.8453511932813</v>
+        <v>63.15484806649307</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>16.46881773874025</v>
+        <v>7.246279805045708</v>
       </c>
       <c r="C7" t="n">
-        <v>114.563084851673</v>
+        <v>116.0602501006494</v>
       </c>
       <c r="D7" t="n">
-        <v>28.50602634051038</v>
+        <v>37.54890444432775</v>
       </c>
     </row>
     <row r="8">
@@ -1797,13 +1797,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>9.262789589568655</v>
+        <v>4.589670517353839</v>
       </c>
       <c r="C8" t="n">
-        <v>78.60853867904211</v>
+        <v>52.48914100755572</v>
       </c>
       <c r="D8" t="n">
-        <v>27.12078032981814</v>
+        <v>37.55184968744049</v>
       </c>
     </row>
     <row r="9">
@@ -1811,13 +1811,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.214062057254808</v>
+        <v>3.328124717396686</v>
       </c>
       <c r="C9" t="n">
-        <v>45.04062117543515</v>
+        <v>35.72187196672443</v>
       </c>
       <c r="D9" t="n">
-        <v>27.29062268265283</v>
+        <v>41.93437143919824</v>
       </c>
     </row>
     <row r="10">
@@ -1825,13 +1825,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>3.701188845010476</v>
+        <v>2.2776546738526</v>
       </c>
       <c r="C10" t="n">
         <v>30.17892442854695</v>
       </c>
       <c r="D10" t="n">
-        <v>28.61303684027329</v>
+        <v>31.8871654339364</v>
       </c>
     </row>
     <row r="11">
@@ -1839,13 +1839,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>3.020837685967435</v>
+        <v>1.421570675749381</v>
       </c>
       <c r="C11" t="n">
-        <v>26.29905750136355</v>
+        <v>26.83214650476957</v>
       </c>
       <c r="D11" t="n">
-        <v>28.60910984945629</v>
+        <v>31.8076438698924</v>
       </c>
     </row>
     <row r="12">
@@ -1853,13 +1853,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>2.169662426385451</v>
+        <v>1.084831213192725</v>
       </c>
       <c r="C12" t="n">
-        <v>24.5171854181556</v>
+        <v>21.69662426385451</v>
       </c>
       <c r="D12" t="n">
-        <v>27.12078032981814</v>
+        <v>30.8092064546734</v>
       </c>
     </row>
     <row r="13">
@@ -1867,13 +1867,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>1.560978849752429</v>
+        <v>0.7804894248762143</v>
       </c>
       <c r="C13" t="n">
-        <v>22.63419332141022</v>
+        <v>20.81305133003238</v>
       </c>
       <c r="D13" t="n">
-        <v>25.49598787928967</v>
+        <v>23.93500902953724</v>
       </c>
     </row>
     <row r="14">
@@ -1881,13 +1881,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0.921861094287755</v>
+        <v>0.6145740628585034</v>
       </c>
       <c r="C14" t="n">
-        <v>20.58823110575986</v>
+        <v>21.20280516861837</v>
       </c>
       <c r="D14" t="n">
-        <v>24.89024954576939</v>
+        <v>20.89551813718911</v>
       </c>
     </row>
     <row r="15">
@@ -1898,10 +1898,10 @@
         <v>0.7166758241001715</v>
       </c>
       <c r="C15" t="n">
+        <v>23.65030219530566</v>
+      </c>
+      <c r="D15" t="n">
         <v>17.5585576904542</v>
-      </c>
-      <c r="D15" t="n">
-        <v>22.21695054710532</v>
       </c>
     </row>
     <row r="16">
@@ -1909,13 +1909,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>0.4133157834879072</v>
+        <v>5.373105185342793</v>
       </c>
       <c r="C16" t="n">
-        <v>16.53263133951629</v>
+        <v>37.19842051391164</v>
       </c>
       <c r="D16" t="n">
-        <v>20.25247339090745</v>
+        <v>12.81278928812512</v>
       </c>
     </row>
     <row r="17">
@@ -1926,10 +1926,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>16.05550195525234</v>
+        <v>47.6942852200143</v>
       </c>
       <c r="D17" t="n">
-        <v>17.9443845382232</v>
+        <v>4.722206457427158</v>
       </c>
     </row>
     <row r="18">
@@ -1940,10 +1940,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>16.05157496443535</v>
+        <v>1.070104997629023</v>
       </c>
       <c r="D18" t="n">
-        <v>13.9113649691773</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -1954,10 +1954,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>16.85071759569225</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>9.027170140549421</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1965,13 +1965,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>5.37997741927252</v>
+        <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>74.64718669240621</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>6.724971774090649</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.395865308989717</v>
+        <v>0.3337942194439155</v>
       </c>
       <c r="C2" t="n">
-        <v>3.492076584005904</v>
+        <v>3.910301106015046</v>
       </c>
       <c r="D2" t="n">
-        <v>13.28500993386784</v>
+        <v>9.423796213065133</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>20.38108234016379</v>
+        <v>2.734167356327367</v>
       </c>
       <c r="C3" t="n">
-        <v>47.82583941238337</v>
+        <v>23.39995653072273</v>
       </c>
       <c r="D3" t="n">
-        <v>72.26153977108648</v>
+        <v>71.34851440613694</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>28.57573042751191</v>
+        <v>11.63960078155018</v>
       </c>
       <c r="C4" t="n">
-        <v>137.3523943103543</v>
+        <v>72.51777592189489</v>
       </c>
       <c r="D4" t="n">
-        <v>119.0123654473196</v>
+        <v>168.2381770859589</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>29.28062527916113</v>
+        <v>22.72745935331366</v>
       </c>
       <c r="C5" t="n">
-        <v>151.9990883100124</v>
+        <v>150.6491852166731</v>
       </c>
       <c r="D5" t="n">
-        <v>86.76195336281188</v>
+        <v>153.668059407232</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>28.49817235887642</v>
+        <v>19.32079481957723</v>
       </c>
       <c r="C6" t="n">
-        <v>146.2745174465493</v>
+        <v>210.6369151892659</v>
       </c>
       <c r="D6" t="n">
-        <v>41.25794727097221</v>
+        <v>80.70457002760907</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>15.4507453694363</v>
+        <v>8.144578954431539</v>
       </c>
       <c r="C7" t="n">
-        <v>143.6080906818149</v>
+        <v>170.4372919434718</v>
       </c>
       <c r="D7" t="n">
-        <v>31.56024344842221</v>
+        <v>42.39971985101125</v>
       </c>
     </row>
     <row r="8">
@@ -2108,13 +2108,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>7.927612711792993</v>
+        <v>4.339324852770902</v>
       </c>
       <c r="C8" t="n">
-        <v>102.3913768144211</v>
+        <v>80.02716411167874</v>
       </c>
       <c r="D8" t="n">
-        <v>27.87181732356695</v>
+        <v>40.38910055271378</v>
       </c>
     </row>
     <row r="9">
@@ -2122,13 +2122,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>4.437499623195581</v>
+        <v>2.884374755077128</v>
       </c>
       <c r="C9" t="n">
-        <v>50.25468323268996</v>
+        <v>45.26249615659493</v>
       </c>
       <c r="D9" t="n">
-        <v>28.28906009787183</v>
+        <v>41.93437143919824</v>
       </c>
     </row>
     <row r="10">
@@ -2136,13 +2136,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>2.135301256736813</v>
+        <v>1.423534171157875</v>
       </c>
       <c r="C10" t="n">
-        <v>32.45657910239955</v>
+        <v>32.88363935374691</v>
       </c>
       <c r="D10" t="n">
-        <v>29.89421759431538</v>
+        <v>32.88363935374691</v>
       </c>
     </row>
     <row r="11">
@@ -2150,13 +2150,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>1.599267010218054</v>
+        <v>0.7107853378746906</v>
       </c>
       <c r="C11" t="n">
-        <v>29.14219885286231</v>
+        <v>27.54293184264426</v>
       </c>
       <c r="D11" t="n">
-        <v>29.67528785626833</v>
+        <v>33.05151821117311</v>
       </c>
     </row>
     <row r="12">
@@ -2164,13 +2164,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>1.084831213192725</v>
+        <v>0.4339324852770902</v>
       </c>
       <c r="C12" t="n">
-        <v>20.61179305066178</v>
+        <v>23.21538796232432</v>
       </c>
       <c r="D12" t="n">
-        <v>28.42257778564941</v>
+        <v>29.50740899884213</v>
       </c>
     </row>
     <row r="13">
@@ -2178,13 +2178,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0.5203262832508095</v>
+        <v>0.2601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>16.91060420565131</v>
+        <v>17.43093048890212</v>
       </c>
       <c r="D13" t="n">
-        <v>26.01631416254048</v>
+        <v>24.19517217116264</v>
       </c>
     </row>
     <row r="14">
@@ -2195,10 +2195,10 @@
         <v>0.3072870314292517</v>
       </c>
       <c r="C14" t="n">
-        <v>14.74977750860408</v>
+        <v>19.66637001147211</v>
       </c>
       <c r="D14" t="n">
-        <v>18.4372218857551</v>
+        <v>16.59349969717959</v>
       </c>
     </row>
     <row r="15">
@@ -2206,13 +2206,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>4.30005494460103</v>
       </c>
       <c r="C15" t="n">
-        <v>13.97517856995334</v>
+        <v>31.53373626040754</v>
       </c>
       <c r="D15" t="n">
-        <v>17.20021977840412</v>
+        <v>10.75013736150257</v>
       </c>
     </row>
     <row r="16">
@@ -2223,10 +2223,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>13.63942085510094</v>
+        <v>40.5049467818149</v>
       </c>
       <c r="D16" t="n">
-        <v>15.29268398905256</v>
+        <v>3.719842051391165</v>
       </c>
     </row>
     <row r="17">
@@ -2237,10 +2237,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>13.69439872653876</v>
+        <v>0.4722206457427158</v>
       </c>
       <c r="D17" t="n">
-        <v>11.8055161435679</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2251,10 +2251,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>14.44641746799181</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>7.490734983403163</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2262,13 +2262,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>4.212679398923063</v>
+        <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>64.99562501195582</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>5.416302084329653</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.263730279543897</v>
+        <v>0.4781111319681966</v>
       </c>
       <c r="C2" t="n">
-        <v>10.30344215607028</v>
+        <v>9.841038987370027</v>
       </c>
       <c r="D2" t="n">
-        <v>17.60764507566654</v>
+        <v>12.6508009169244</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>15.94849145548944</v>
+        <v>1.934042977366216</v>
       </c>
       <c r="C3" t="n">
-        <v>30.07584091960103</v>
+        <v>19.20789383358884</v>
       </c>
       <c r="D3" t="n">
-        <v>66.61158173314608</v>
+        <v>63.25400458462199</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>33.60424216866407</v>
+        <v>8.62759882492097</v>
       </c>
       <c r="C4" t="n">
-        <v>128.2525748396906</v>
+        <v>65.39617807528853</v>
       </c>
       <c r="D4" t="n">
-        <v>126.6317093799791</v>
+        <v>165.9408874580214</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>35.36746104549135</v>
+        <v>20.66578917439536</v>
       </c>
       <c r="C5" t="n">
-        <v>200.4974248998049</v>
+        <v>142.3534171157875</v>
       </c>
       <c r="D5" t="n">
-        <v>105.9305772882309</v>
+        <v>175.0701593598125</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>33.40887437551896</v>
+        <v>24.35225180384214</v>
       </c>
       <c r="C6" t="n">
-        <v>191.758888584304</v>
+        <v>226.7375775389137</v>
       </c>
       <c r="D6" t="n">
-        <v>55.2252718592916</v>
+        <v>104.2920403698429</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>22.75691178444107</v>
+        <v>14.07335334037803</v>
       </c>
       <c r="C7" t="n">
-        <v>176.126519889582</v>
+        <v>230.5634483423634</v>
       </c>
       <c r="D7" t="n">
-        <v>35.27321326588365</v>
+        <v>52.58044354405067</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>11.09865779651019</v>
+        <v>6.00829594999048</v>
       </c>
       <c r="C8" t="n">
-        <v>141.6121975990812</v>
+        <v>144.0322056900496</v>
       </c>
       <c r="D8" t="n">
-        <v>29.6242369756475</v>
+        <v>42.30841731451629</v>
       </c>
     </row>
     <row r="9">
@@ -2433,13 +2433,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.657812019574366</v>
+        <v>3.328124717396686</v>
       </c>
       <c r="C9" t="n">
-        <v>81.7609305573786</v>
+        <v>68.44843168779184</v>
       </c>
       <c r="D9" t="n">
-        <v>29.28749751309084</v>
+        <v>42.82187136383736</v>
       </c>
     </row>
     <row r="10">
@@ -2447,13 +2447,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>2.704714925199962</v>
+        <v>1.70824100538945</v>
       </c>
       <c r="C10" t="n">
-        <v>43.70249905454677</v>
+        <v>42.13661146627311</v>
       </c>
       <c r="D10" t="n">
-        <v>30.17892442854695</v>
+        <v>35.01894061048373</v>
       </c>
     </row>
     <row r="11">
@@ -2461,13 +2461,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>1.599267010218054</v>
+        <v>0.7107853378746906</v>
       </c>
       <c r="C11" t="n">
-        <v>32.87382187670443</v>
+        <v>32.16303653882975</v>
       </c>
       <c r="D11" t="n">
-        <v>30.20837685967435</v>
+        <v>33.40691088011046</v>
       </c>
     </row>
     <row r="12">
@@ -2475,13 +2475,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>1.084831213192725</v>
+        <v>0.4339324852770902</v>
       </c>
       <c r="C12" t="n">
-        <v>24.95111790343269</v>
+        <v>26.25291535926396</v>
       </c>
       <c r="D12" t="n">
-        <v>28.8565102709265</v>
+        <v>30.15830772675777</v>
       </c>
     </row>
     <row r="13">
@@ -2492,10 +2492,10 @@
         <v>0.2601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>18.99190933865455</v>
+        <v>20.03256190515617</v>
       </c>
       <c r="D13" t="n">
-        <v>26.79680358741669</v>
+        <v>24.97566159603886</v>
       </c>
     </row>
     <row r="14">
@@ -2503,13 +2503,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>0.921861094287755</v>
       </c>
       <c r="C14" t="n">
-        <v>15.97892563432109</v>
+        <v>20.58823110575986</v>
       </c>
       <c r="D14" t="n">
-        <v>19.0517959486136</v>
+        <v>16.90078672860884</v>
       </c>
     </row>
     <row r="15">
@@ -2517,13 +2517,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>2.866703296400686</v>
       </c>
       <c r="C15" t="n">
-        <v>15.40853021815369</v>
+        <v>31.89207417245764</v>
       </c>
       <c r="D15" t="n">
-        <v>17.20021977840412</v>
+        <v>10.39179944945249</v>
       </c>
     </row>
     <row r="16">
@@ -2534,10 +2534,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>14.46605242207675</v>
+        <v>41.33157834879071</v>
       </c>
       <c r="D16" t="n">
-        <v>14.87936820556466</v>
+        <v>3.306526267903257</v>
       </c>
     </row>
     <row r="17">
@@ -2548,10 +2548,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>14.63884001802419</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>10.86107485208246</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2559,13 +2559,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>3.21031499288707</v>
+        <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>35.31346492175777</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>6.955682484588652</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2576,10 +2576,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>34.9050578767911</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>3.610868056219768</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.528000338435537</v>
+        <v>0.321031499288707</v>
       </c>
       <c r="C2" t="n">
-        <v>4.890085314853362</v>
+        <v>5.116869034534376</v>
       </c>
       <c r="D2" t="n">
-        <v>12.30326222962103</v>
+        <v>9.108655200001905</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>16.59644494029233</v>
+        <v>2.886338250485623</v>
       </c>
       <c r="C3" t="n">
-        <v>36.24121650227101</v>
+        <v>29.07936699979052</v>
       </c>
       <c r="D3" t="n">
-        <v>67.34298377280996</v>
+        <v>68.84505776030758</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>36.782159487311</v>
+        <v>14.15385665212627</v>
       </c>
       <c r="C4" t="n">
-        <v>122.037130124104</v>
+        <v>90.11756701592746</v>
       </c>
       <c r="D4" t="n">
-        <v>133.4087137823948</v>
+        <v>171.428857124761</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>36.54555829058752</v>
+        <v>15.04528356758237</v>
       </c>
       <c r="C5" t="n">
-        <v>242.5162266415684</v>
+        <v>201.3564541410209</v>
       </c>
       <c r="D5" t="n">
-        <v>111.3056459689821</v>
+        <v>159.3131087066512</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>27.37112599440108</v>
+        <v>8.734609324683873</v>
       </c>
       <c r="C6" t="n">
-        <v>225.6507828303124</v>
+        <v>207.4167827193364</v>
       </c>
       <c r="D6" t="n">
-        <v>53.93721887131977</v>
+        <v>82.55614619781855</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>7.306166415004762</v>
+        <v>3.952516257297658</v>
       </c>
       <c r="C7" t="n">
-        <v>185.3490578232766</v>
+        <v>101.2682574407627</v>
       </c>
       <c r="D7" t="n">
-        <v>35.03366682604743</v>
+        <v>37.42913122440964</v>
       </c>
     </row>
     <row r="8">
@@ -2730,13 +2730,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>3.922082078466008</v>
+        <v>2.253110981246429</v>
       </c>
       <c r="C8" t="n">
-        <v>101.8906854852552</v>
+        <v>50.40292713603124</v>
       </c>
       <c r="D8" t="n">
-        <v>31.29320807286708</v>
+        <v>31.54355373745002</v>
       </c>
     </row>
     <row r="9">
@@ -2744,13 +2744,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.885937339858122</v>
+        <v>1.220312396378785</v>
       </c>
       <c r="C9" t="n">
-        <v>33.28124717396686</v>
+        <v>32.17187226816797</v>
       </c>
       <c r="D9" t="n">
-        <v>31.61718481526852</v>
+        <v>26.73593522975338</v>
       </c>
     </row>
     <row r="10">
@@ -2758,13 +2758,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.1388273369263</v>
+        <v>0.4270602513473625</v>
       </c>
       <c r="C10" t="n">
-        <v>25.76596849795754</v>
+        <v>25.19655482949439</v>
       </c>
       <c r="D10" t="n">
-        <v>23.63066724122073</v>
+        <v>26.1930287493049</v>
       </c>
     </row>
     <row r="11">
@@ -2772,13 +2772,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>0.7107853378746906</v>
+        <v>0.1776963344686726</v>
       </c>
       <c r="C11" t="n">
-        <v>19.90198946049134</v>
+        <v>20.96816746730337</v>
       </c>
       <c r="D11" t="n">
-        <v>23.10052348092744</v>
+        <v>24.16670148773948</v>
       </c>
     </row>
     <row r="12">
@@ -2789,10 +2789,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>15.4046032273367</v>
+        <v>16.27246819789088</v>
       </c>
       <c r="D12" t="n">
-        <v>21.69662426385451</v>
+        <v>20.39482680802324</v>
       </c>
     </row>
     <row r="13">
@@ -2800,13 +2800,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>0.5203262832508095</v>
       </c>
       <c r="C13" t="n">
-        <v>13.00815708127024</v>
+        <v>16.91060420565131</v>
       </c>
       <c r="D13" t="n">
-        <v>15.60978849752428</v>
+        <v>13.78864650614645</v>
       </c>
     </row>
     <row r="14">
@@ -2814,13 +2814,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>2.151009220004762</v>
       </c>
       <c r="C14" t="n">
-        <v>12.90605532002857</v>
+        <v>26.73397173434489</v>
       </c>
       <c r="D14" t="n">
-        <v>14.44249047717483</v>
+        <v>8.604036880019047</v>
       </c>
     </row>
     <row r="15">
@@ -2831,10 +2831,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>12.18348900970292</v>
+        <v>35.1171153809084</v>
       </c>
       <c r="D15" t="n">
-        <v>12.541826921753</v>
+        <v>2.5083653843506</v>
       </c>
     </row>
     <row r="16">
@@ -2845,10 +2845,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>12.39947350463721</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>9.092947236733956</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -2856,13 +2856,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2.361103228713579</v>
+        <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>30.22212132753381</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>5.66664774891259</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2873,10 +2873,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>29.96293993361265</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>2.675262494072558</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.291800052339555</v>
+        <v>0.170824100538945</v>
       </c>
       <c r="C2" t="n">
-        <v>9.229410167624264</v>
+        <v>3.114103717870883</v>
       </c>
       <c r="D2" t="n">
-        <v>14.01346673041897</v>
+        <v>7.723409189309657</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>12.80689880189964</v>
+        <v>2.002765316663493</v>
       </c>
       <c r="C3" t="n">
-        <v>27.67546778271759</v>
+        <v>24.16571974003524</v>
       </c>
       <c r="D3" t="n">
-        <v>62.17899084847173</v>
+        <v>60.55419839794327</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>34.33171721751096</v>
+        <v>9.342311153612647</v>
       </c>
       <c r="C4" t="n">
-        <v>107.8449853115121</v>
+        <v>78.55454255530854</v>
       </c>
       <c r="D4" t="n">
-        <v>135.744291570798</v>
+        <v>160.7719857951619</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>44.37499623195583</v>
+        <v>14.25988540418492</v>
       </c>
       <c r="C5" t="n">
-        <v>234.0731963850458</v>
+        <v>165.3017697025567</v>
       </c>
       <c r="D5" t="n">
-        <v>128.8298424897877</v>
+        <v>165.5472066286184</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>35.86422538384024</v>
+        <v>8.613854357061516</v>
       </c>
       <c r="C6" t="n">
-        <v>299.0698031447059</v>
+        <v>214.1790609061884</v>
       </c>
       <c r="D6" t="n">
-        <v>71.04417261782045</v>
+        <v>90.16370915802707</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>15.15131231964102</v>
+        <v>3.233876937788993</v>
       </c>
       <c r="C7" t="n">
-        <v>244.5170284628233</v>
+        <v>134.6250991879566</v>
       </c>
       <c r="D7" t="n">
-        <v>39.94436884268997</v>
+        <v>37.96811071404115</v>
       </c>
     </row>
     <row r="8">
@@ -3041,13 +3041,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>4.923464736797754</v>
+        <v>1.168279768053704</v>
       </c>
       <c r="C8" t="n">
-        <v>158.9694970101648</v>
+        <v>55.40984042768998</v>
       </c>
       <c r="D8" t="n">
-        <v>33.12907627980861</v>
+        <v>27.28767743954009</v>
       </c>
     </row>
     <row r="9">
@@ -3055,13 +3055,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>2.218749811597791</v>
+        <v>0.4437499623195582</v>
       </c>
       <c r="C9" t="n">
-        <v>66.22968187619405</v>
+        <v>28.84374755077128</v>
       </c>
       <c r="D9" t="n">
-        <v>32.39374724932775</v>
+        <v>21.1890607007589</v>
       </c>
     </row>
     <row r="10">
@@ -3069,13 +3069,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.1388273369263</v>
+        <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>31.17539834835747</v>
+        <v>18.2212373908208</v>
       </c>
       <c r="D10" t="n">
-        <v>24.91184799526281</v>
+        <v>19.92947839621025</v>
       </c>
     </row>
     <row r="11">
@@ -3083,13 +3083,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>0.5330890034060179</v>
+        <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>23.27821981539612</v>
+        <v>13.32722508515045</v>
       </c>
       <c r="D11" t="n">
-        <v>23.81130881880213</v>
+        <v>17.59193711239859</v>
       </c>
     </row>
     <row r="12">
@@ -3100,10 +3100,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>17.57426565372215</v>
+        <v>11.49921085984289</v>
       </c>
       <c r="D12" t="n">
-        <v>21.91359050649305</v>
+        <v>13.4519070435898</v>
       </c>
     </row>
     <row r="13">
@@ -3111,13 +3111,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>0.5203262832508095</v>
       </c>
       <c r="C13" t="n">
-        <v>15.08946221427348</v>
+        <v>13.78864650614645</v>
       </c>
       <c r="D13" t="n">
-        <v>15.60978849752428</v>
+        <v>8.065057390387548</v>
       </c>
     </row>
     <row r="14">
@@ -3128,10 +3128,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>13.52062938288707</v>
+        <v>16.59349969717959</v>
       </c>
       <c r="D14" t="n">
-        <v>14.13520344574558</v>
+        <v>2.765583282863265</v>
       </c>
     </row>
     <row r="15">
@@ -3142,10 +3142,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>13.25850274585317</v>
+        <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>11.82515109765283</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -3153,13 +3153,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.653263133951629</v>
+        <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>23.97231544229862</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>8.266315669758143</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3170,10 +3170,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>34.47210713921825</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>4.249985811684442</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -3184,10 +3184,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>0.5350524988145117</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>1.070104997629023</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.219731559302038</v>
+        <v>0.3279037332184347</v>
       </c>
       <c r="C2" t="n">
-        <v>6.31558298141973</v>
+        <v>5.464407721837746</v>
       </c>
       <c r="D2" t="n">
-        <v>10.71773968726243</v>
+        <v>7.745007638803087</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>12.22275891787279</v>
+        <v>1.232093368829747</v>
       </c>
       <c r="C3" t="n">
-        <v>31.54846247597125</v>
+        <v>17.07259257685203</v>
       </c>
       <c r="D3" t="n">
-        <v>59.77861771158828</v>
+        <v>52.95547116707295</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>31.33247798103695</v>
+        <v>6.53451271946677</v>
       </c>
       <c r="C4" t="n">
-        <v>94.57175635009524</v>
+        <v>68.30607827067608</v>
       </c>
       <c r="D4" t="n">
-        <v>136.1526986157647</v>
+        <v>155.271253408267</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>48.30198704894308</v>
+        <v>14.50532233024663</v>
       </c>
       <c r="C5" t="n">
-        <v>228.9681083229624</v>
+        <v>155.9260791269997</v>
       </c>
       <c r="D5" t="n">
-        <v>141.3471257189345</v>
+        <v>185.3294228691917</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>41.37870223859457</v>
+        <v>13.76606630894878</v>
       </c>
       <c r="C6" t="n">
-        <v>336.222081516518</v>
+        <v>240.2621339126177</v>
       </c>
       <c r="D6" t="n">
-        <v>82.35488791844796</v>
+        <v>118.500874893407</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>13.59426046070558</v>
+        <v>6.407867265618931</v>
       </c>
       <c r="C7" t="n">
-        <v>306.3200099405685</v>
+        <v>226.0120659854752</v>
       </c>
       <c r="D7" t="n">
-        <v>44.6155244194963</v>
+        <v>52.64033015400972</v>
       </c>
     </row>
     <row r="8">
@@ -3352,13 +3352,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>4.005530633326986</v>
+        <v>2.169662426385451</v>
       </c>
       <c r="C8" t="n">
-        <v>200.7772229955152</v>
+        <v>116.7445282505095</v>
       </c>
       <c r="D8" t="n">
-        <v>34.38080460272329</v>
+        <v>30.70906818884022</v>
       </c>
     </row>
     <row r="9">
@@ -3366,13 +3366,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.664062358698343</v>
+        <v>0.6656249434793372</v>
       </c>
       <c r="C9" t="n">
-        <v>72.66405632982764</v>
+        <v>48.36874589283183</v>
       </c>
       <c r="D9" t="n">
-        <v>31.94999728700819</v>
+        <v>22.96406055003713</v>
       </c>
     </row>
     <row r="10">
@@ -3380,13 +3380,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0.5694136684631501</v>
+        <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>31.8871654339364</v>
+        <v>25.90832191507333</v>
       </c>
       <c r="D10" t="n">
-        <v>25.62361508084176</v>
+        <v>20.64124548178919</v>
       </c>
     </row>
     <row r="11">
@@ -3397,10 +3397,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>22.7451308119901</v>
+        <v>17.05884810899257</v>
       </c>
       <c r="D11" t="n">
-        <v>24.16670148773948</v>
+        <v>18.30272245027328</v>
       </c>
     </row>
     <row r="12">
@@ -3411,10 +3411,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>16.48943444052943</v>
+        <v>13.23494080095125</v>
       </c>
       <c r="D12" t="n">
-        <v>19.96089432274615</v>
+        <v>14.10280577150543</v>
       </c>
     </row>
     <row r="13">
@@ -3422,13 +3422,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>0.2601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>11.18701508989241</v>
+        <v>14.04880964777186</v>
       </c>
       <c r="D13" t="n">
-        <v>16.1301147807751</v>
+        <v>8.585383673638358</v>
       </c>
     </row>
     <row r="14">
@@ -3439,10 +3439,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>11.06233313145306</v>
+        <v>16.90078672860884</v>
       </c>
       <c r="D14" t="n">
-        <v>11.06233313145306</v>
+        <v>3.072870314292517</v>
       </c>
     </row>
     <row r="15">
@@ -3450,13 +3450,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.075013736150257</v>
+        <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>20.0669230748048</v>
+        <v>3.583379120500858</v>
       </c>
       <c r="D15" t="n">
-        <v>6.808420328951629</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -3467,10 +3467,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>29.34542062764141</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>3.306526267903257</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3484,7 +3484,7 @@
         <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>0.4722206457427158</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.353249247079604</v>
+        <v>0.2532909076956771</v>
       </c>
       <c r="C2" t="n">
-        <v>9.94510424402019</v>
+        <v>8.053276417936585</v>
       </c>
       <c r="D2" t="n">
-        <v>17.57622914913065</v>
+        <v>13.30268139254428</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>9.979465413668827</v>
+        <v>1.173188506574938</v>
       </c>
       <c r="C3" t="n">
-        <v>28.4265047764664</v>
+        <v>19.44842202112931</v>
       </c>
       <c r="D3" t="n">
-        <v>55.78290455530377</v>
+        <v>47.26133448244146</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>27.35050929261189</v>
+        <v>4.390375733391735</v>
       </c>
       <c r="C4" t="n">
-        <v>87.53949754457535</v>
+        <v>54.2798488201019</v>
       </c>
       <c r="D4" t="n">
-        <v>133.2938493009979</v>
+        <v>147.5115195539003</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>47.66385104118265</v>
+        <v>12.51728322914684</v>
       </c>
       <c r="C5" t="n">
-        <v>206.1179305066179</v>
+        <v>140.6353586333556</v>
       </c>
       <c r="D5" t="n">
-        <v>153.226272940321</v>
+        <v>198.1657741022187</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>49.83154997215961</v>
+        <v>16.66418553188536</v>
       </c>
       <c r="C6" t="n">
-        <v>347.8548100641384</v>
+        <v>245.0520809616379</v>
       </c>
       <c r="D6" t="n">
-        <v>99.94486153543805</v>
+        <v>144.2216829969692</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>24.852943133008</v>
+        <v>10.95924962250714</v>
       </c>
       <c r="C7" t="n">
-        <v>374.5907452938917</v>
+        <v>286.4376554341621</v>
       </c>
       <c r="D7" t="n">
-        <v>53.29908286355933</v>
+        <v>71.44472568115313</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>7.093127163183205</v>
+        <v>4.255876297909922</v>
       </c>
       <c r="C8" t="n">
-        <v>275.9643709252571</v>
+        <v>204.0317166350934</v>
       </c>
       <c r="D8" t="n">
-        <v>36.96770980341364</v>
+        <v>36.63391558396972</v>
       </c>
     </row>
     <row r="9">
@@ -3677,13 +3677,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>2.218749811597791</v>
+        <v>1.331249886958674</v>
       </c>
       <c r="C9" t="n">
-        <v>134.2343636016663</v>
+        <v>93.2984295776871</v>
       </c>
       <c r="D9" t="n">
-        <v>32.9484347022272</v>
+        <v>24.84999788989526</v>
       </c>
     </row>
     <row r="10">
@@ -3691,13 +3691,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0.7117670855789376</v>
+        <v>0.1423534171157875</v>
       </c>
       <c r="C10" t="n">
-        <v>49.53898915629405</v>
+        <v>40.28601704376787</v>
       </c>
       <c r="D10" t="n">
-        <v>26.90479583488384</v>
+        <v>21.6377194015997</v>
       </c>
     </row>
     <row r="11">
@@ -3708,10 +3708,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>27.36523550817559</v>
+        <v>22.7451308119901</v>
       </c>
       <c r="D11" t="n">
-        <v>24.34439782220815</v>
+        <v>19.01350778814797</v>
       </c>
     </row>
     <row r="12">
@@ -3722,10 +3722,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>19.09302935219197</v>
+        <v>15.83853571261379</v>
       </c>
       <c r="D12" t="n">
-        <v>20.39482680802324</v>
+        <v>14.75370449942107</v>
       </c>
     </row>
     <row r="13">
@@ -3736,10 +3736,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>12.74799393964483</v>
+        <v>14.56913593102267</v>
       </c>
       <c r="D13" t="n">
-        <v>16.3902779224005</v>
+        <v>9.105709956889166</v>
       </c>
     </row>
     <row r="14">
@@ -3750,10 +3750,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>11.67690719431156</v>
+        <v>16.59349969717959</v>
       </c>
       <c r="D14" t="n">
-        <v>11.06233313145306</v>
+        <v>3.68744437715102</v>
       </c>
     </row>
     <row r="15">
@@ -3761,13 +3761,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0.7166758241001715</v>
+        <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>21.14193681095506</v>
+        <v>8.241771977151972</v>
       </c>
       <c r="D15" t="n">
-        <v>6.450082416901544</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -3778,10 +3778,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>27.69215749368978</v>
+        <v>0.8266315669758143</v>
       </c>
       <c r="D16" t="n">
-        <v>2.89321048441535</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.625013434706723</v>
+        <v>2.092104357749953</v>
       </c>
       <c r="C2" t="n">
-        <v>8.541205026947251</v>
+        <v>4.641703145678919</v>
       </c>
       <c r="D2" t="n">
-        <v>15.27108553955914</v>
+        <v>18.10146417090269</v>
       </c>
     </row>
     <row r="3">
@@ -3904,13 +3904,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>0.06872233929727672</v>
+        <v>0.07363107781851078</v>
       </c>
       <c r="C3" t="n">
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>4.138066573400306</v>
+        <v>4.196971435655114</v>
       </c>
     </row>
     <row r="4">
@@ -3918,13 +3918,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2.233476027161494</v>
+        <v>2.616357631817749</v>
       </c>
       <c r="C4" t="n">
-        <v>3.994731408580271</v>
+        <v>4.390375733391735</v>
       </c>
       <c r="D4" t="n">
-        <v>23.03670988015141</v>
+        <v>24.32574461582747</v>
       </c>
     </row>
     <row r="5">
@@ -3932,13 +3932,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>6.111379458936396</v>
+        <v>7.706719478337463</v>
       </c>
       <c r="C5" t="n">
-        <v>12.64000169217769</v>
+        <v>14.38260386721577</v>
       </c>
       <c r="D5" t="n">
-        <v>25.47635292520474</v>
+        <v>27.95526587842793</v>
       </c>
     </row>
     <row r="6">
@@ -3946,13 +3946,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>7.3258013690897</v>
+        <v>10.2641722479004</v>
       </c>
       <c r="C6" t="n">
-        <v>15.8994040702771</v>
+        <v>19.64280806657019</v>
       </c>
       <c r="D6" t="n">
-        <v>31.27553661419064</v>
+        <v>36.14598697495907</v>
       </c>
     </row>
     <row r="7">
@@ -3960,13 +3960,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>7.72537268471815</v>
+        <v>12.0970952117292</v>
       </c>
       <c r="C7" t="n">
-        <v>17.54677671800324</v>
+        <v>23.2360046641135</v>
       </c>
       <c r="D7" t="n">
-        <v>29.70375853969149</v>
+        <v>35.69241953559704</v>
       </c>
     </row>
     <row r="8">
@@ -3974,13 +3974,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>8.261406931236909</v>
+        <v>14.26970288122739</v>
       </c>
       <c r="C8" t="n">
-        <v>18.52557917913731</v>
+        <v>25.61870634232051</v>
       </c>
       <c r="D8" t="n">
-        <v>35.04839304161113</v>
+        <v>44.31118263117978</v>
       </c>
     </row>
     <row r="9">
@@ -3988,13 +3988,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>8.320311793491715</v>
+        <v>15.08749871886498</v>
       </c>
       <c r="C9" t="n">
-        <v>20.74531073843935</v>
+        <v>30.7296848906294</v>
       </c>
       <c r="D9" t="n">
-        <v>38.71718421238145</v>
+        <v>49.36718330805084</v>
       </c>
     </row>
     <row r="10">
@@ -4002,13 +4002,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>7.544731107136738</v>
+        <v>14.94710879715769</v>
       </c>
       <c r="C10" t="n">
-        <v>24.62714116103124</v>
+        <v>37.72365553568369</v>
       </c>
       <c r="D10" t="n">
-        <v>51.53193699591508</v>
+        <v>69.04140730115694</v>
       </c>
     </row>
     <row r="11">
@@ -4016,13 +4016,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>6.04167537193487</v>
+        <v>12.61643974727576</v>
       </c>
       <c r="C11" t="n">
-        <v>24.34439782220815</v>
+        <v>38.20471191076462</v>
       </c>
       <c r="D11" t="n">
-        <v>43.5356019448248</v>
+        <v>58.10670137125595</v>
       </c>
     </row>
     <row r="12">
@@ -4030,13 +4030,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>5.207189823325082</v>
+        <v>11.28224461720434</v>
       </c>
       <c r="C12" t="n">
-        <v>22.56448923440869</v>
+        <v>36.66729500591412</v>
       </c>
       <c r="D12" t="n">
-        <v>42.52538355715483</v>
+        <v>59.44875048296136</v>
       </c>
     </row>
     <row r="13">
@@ -4044,13 +4044,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>4.682936549257286</v>
+        <v>10.926851948267</v>
       </c>
       <c r="C13" t="n">
-        <v>21.853703896534</v>
+        <v>36.94316611080748</v>
       </c>
       <c r="D13" t="n">
-        <v>43.70740779306801</v>
+        <v>60.87817514034472</v>
       </c>
     </row>
     <row r="14">
@@ -4058,13 +4058,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>4.916592502868027</v>
+        <v>11.67690719431156</v>
       </c>
       <c r="C14" t="n">
-        <v>23.04652735719387</v>
+        <v>39.33274002294421</v>
       </c>
       <c r="D14" t="n">
-        <v>44.55661955724149</v>
+        <v>63.60841550585509</v>
       </c>
     </row>
     <row r="15">
@@ -4072,13 +4072,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>5.733406592801372</v>
+        <v>13.61684065790326</v>
       </c>
       <c r="C15" t="n">
-        <v>25.80032966760617</v>
+        <v>45.50891483036089</v>
       </c>
       <c r="D15" t="n">
-        <v>41.92553570986004</v>
+        <v>61.27578296056467</v>
       </c>
     </row>
     <row r="16">
@@ -4086,13 +4086,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>6.199736752318607</v>
+        <v>14.87936820556466</v>
       </c>
       <c r="C16" t="n">
-        <v>28.9321048441535</v>
+        <v>51.25115715250048</v>
       </c>
       <c r="D16" t="n">
-        <v>40.09163099832699</v>
+        <v>57.864209688307</v>
       </c>
     </row>
     <row r="17">
@@ -4100,13 +4100,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>6.611089040398022</v>
+        <v>16.99994324673777</v>
       </c>
       <c r="C17" t="n">
-        <v>31.16656261901925</v>
+        <v>56.19425684338318</v>
       </c>
       <c r="D17" t="n">
-        <v>35.8887690764464</v>
+        <v>53.8331536146696</v>
       </c>
     </row>
     <row r="18">
@@ -4114,13 +4114,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>6.955682484588652</v>
+        <v>18.1917849596934</v>
       </c>
       <c r="C18" t="n">
-        <v>33.70830742531424</v>
+        <v>62.06608986248335</v>
       </c>
       <c r="D18" t="n">
-        <v>30.49799243242716</v>
+        <v>45.47946239923349</v>
       </c>
     </row>
     <row r="19">
@@ -4128,13 +4128,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>7.823547455142832</v>
+        <v>20.46158565191202</v>
       </c>
       <c r="C19" t="n">
-        <v>36.10868056219768</v>
+        <v>66.80105904006572</v>
       </c>
       <c r="D19" t="n">
-        <v>22.8688310227252</v>
+        <v>34.9050578767911</v>
       </c>
     </row>
     <row r="20">
@@ -4142,13 +4142,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>7.397468951499714</v>
+        <v>20.84741249968101</v>
       </c>
       <c r="C20" t="n">
-        <v>39.00483628972577</v>
+        <v>73.30219233758808</v>
       </c>
       <c r="D20" t="n">
-        <v>13.4499435481813</v>
+        <v>20.17491532227195</v>
       </c>
     </row>
     <row r="21">
@@ -4156,13 +4156,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>11.44977350273866</v>
+        <v>27.41820207255788</v>
       </c>
       <c r="C21" t="n">
-        <v>54.95891281314559</v>
+        <v>99.77179087514119</v>
       </c>
       <c r="D21" t="n">
-        <v>0.763318233515911</v>
+        <v>0.761616724237719</v>
       </c>
     </row>
   </sheetData>
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>1.720021977840412</v>
+        <v>0.2424916829489621</v>
       </c>
       <c r="C2" t="n">
-        <v>5.886559234663874</v>
+        <v>18.28603273930109</v>
       </c>
       <c r="D2" t="n">
-        <v>13.07589767286327</v>
+        <v>16.47961696348696</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>12.84125997154828</v>
+        <v>1.011200135374215</v>
       </c>
       <c r="C3" t="n">
-        <v>35.76997760423254</v>
+        <v>25.35363446217388</v>
       </c>
       <c r="D3" t="n">
-        <v>62.40970155896974</v>
+        <v>46.62319847468103</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>36.88426124855267</v>
+        <v>3.331069960509427</v>
       </c>
       <c r="C4" t="n">
-        <v>123.8494363861436</v>
+        <v>50.94877885959247</v>
       </c>
       <c r="D4" t="n">
-        <v>136.8418855041459</v>
+        <v>137.824614956097</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>28.49522711576368</v>
+        <v>10.01382658331747</v>
       </c>
       <c r="C5" t="n">
-        <v>301.0283898146783</v>
+        <v>121.6876279413922</v>
       </c>
       <c r="D5" t="n">
-        <v>140.7580770963865</v>
+        <v>205.2589012654019</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>15.41638419978766</v>
+        <v>17.02645043475243</v>
       </c>
       <c r="C6" t="n">
-        <v>308.0861740605086</v>
+        <v>234.3048888432481</v>
       </c>
       <c r="D6" t="n">
-        <v>78.85299385739957</v>
+        <v>168.3324248655666</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>4.671155576806323</v>
+        <v>14.67221943996858</v>
       </c>
       <c r="C7" t="n">
-        <v>194.0326162673396</v>
+        <v>319.2555176917245</v>
       </c>
       <c r="D7" t="n">
-        <v>32.21899615797182</v>
+        <v>89.65025510870598</v>
       </c>
     </row>
     <row r="8">
@@ -4285,13 +4285,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>1.50207398749762</v>
+        <v>7.42692138262712</v>
       </c>
       <c r="C8" t="n">
-        <v>98.88653751025997</v>
+        <v>282.3064610946915</v>
       </c>
       <c r="D8" t="n">
-        <v>24.28352946454485</v>
+        <v>44.81187396034566</v>
       </c>
     </row>
     <row r="9">
@@ -4299,13 +4299,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>0.4437499623195582</v>
+        <v>2.440624792757569</v>
       </c>
       <c r="C9" t="n">
-        <v>37.82968428774233</v>
+        <v>160.3046738879404</v>
       </c>
       <c r="D9" t="n">
-        <v>20.52343575727956</v>
+        <v>27.29062268265283</v>
       </c>
     </row>
     <row r="10">
@@ -4313,13 +4313,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0</v>
+        <v>0.5694136684631501</v>
       </c>
       <c r="C10" t="n">
-        <v>21.35301256736813</v>
+        <v>69.75317438673588</v>
       </c>
       <c r="D10" t="n">
-        <v>19.07535789351553</v>
+        <v>22.63419332141022</v>
       </c>
     </row>
     <row r="11">
@@ -4330,10 +4330,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>15.28188476430585</v>
+        <v>32.16303653882975</v>
       </c>
       <c r="D11" t="n">
-        <v>16.34806277111788</v>
+        <v>19.54659679155399</v>
       </c>
     </row>
     <row r="12">
@@ -4344,10 +4344,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>10.41437964665016</v>
+        <v>19.7439280801076</v>
       </c>
       <c r="D12" t="n">
-        <v>13.23494080095125</v>
+        <v>15.4046032273367</v>
       </c>
     </row>
     <row r="13">
@@ -4358,10 +4358,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>9.626036240139976</v>
+        <v>15.86995163914969</v>
       </c>
       <c r="D13" t="n">
-        <v>9.105709956889166</v>
+        <v>9.886199381765381</v>
       </c>
     </row>
     <row r="14">
@@ -4369,13 +4369,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0.3072870314292517</v>
+        <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>17.51536079146734</v>
+        <v>16.59349969717959</v>
       </c>
       <c r="D14" t="n">
-        <v>5.223879534297279</v>
+        <v>4.302018440009523</v>
       </c>
     </row>
     <row r="15">
@@ -4386,10 +4386,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>23.29196428325557</v>
+        <v>11.10847527355266</v>
       </c>
       <c r="D15" t="n">
-        <v>2.150027472300515</v>
+        <v>0.3583379120500857</v>
       </c>
     </row>
     <row r="16">
@@ -4400,7 +4400,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>0</v>
+        <v>2.89321048441535</v>
       </c>
       <c r="D16" t="n">
         <v>0</v>
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.884595739255381</v>
+        <v>3.424335992412874</v>
       </c>
       <c r="C2" t="n">
-        <v>7.638978886744431</v>
+        <v>5.943500601510189</v>
       </c>
       <c r="D2" t="n">
-        <v>15.79828405673967</v>
+        <v>36.25103397931347</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>9.832203258031806</v>
+        <v>3.470478134512474</v>
       </c>
       <c r="C3" t="n">
-        <v>21.51990967709008</v>
+        <v>9.164614819143976</v>
       </c>
       <c r="D3" t="n">
-        <v>15.96321767105314</v>
+        <v>15.32017292477148</v>
       </c>
     </row>
     <row r="4">
@@ -4540,13 +4540,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1.008254892261474</v>
+        <v>0.9189158511750145</v>
       </c>
       <c r="C4" t="n">
-        <v>1.493238258159399</v>
+        <v>1.710204500797944</v>
       </c>
       <c r="D4" t="n">
-        <v>19.62906359871073</v>
+        <v>18.45489334443154</v>
       </c>
     </row>
     <row r="5">
@@ -4554,13 +4554,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>4.736932672990861</v>
+        <v>3.632466505713199</v>
       </c>
       <c r="C5" t="n">
-        <v>9.449321653375552</v>
+        <v>8.197593330460869</v>
       </c>
       <c r="D5" t="n">
-        <v>28.49522711576368</v>
+        <v>24.20008090968388</v>
       </c>
     </row>
     <row r="6">
@@ -4568,13 +4568,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>8.050331174823848</v>
+        <v>5.75598678999905</v>
       </c>
       <c r="C6" t="n">
-        <v>18.27425176685013</v>
+        <v>14.49059611468292</v>
       </c>
       <c r="D6" t="n">
-        <v>32.8453511932813</v>
+        <v>28.6591789823729</v>
       </c>
     </row>
     <row r="7">
@@ -4582,13 +4582,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>8.683558444063037</v>
+        <v>6.108434215823654</v>
       </c>
       <c r="C7" t="n">
-        <v>20.9603134856694</v>
+        <v>16.58859095865835</v>
       </c>
       <c r="D7" t="n">
-        <v>32.21899615797182</v>
+        <v>27.90716024091983</v>
       </c>
     </row>
     <row r="8">
@@ -4596,13 +4596,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>8.762098260402782</v>
+        <v>6.508987279156353</v>
       </c>
       <c r="C8" t="n">
-        <v>21.69662426385451</v>
+        <v>17.19040230136165</v>
       </c>
       <c r="D8" t="n">
-        <v>35.79943003535994</v>
+        <v>32.04424506661589</v>
       </c>
     </row>
     <row r="9">
@@ -4610,13 +4610,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>8.874999246391162</v>
+        <v>6.656249434793372</v>
       </c>
       <c r="C9" t="n">
-        <v>22.74218556887735</v>
+        <v>18.74843590800133</v>
       </c>
       <c r="D9" t="n">
-        <v>39.2718716652809</v>
+        <v>34.72343455150543</v>
       </c>
     </row>
     <row r="10">
@@ -4624,13 +4624,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8.256498192715677</v>
+        <v>6.26355035309465</v>
       </c>
       <c r="C10" t="n">
-        <v>25.62361508084176</v>
+        <v>21.78007281871549</v>
       </c>
       <c r="D10" t="n">
-        <v>50.67781649322036</v>
+        <v>46.12250714551515</v>
       </c>
     </row>
     <row r="11">
@@ -4638,13 +4638,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>6.75246070980956</v>
+        <v>5.330890034060179</v>
       </c>
       <c r="C11" t="n">
-        <v>27.36523550817559</v>
+        <v>22.7451308119901</v>
       </c>
       <c r="D11" t="n">
-        <v>46.37874329632356</v>
+        <v>41.04785326226338</v>
       </c>
     </row>
     <row r="12">
@@ -4652,13 +4652,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>5.641122308602172</v>
+        <v>4.339324852770901</v>
       </c>
       <c r="C12" t="n">
-        <v>25.81898287398687</v>
+        <v>21.69662426385451</v>
       </c>
       <c r="D12" t="n">
-        <v>43.17628228507047</v>
+        <v>39.4878561602152</v>
       </c>
     </row>
     <row r="13">
@@ -4666,13 +4666,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>4.943099690882691</v>
+        <v>3.902447124381071</v>
       </c>
       <c r="C13" t="n">
-        <v>23.93500902953724</v>
+        <v>20.55288818840698</v>
       </c>
       <c r="D13" t="n">
-        <v>44.22773407631881</v>
+        <v>40.06512381031234</v>
       </c>
     </row>
     <row r="14">
@@ -4680,13 +4680,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>4.609305471438775</v>
+        <v>3.994731408580272</v>
       </c>
       <c r="C14" t="n">
-        <v>23.96838845148163</v>
+        <v>21.20280516861837</v>
       </c>
       <c r="D14" t="n">
-        <v>44.86390658867074</v>
+        <v>40.86917518009047</v>
       </c>
     </row>
     <row r="15">
@@ -4694,13 +4694,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>5.375068680751286</v>
+        <v>4.30005494460103</v>
       </c>
       <c r="C15" t="n">
-        <v>26.15866757965626</v>
+        <v>23.29196428325557</v>
       </c>
       <c r="D15" t="n">
-        <v>42.28387362191012</v>
+        <v>39.77550823755952</v>
       </c>
     </row>
     <row r="16">
@@ -4708,13 +4708,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>5.7864209688307</v>
+        <v>4.959789401854886</v>
       </c>
       <c r="C16" t="n">
-        <v>28.9321048441535</v>
+        <v>26.03889435973815</v>
       </c>
       <c r="D16" t="n">
-        <v>40.5049467818149</v>
+        <v>36.78510473042374</v>
       </c>
     </row>
     <row r="17">
@@ -4722,13 +4722,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>6.138868394655306</v>
+        <v>5.194427103169874</v>
       </c>
       <c r="C17" t="n">
-        <v>31.63878326476196</v>
+        <v>28.80545939030567</v>
       </c>
       <c r="D17" t="n">
-        <v>36.36098972218912</v>
+        <v>34.47210713921825</v>
       </c>
     </row>
     <row r="18">
@@ -4736,13 +4736,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>6.42062998577414</v>
+        <v>5.885577486959628</v>
       </c>
       <c r="C18" t="n">
-        <v>34.24335992412875</v>
+        <v>31.03304493124168</v>
       </c>
       <c r="D18" t="n">
-        <v>31.03304493124168</v>
+        <v>28.89283493598363</v>
       </c>
     </row>
     <row r="19">
@@ -4750,13 +4750,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>7.221736112439537</v>
+        <v>6.018113427032947</v>
       </c>
       <c r="C19" t="n">
-        <v>36.71049190490098</v>
+        <v>33.09962384868121</v>
       </c>
       <c r="D19" t="n">
-        <v>23.47064236542849</v>
+        <v>21.66520833731861</v>
       </c>
     </row>
     <row r="20">
@@ -4767,10 +4767,10 @@
         <v>6.724971774090649</v>
       </c>
       <c r="C20" t="n">
-        <v>39.00483628972577</v>
+        <v>36.31484758008951</v>
       </c>
       <c r="D20" t="n">
-        <v>14.12244072559037</v>
+        <v>12.77744637077223</v>
       </c>
     </row>
     <row r="21">
@@ -4778,13 +4778,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>13.39712103272468</v>
+        <v>11.67788443374054</v>
       </c>
       <c r="C21" t="n">
-        <v>70.13786893602918</v>
+        <v>59.9464734265348</v>
       </c>
       <c r="D21" t="n">
-        <v>1.576131886202903</v>
+        <v>0.7785256289160364</v>
       </c>
     </row>
   </sheetData>
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.888702656521616</v>
+        <v>2.77638250760998</v>
       </c>
       <c r="C2" t="n">
-        <v>6.696501090667494</v>
+        <v>6.948810250658924</v>
       </c>
       <c r="D2" t="n">
-        <v>24.78618428911922</v>
+        <v>34.42989198793564</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>16.10557108816893</v>
+        <v>8.752280783360314</v>
       </c>
       <c r="C3" t="n">
-        <v>26.69372007847078</v>
+        <v>18.53048791765854</v>
       </c>
       <c r="D3" t="n">
-        <v>25.37326941625881</v>
+        <v>43.36870483510285</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>11.53749902030852</v>
+        <v>4.518002934943822</v>
       </c>
       <c r="C4" t="n">
-        <v>33.3489877655599</v>
+        <v>15.46841682811274</v>
       </c>
       <c r="D4" t="n">
-        <v>23.43235420496287</v>
+        <v>22.39857387239098</v>
       </c>
     </row>
     <row r="5">
@@ -4865,13 +4865,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>3.067961575771283</v>
+        <v>2.454369260617026</v>
       </c>
       <c r="C5" t="n">
-        <v>5.424156065963628</v>
+        <v>5.129631754689585</v>
       </c>
       <c r="D5" t="n">
-        <v>29.40334374219198</v>
+        <v>25.72178985126644</v>
       </c>
     </row>
     <row r="6">
@@ -4879,13 +4879,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>7.446556336712058</v>
+        <v>5.514476854754335</v>
       </c>
       <c r="C6" t="n">
-        <v>16.50317890838889</v>
+        <v>13.68556299720054</v>
       </c>
       <c r="D6" t="n">
-        <v>34.57617239586842</v>
+        <v>30.06798693796707</v>
       </c>
     </row>
     <row r="7">
@@ -4893,13 +4893,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.462084373530759</v>
+        <v>6.767186925373263</v>
       </c>
       <c r="C7" t="n">
-        <v>24.3139636433765</v>
+        <v>19.40326162673396</v>
       </c>
       <c r="D7" t="n">
-        <v>34.97378021608837</v>
+        <v>30.48228446915921</v>
       </c>
     </row>
     <row r="8">
@@ -4907,13 +4907,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>9.596583809012571</v>
+        <v>6.926230053461247</v>
       </c>
       <c r="C8" t="n">
-        <v>25.61870634232051</v>
+        <v>20.36144738607885</v>
       </c>
       <c r="D8" t="n">
-        <v>36.63391558396972</v>
+        <v>32.96217917008666</v>
       </c>
     </row>
     <row r="9">
@@ -4921,13 +4921,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>9.429686699290611</v>
+        <v>7.09999939711293</v>
       </c>
       <c r="C9" t="n">
-        <v>25.73749781453438</v>
+        <v>20.85624822901923</v>
       </c>
       <c r="D9" t="n">
-        <v>40.27030908049991</v>
+        <v>35.38905949498476</v>
       </c>
     </row>
     <row r="10">
@@ -4935,13 +4935,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8.825911861178826</v>
+        <v>6.690610604442014</v>
       </c>
       <c r="C10" t="n">
-        <v>27.3318560862312</v>
+        <v>22.91890015564179</v>
       </c>
       <c r="D10" t="n">
-        <v>50.1084028247572</v>
+        <v>45.26838664282043</v>
       </c>
     </row>
     <row r="11">
@@ -4949,13 +4949,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>7.640942382152923</v>
+        <v>5.863979037466197</v>
       </c>
       <c r="C11" t="n">
-        <v>29.14219885286231</v>
+        <v>24.87748682561417</v>
       </c>
       <c r="D11" t="n">
-        <v>47.97801030654161</v>
+        <v>43.35790561035613</v>
       </c>
     </row>
     <row r="12">
@@ -4963,13 +4963,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>6.075054793879263</v>
+        <v>4.773257338047991</v>
       </c>
       <c r="C12" t="n">
-        <v>29.29044275620359</v>
+        <v>24.5171854181556</v>
       </c>
       <c r="D12" t="n">
-        <v>44.69504598354028</v>
+        <v>40.57268737340794</v>
       </c>
     </row>
     <row r="13">
@@ -4977,13 +4977,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>5.203262832508096</v>
+        <v>3.902447124381071</v>
       </c>
       <c r="C13" t="n">
-        <v>26.79680358741669</v>
+        <v>22.89435646303562</v>
       </c>
       <c r="D13" t="n">
-        <v>44.74806035956962</v>
+        <v>40.32528695193774</v>
       </c>
     </row>
     <row r="14">
@@ -4991,13 +4991,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>4.609305471438775</v>
+        <v>3.68744437715102</v>
       </c>
       <c r="C14" t="n">
-        <v>25.50482360862789</v>
+        <v>22.43195329433537</v>
       </c>
       <c r="D14" t="n">
-        <v>44.86390658867074</v>
+        <v>41.17646221151972</v>
       </c>
     </row>
     <row r="15">
@@ -5005,13 +5005,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>5.0167307687012</v>
+        <v>3.941717032550943</v>
       </c>
       <c r="C15" t="n">
-        <v>26.51700549170635</v>
+        <v>23.65030219530566</v>
       </c>
       <c r="D15" t="n">
-        <v>43.00054944601029</v>
+        <v>40.1338461496096</v>
       </c>
     </row>
     <row r="16">
@@ -5019,13 +5019,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>5.373105185342793</v>
+        <v>4.546473618366978</v>
       </c>
       <c r="C16" t="n">
-        <v>29.34542062764141</v>
+        <v>26.03889435973815</v>
       </c>
       <c r="D16" t="n">
-        <v>40.5049467818149</v>
+        <v>37.19842051391164</v>
       </c>
     </row>
     <row r="17">
@@ -5033,13 +5033,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>5.66664774891259</v>
+        <v>4.722206457427158</v>
       </c>
       <c r="C17" t="n">
-        <v>31.63878326476196</v>
+        <v>29.27768003604838</v>
       </c>
       <c r="D17" t="n">
-        <v>36.83321036793183</v>
+        <v>34.94432778496098</v>
       </c>
     </row>
     <row r="18">
@@ -5047,13 +5047,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>5.885577486959628</v>
+        <v>5.350524988145117</v>
       </c>
       <c r="C18" t="n">
-        <v>34.77841242294325</v>
+        <v>31.56809743005619</v>
       </c>
       <c r="D18" t="n">
-        <v>31.56809743005619</v>
+        <v>29.42788743479814</v>
       </c>
     </row>
     <row r="19">
@@ -5061,13 +5061,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>6.619924769736241</v>
+        <v>5.416302084329653</v>
       </c>
       <c r="C19" t="n">
-        <v>36.71049190490098</v>
+        <v>33.09962384868121</v>
       </c>
       <c r="D19" t="n">
-        <v>24.07245370813179</v>
+        <v>22.26701968002191</v>
       </c>
     </row>
     <row r="20">
@@ -5078,10 +5078,10 @@
         <v>6.052474596681584</v>
       </c>
       <c r="C20" t="n">
-        <v>39.00483628972577</v>
+        <v>36.31484758008951</v>
       </c>
       <c r="D20" t="n">
-        <v>14.79493790299943</v>
+        <v>13.4499435481813</v>
       </c>
     </row>
     <row r="21">
@@ -5089,13 +5089,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>15.43867705097228</v>
+        <v>13.62755275102031</v>
       </c>
       <c r="C21" t="n">
-        <v>86.13156670542429</v>
+        <v>73.74910900552165</v>
       </c>
       <c r="D21" t="n">
-        <v>3.25024780020469</v>
+        <v>1.603241500120036</v>
       </c>
     </row>
   </sheetData>
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.771874679716245</v>
+        <v>2.435716054236337</v>
       </c>
       <c r="C2" t="n">
-        <v>7.639960634448678</v>
+        <v>5.002986300841745</v>
       </c>
       <c r="D2" t="n">
-        <v>22.00194779987526</v>
+        <v>40.36357511240336</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>14.61822331623501</v>
+        <v>9.35114688295087</v>
       </c>
       <c r="C3" t="n">
-        <v>26.56609287691869</v>
+        <v>23.98900515327081</v>
       </c>
       <c r="D3" t="n">
-        <v>39.31408681656352</v>
+        <v>61.81083545937918</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>22.67935371580556</v>
+        <v>11.99695694589602</v>
       </c>
       <c r="C4" t="n">
-        <v>52.40372895728624</v>
+        <v>34.61249706092554</v>
       </c>
       <c r="D4" t="n">
-        <v>30.88578277560466</v>
+        <v>39.9217886454923</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>10.40652566501619</v>
+        <v>4.859651136021713</v>
       </c>
       <c r="C5" t="n">
-        <v>37.42913122440965</v>
+        <v>19.19316761802515</v>
       </c>
       <c r="D5" t="n">
-        <v>31.07231483941155</v>
+        <v>28.00435326364027</v>
       </c>
     </row>
     <row r="6">
@@ -5190,13 +5190,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>5.957245069369646</v>
+        <v>4.467933802027235</v>
       </c>
       <c r="C6" t="n">
-        <v>12.27675504160637</v>
+        <v>10.54593383901924</v>
       </c>
       <c r="D6" t="n">
-        <v>36.54850353370026</v>
+        <v>31.95981476405067</v>
       </c>
     </row>
     <row r="7">
@@ -5204,13 +5204,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.462084373530759</v>
+        <v>6.94684675525043</v>
       </c>
       <c r="C7" t="n">
-        <v>24.13430381349934</v>
+        <v>19.8823545064064</v>
       </c>
       <c r="D7" t="n">
-        <v>37.4890178343687</v>
+        <v>32.81786225756237</v>
       </c>
     </row>
     <row r="8">
@@ -5218,13 +5218,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.43106935762236</v>
+        <v>7.510369937488099</v>
       </c>
       <c r="C8" t="n">
-        <v>29.79113408536946</v>
+        <v>23.86628669023996</v>
       </c>
       <c r="D8" t="n">
-        <v>37.88564390688441</v>
+        <v>33.96356182841841</v>
       </c>
     </row>
     <row r="9">
@@ -5232,13 +5232,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>9.984374152190059</v>
+        <v>7.432811868852599</v>
       </c>
       <c r="C9" t="n">
-        <v>29.7312474754104</v>
+        <v>23.96249796525614</v>
       </c>
       <c r="D9" t="n">
-        <v>41.15780900513902</v>
+        <v>36.49843440078366</v>
       </c>
     </row>
     <row r="10">
@@ -5246,13 +5246,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>9.395325529641976</v>
+        <v>7.117670855789377</v>
       </c>
       <c r="C10" t="n">
-        <v>29.89421759431538</v>
+        <v>24.76949457814703</v>
       </c>
       <c r="D10" t="n">
-        <v>49.25428232206248</v>
+        <v>44.69897297435728</v>
       </c>
     </row>
     <row r="11">
@@ -5260,13 +5260,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>8.174031385558941</v>
+        <v>6.397068040872215</v>
       </c>
       <c r="C11" t="n">
-        <v>30.91916219754903</v>
+        <v>26.47675383583222</v>
       </c>
       <c r="D11" t="n">
-        <v>49.75497365122833</v>
+        <v>44.42408361716816</v>
       </c>
     </row>
     <row r="12">
@@ -5274,13 +5274,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>6.725953521794898</v>
+        <v>5.207189823325082</v>
       </c>
       <c r="C12" t="n">
-        <v>31.89403766786613</v>
+        <v>27.12078032981814</v>
       </c>
       <c r="D12" t="n">
-        <v>46.2138096820101</v>
+        <v>42.09145107187774</v>
       </c>
     </row>
     <row r="13">
@@ -5288,13 +5288,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>5.463425974133501</v>
+        <v>4.162610266006476</v>
       </c>
       <c r="C13" t="n">
-        <v>30.17892442854696</v>
+        <v>25.49598787928967</v>
       </c>
       <c r="D13" t="n">
-        <v>45.00822350119503</v>
+        <v>41.10577637681396</v>
       </c>
     </row>
     <row r="14">
@@ -5302,13 +5302,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>4.609305471438775</v>
+        <v>3.68744437715102</v>
       </c>
       <c r="C14" t="n">
-        <v>27.9631198600619</v>
+        <v>24.27567548291088</v>
       </c>
       <c r="D14" t="n">
-        <v>45.47848065152925</v>
+        <v>41.48374924294897</v>
       </c>
     </row>
     <row r="15">
@@ -5316,13 +5316,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4.658392856651115</v>
+        <v>3.583379120500858</v>
       </c>
       <c r="C15" t="n">
-        <v>27.23368131580652</v>
+        <v>24.36697801940583</v>
       </c>
       <c r="D15" t="n">
-        <v>43.00054944601029</v>
+        <v>40.1338461496096</v>
       </c>
     </row>
     <row r="16">
@@ -5330,13 +5330,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>4.959789401854886</v>
+        <v>4.133157834879071</v>
       </c>
       <c r="C16" t="n">
-        <v>29.75873641112932</v>
+        <v>26.45221014322606</v>
       </c>
       <c r="D16" t="n">
-        <v>40.91826256530281</v>
+        <v>37.61173629739955</v>
       </c>
     </row>
     <row r="17">
@@ -5344,13 +5344,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>5.194427103169874</v>
+        <v>4.249985811684442</v>
       </c>
       <c r="C17" t="n">
-        <v>32.11100391050468</v>
+        <v>29.27768003604838</v>
       </c>
       <c r="D17" t="n">
-        <v>37.30543101367455</v>
+        <v>35.41654843070368</v>
       </c>
     </row>
     <row r="18">
@@ -5358,13 +5358,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>5.350524988145117</v>
+        <v>4.815472489330605</v>
       </c>
       <c r="C18" t="n">
-        <v>34.77841242294325</v>
+        <v>31.56809743005619</v>
       </c>
       <c r="D18" t="n">
-        <v>31.56809743005619</v>
+        <v>29.42788743479814</v>
       </c>
     </row>
     <row r="19">
@@ -5372,13 +5372,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>6.018113427032947</v>
+        <v>4.814490741626358</v>
       </c>
       <c r="C19" t="n">
-        <v>37.31230324760427</v>
+        <v>33.7014351913845</v>
       </c>
       <c r="D19" t="n">
-        <v>24.67426505083508</v>
+        <v>22.8688310227252</v>
       </c>
     </row>
     <row r="20">
@@ -5389,10 +5389,10 @@
         <v>5.37997741927252</v>
       </c>
       <c r="C20" t="n">
-        <v>39.00483628972577</v>
+        <v>36.31484758008951</v>
       </c>
       <c r="D20" t="n">
-        <v>15.46743508040849</v>
+        <v>14.12244072559037</v>
       </c>
     </row>
     <row r="21">
@@ -5400,13 +5400,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>16.72884648477939</v>
+        <v>14.83669311660686</v>
       </c>
       <c r="C21" t="n">
-        <v>102.0459635571543</v>
+        <v>87.37163724224042</v>
       </c>
       <c r="D21" t="n">
-        <v>4.182211621194847</v>
+        <v>2.472782186101144</v>
       </c>
     </row>
   </sheetData>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.180281724682919</v>
+        <v>1.695478285234242</v>
       </c>
       <c r="C2" t="n">
-        <v>8.259443435828414</v>
+        <v>5.624432597629976</v>
       </c>
       <c r="D2" t="n">
-        <v>30.6413275972472</v>
+        <v>35.09748042682347</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>13.66101930459437</v>
+        <v>8.835729338221293</v>
       </c>
       <c r="C3" t="n">
-        <v>28.33323874456295</v>
+        <v>21.24502031990098</v>
       </c>
       <c r="D3" t="n">
-        <v>47.29078691356886</v>
+        <v>79.75718349301087</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>25.51267759026186</v>
+        <v>15.45565410795754</v>
       </c>
       <c r="C4" t="n">
-        <v>60.2655645728947</v>
+        <v>49.60869324329558</v>
       </c>
       <c r="D4" t="n">
-        <v>42.94655332227672</v>
+        <v>61.88643003260619</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>22.18749811597792</v>
+        <v>11.85460352878024</v>
       </c>
       <c r="C5" t="n">
-        <v>69.48319376806802</v>
+        <v>44.69406423583604</v>
       </c>
       <c r="D5" t="n">
-        <v>34.70478134512475</v>
+        <v>35.76016012719008</v>
       </c>
     </row>
     <row r="6">
@@ -5501,13 +5501,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>9.94215900090745</v>
+        <v>5.675483478250811</v>
       </c>
       <c r="C6" t="n">
-        <v>36.50825187782615</v>
+        <v>21.45413258090555</v>
       </c>
       <c r="D6" t="n">
-        <v>38.52083467153211</v>
+        <v>34.05290086950487</v>
       </c>
     </row>
     <row r="7">
@@ -5515,13 +5515,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>8.563785224144926</v>
+        <v>6.347980655659875</v>
       </c>
       <c r="C7" t="n">
-        <v>21.13997331554657</v>
+        <v>17.48689010804419</v>
       </c>
       <c r="D7" t="n">
-        <v>39.52516257297658</v>
+        <v>35.03366682604743</v>
       </c>
     </row>
     <row r="8">
@@ -5529,13 +5529,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.84831213192725</v>
+        <v>7.927612711792993</v>
       </c>
       <c r="C8" t="n">
-        <v>31.54355373745002</v>
+        <v>25.78560345204247</v>
       </c>
       <c r="D8" t="n">
-        <v>39.8884092235479</v>
+        <v>35.21529015133309</v>
       </c>
     </row>
     <row r="9">
@@ -5543,13 +5543,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>10.6499990956694</v>
+        <v>7.876561831172157</v>
       </c>
       <c r="C9" t="n">
-        <v>33.9468721174462</v>
+        <v>27.73437264497238</v>
       </c>
       <c r="D9" t="n">
-        <v>42.15624642035802</v>
+        <v>37.49687181600267</v>
       </c>
     </row>
     <row r="10">
@@ -5557,13 +5557,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>9.964739198105127</v>
+        <v>7.402377690020952</v>
       </c>
       <c r="C10" t="n">
-        <v>33.59540643932586</v>
+        <v>27.47420950334699</v>
       </c>
       <c r="D10" t="n">
-        <v>48.68486865359933</v>
+        <v>44.55661955724149</v>
       </c>
     </row>
     <row r="11">
@@ -5571,13 +5571,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>8.707120388964958</v>
+        <v>6.75246070980956</v>
       </c>
       <c r="C11" t="n">
-        <v>33.58460721457913</v>
+        <v>28.43141351498762</v>
       </c>
       <c r="D11" t="n">
-        <v>50.82115165804038</v>
+        <v>45.13486895504285</v>
       </c>
     </row>
     <row r="12">
@@ -5585,13 +5585,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>7.376852249710534</v>
+        <v>5.641122308602172</v>
       </c>
       <c r="C12" t="n">
-        <v>33.84673385161303</v>
+        <v>29.29044275620359</v>
       </c>
       <c r="D12" t="n">
-        <v>47.08167465256428</v>
+        <v>43.39324852770902</v>
       </c>
     </row>
     <row r="13">
@@ -5599,13 +5599,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>5.723589115758904</v>
+        <v>4.422773407631881</v>
       </c>
       <c r="C13" t="n">
-        <v>33.30088212805181</v>
+        <v>28.35778243716912</v>
       </c>
       <c r="D13" t="n">
-        <v>45.78871292607123</v>
+        <v>41.88626580169016</v>
       </c>
     </row>
     <row r="14">
@@ -5613,13 +5613,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>4.609305471438775</v>
+        <v>3.68744437715102</v>
       </c>
       <c r="C14" t="n">
-        <v>30.72870314292517</v>
+        <v>26.42668470291564</v>
       </c>
       <c r="D14" t="n">
-        <v>45.47848065152925</v>
+        <v>41.48374924294897</v>
       </c>
     </row>
     <row r="15">
@@ -5627,13 +5627,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4.30005494460103</v>
+        <v>3.225041208450772</v>
       </c>
       <c r="C15" t="n">
-        <v>28.66703296400686</v>
+        <v>25.80032966760617</v>
       </c>
       <c r="D15" t="n">
-        <v>43.71722527011046</v>
+        <v>40.49218406165969</v>
       </c>
     </row>
     <row r="16">
@@ -5641,13 +5641,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>4.546473618366978</v>
+        <v>3.719842051391165</v>
       </c>
       <c r="C16" t="n">
-        <v>30.17205219461722</v>
+        <v>26.86552592671396</v>
       </c>
       <c r="D16" t="n">
-        <v>41.33157834879071</v>
+        <v>38.02505208088746</v>
       </c>
     </row>
     <row r="17">
@@ -5655,13 +5655,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>4.722206457427158</v>
+        <v>3.777765165941727</v>
       </c>
       <c r="C17" t="n">
-        <v>32.58322455624739</v>
+        <v>29.27768003604838</v>
       </c>
       <c r="D17" t="n">
-        <v>37.30543101367455</v>
+        <v>35.41654843070368</v>
       </c>
     </row>
     <row r="18">
@@ -5669,13 +5669,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>4.815472489330605</v>
+        <v>4.280419990516093</v>
       </c>
       <c r="C18" t="n">
-        <v>34.77841242294325</v>
+        <v>31.56809743005619</v>
       </c>
       <c r="D18" t="n">
-        <v>32.1031499288707</v>
+        <v>29.96293993361265</v>
       </c>
     </row>
     <row r="19">
@@ -5683,13 +5683,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>5.416302084329653</v>
+        <v>4.212679398923063</v>
       </c>
       <c r="C19" t="n">
-        <v>37.31230324760427</v>
+        <v>33.7014351913845</v>
       </c>
       <c r="D19" t="n">
-        <v>24.67426505083508</v>
+        <v>23.47064236542849</v>
       </c>
     </row>
     <row r="20">
@@ -5700,10 +5700,10 @@
         <v>4.707480241863455</v>
       </c>
       <c r="C20" t="n">
-        <v>39.67733346713483</v>
+        <v>35.64235040268044</v>
       </c>
       <c r="D20" t="n">
-        <v>16.13993225781756</v>
+        <v>14.79493790299943</v>
       </c>
     </row>
     <row r="21">
@@ -5711,13 +5711,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>18.05004382956612</v>
+        <v>16.07709923228962</v>
       </c>
       <c r="C21" t="n">
-        <v>117.7550478405028</v>
+        <v>101.5395740986713</v>
       </c>
       <c r="D21" t="n">
-        <v>6.016681276522039</v>
+        <v>3.384652469955709</v>
       </c>
     </row>
   </sheetData>
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.253732876052181</v>
+        <v>1.984112110282804</v>
       </c>
       <c r="C2" t="n">
-        <v>5.891467973185108</v>
+        <v>3.98884092235479</v>
       </c>
       <c r="D2" t="n">
-        <v>27.57238427377167</v>
+        <v>27.17772169666445</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>12.48783079801943</v>
+        <v>7.176575718044184</v>
       </c>
       <c r="C3" t="n">
-        <v>28.54922323949725</v>
+        <v>21.56899706230243</v>
       </c>
       <c r="D3" t="n">
-        <v>56.49958037940394</v>
+        <v>88.69108760165686</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>18.96540215063988</v>
+        <v>16.43838355990859</v>
       </c>
       <c r="C4" t="n">
-        <v>54.77759490615503</v>
+        <v>51.59967758750811</v>
       </c>
       <c r="D4" t="n">
-        <v>49.05989627662161</v>
+        <v>86.53124265231386</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>18.4077694546277</v>
+        <v>17.52419652080557</v>
       </c>
       <c r="C5" t="n">
-        <v>68.30509652297184</v>
+        <v>69.60591223109887</v>
       </c>
       <c r="D5" t="n">
-        <v>33.67394625566561</v>
+        <v>48.69468613064181</v>
       </c>
     </row>
     <row r="6">
@@ -5815,10 +5815,10 @@
         <v>10.90819874188631</v>
       </c>
       <c r="C6" t="n">
-        <v>50.11331156327844</v>
+        <v>47.57745724320893</v>
       </c>
       <c r="D6" t="n">
-        <v>31.67805317293184</v>
+        <v>37.79630486579796</v>
       </c>
     </row>
     <row r="7">
@@ -5826,13 +5826,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>5.090361846519712</v>
+        <v>6.767186925373263</v>
       </c>
       <c r="C7" t="n">
-        <v>23.83487076370406</v>
+        <v>24.67328330313084</v>
       </c>
       <c r="D7" t="n">
-        <v>30.78171751895449</v>
+        <v>36.89015173477814</v>
       </c>
     </row>
     <row r="8">
@@ -5840,13 +5840,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>4.840016181936775</v>
+        <v>7.677267047210056</v>
       </c>
       <c r="C8" t="n">
-        <v>18.60902773399829</v>
+        <v>25.03456645829366</v>
       </c>
       <c r="D8" t="n">
-        <v>30.0414797499524</v>
+        <v>37.05115835827462</v>
       </c>
     </row>
     <row r="9">
@@ -5854,13 +5854,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>4.881249585515139</v>
+        <v>8.320311793491715</v>
       </c>
       <c r="C9" t="n">
-        <v>21.74374815365835</v>
+        <v>30.7296848906294</v>
       </c>
       <c r="D9" t="n">
-        <v>29.95312245657017</v>
+        <v>38.49530923122167</v>
       </c>
     </row>
     <row r="10">
@@ -5868,13 +5868,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4.270602513473626</v>
+        <v>7.829437941368314</v>
       </c>
       <c r="C10" t="n">
-        <v>21.49536598448391</v>
+        <v>31.03304493124168</v>
       </c>
       <c r="D10" t="n">
-        <v>33.45305302221006</v>
+        <v>44.12955930589413</v>
       </c>
     </row>
     <row r="11">
@@ -5882,13 +5882,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>3.731623023842126</v>
+        <v>7.107853378746905</v>
       </c>
       <c r="C11" t="n">
-        <v>20.25738212942868</v>
+        <v>30.56376952861169</v>
       </c>
       <c r="D11" t="n">
-        <v>34.65078522139116</v>
+        <v>46.20104696185489</v>
       </c>
     </row>
     <row r="12">
@@ -5896,13 +5896,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.037527396939631</v>
+        <v>6.075054793879263</v>
       </c>
       <c r="C12" t="n">
-        <v>19.7439280801076</v>
+        <v>31.46010518258904</v>
       </c>
       <c r="D12" t="n">
-        <v>31.89403766786613</v>
+        <v>44.47807974090174</v>
       </c>
     </row>
     <row r="13">
@@ -5910,13 +5910,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.341468274628643</v>
+        <v>4.682936549257286</v>
       </c>
       <c r="C13" t="n">
-        <v>18.99190933865455</v>
+        <v>30.95941385342317</v>
       </c>
       <c r="D13" t="n">
-        <v>30.43908757017236</v>
+        <v>42.14642894331557</v>
       </c>
     </row>
     <row r="14">
@@ -5924,13 +5924,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.536435157146258</v>
+        <v>3.68744437715102</v>
       </c>
       <c r="C14" t="n">
-        <v>17.51536079146734</v>
+        <v>28.88498095434966</v>
       </c>
       <c r="D14" t="n">
-        <v>29.49955501720816</v>
+        <v>41.79103627437823</v>
       </c>
     </row>
     <row r="15">
@@ -5938,13 +5938,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.433351648200343</v>
+        <v>3.225041208450772</v>
       </c>
       <c r="C15" t="n">
-        <v>16.12520604225386</v>
+        <v>27.23368131580652</v>
       </c>
       <c r="D15" t="n">
-        <v>28.30869505195678</v>
+        <v>40.85052197370977</v>
       </c>
     </row>
     <row r="16">
@@ -5952,13 +5952,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.239947350463722</v>
+        <v>3.306526267903257</v>
       </c>
       <c r="C16" t="n">
-        <v>15.70599977254047</v>
+        <v>27.69215749368978</v>
       </c>
       <c r="D16" t="n">
-        <v>26.03889435973815</v>
+        <v>38.02505208088746</v>
       </c>
     </row>
     <row r="17">
@@ -5966,13 +5966,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>1.416661937228147</v>
+        <v>3.305544520199011</v>
       </c>
       <c r="C17" t="n">
-        <v>16.52772260099505</v>
+        <v>29.27768003604838</v>
       </c>
       <c r="D17" t="n">
-        <v>23.61103228713579</v>
+        <v>35.8887690764464</v>
       </c>
     </row>
     <row r="18">
@@ -5980,13 +5980,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1.070104997629023</v>
+        <v>3.745367491701582</v>
       </c>
       <c r="C18" t="n">
-        <v>17.12167996206437</v>
+        <v>31.56809743005619</v>
       </c>
       <c r="D18" t="n">
-        <v>20.33199495495144</v>
+        <v>29.96293993361265</v>
       </c>
     </row>
     <row r="19">
@@ -5994,13 +5994,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1.203622685406589</v>
+        <v>3.610868056219768</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>33.7014351913845</v>
       </c>
       <c r="D19" t="n">
-        <v>15.64709491028566</v>
+        <v>24.07245370813179</v>
       </c>
     </row>
     <row r="20">
@@ -6008,13 +6008,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>1.34499435481813</v>
+        <v>4.03498306445439</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>35.64235040268044</v>
       </c>
       <c r="D20" t="n">
-        <v>10.08745766113597</v>
+        <v>15.46743508040849</v>
       </c>
     </row>
     <row r="21">
@@ -6022,13 +6022,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.052007904454229</v>
+        <v>17.34396876116365</v>
       </c>
       <c r="C21" t="n">
-        <v>66.99407509231517</v>
+        <v>114.4701938236801</v>
       </c>
       <c r="D21" t="n">
-        <v>4.407504940283893</v>
+        <v>4.335992190290912</v>
       </c>
     </row>
   </sheetData>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.738896168399354</v>
+        <v>2.510328879759094</v>
       </c>
       <c r="C2" t="n">
-        <v>9.049750337747097</v>
+        <v>10.87187407682918</v>
       </c>
       <c r="D2" t="n">
-        <v>21.15764477422301</v>
+        <v>32.81688050985813</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>18.11324514335365</v>
+        <v>6.911503837897545</v>
       </c>
       <c r="C3" t="n">
-        <v>24.98547907308132</v>
+        <v>18.18687622117216</v>
       </c>
       <c r="D3" t="n">
-        <v>66.00780689503431</v>
+        <v>89.38321973315085</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>22.29647211114931</v>
+        <v>14.97067074205961</v>
       </c>
       <c r="C4" t="n">
-        <v>65.39617807528853</v>
+        <v>52.79937328209771</v>
       </c>
       <c r="D4" t="n">
-        <v>66.81284001251667</v>
+        <v>108.7894266029976</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>24.51914891356409</v>
+        <v>21.13211933391259</v>
       </c>
       <c r="C5" t="n">
-        <v>88.55364292306231</v>
+        <v>81.97593330460867</v>
       </c>
       <c r="D5" t="n">
-        <v>44.86587008407924</v>
+        <v>65.9489020327795</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>18.99878157258428</v>
+        <v>16.90569546713008</v>
       </c>
       <c r="C6" t="n">
-        <v>84.52847733565039</v>
+        <v>79.01400048089606</v>
       </c>
       <c r="D6" t="n">
-        <v>35.74347041621788</v>
+        <v>44.11581483803468</v>
       </c>
     </row>
     <row r="7">
@@ -6137,13 +6137,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.581857593448868</v>
+        <v>9.82140403328509</v>
       </c>
       <c r="C7" t="n">
-        <v>52.10135066437822</v>
+        <v>46.35223610830891</v>
       </c>
       <c r="D7" t="n">
-        <v>33.17718191731671</v>
+        <v>39.16584291322225</v>
       </c>
     </row>
     <row r="8">
@@ -6151,13 +6151,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>5.507604620824606</v>
+        <v>7.760715602071035</v>
       </c>
       <c r="C8" t="n">
-        <v>26.45319189093031</v>
+        <v>29.2069942013426</v>
       </c>
       <c r="D8" t="n">
-        <v>32.12769362147687</v>
+        <v>38.88702656521616</v>
       </c>
     </row>
     <row r="9">
@@ -6165,13 +6165,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.214062057254808</v>
+        <v>8.431249284071605</v>
       </c>
       <c r="C9" t="n">
-        <v>23.18593553119691</v>
+        <v>31.50624732468863</v>
       </c>
       <c r="D9" t="n">
-        <v>31.39530983410874</v>
+        <v>39.60468413702056</v>
       </c>
     </row>
     <row r="10">
@@ -6179,13 +6179,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4.697662764820988</v>
+        <v>8.114144775599888</v>
       </c>
       <c r="C10" t="n">
-        <v>24.34243432679967</v>
+        <v>34.44952694202058</v>
       </c>
       <c r="D10" t="n">
-        <v>33.59540643932586</v>
+        <v>43.84485247166256</v>
       </c>
     </row>
     <row r="11">
@@ -6193,13 +6193,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.08701569277947</v>
+        <v>7.463246047684251</v>
       </c>
       <c r="C11" t="n">
-        <v>23.45591614986479</v>
+        <v>33.7623035490478</v>
       </c>
       <c r="D11" t="n">
-        <v>35.36157055926586</v>
+        <v>46.91183229972957</v>
       </c>
     </row>
     <row r="12">
@@ -6207,13 +6207,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.254493639578176</v>
+        <v>6.292021036517808</v>
       </c>
       <c r="C12" t="n">
-        <v>21.91359050649305</v>
+        <v>33.1958351236974</v>
       </c>
       <c r="D12" t="n">
-        <v>33.1958351236974</v>
+        <v>44.91201222617883</v>
       </c>
     </row>
     <row r="13">
@@ -6221,13 +6221,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.601631416254048</v>
+        <v>4.943099690882691</v>
       </c>
       <c r="C13" t="n">
-        <v>21.07321447165778</v>
+        <v>33.30088212805181</v>
       </c>
       <c r="D13" t="n">
-        <v>30.95941385342317</v>
+        <v>42.92691836819179</v>
       </c>
     </row>
     <row r="14">
@@ -6235,13 +6235,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.84372218857551</v>
+        <v>3.68744437715102</v>
       </c>
       <c r="C14" t="n">
-        <v>19.35908298004286</v>
+        <v>31.34327720578367</v>
       </c>
       <c r="D14" t="n">
-        <v>30.11412908006666</v>
+        <v>42.09832330580748</v>
       </c>
     </row>
     <row r="15">
@@ -6249,13 +6249,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.433351648200343</v>
+        <v>3.225041208450772</v>
       </c>
       <c r="C15" t="n">
-        <v>17.5585576904542</v>
+        <v>29.02537087605695</v>
       </c>
       <c r="D15" t="n">
-        <v>28.66703296400686</v>
+        <v>40.85052197370977</v>
       </c>
     </row>
     <row r="16">
@@ -6263,13 +6263,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.239947350463722</v>
+        <v>2.89321048441535</v>
       </c>
       <c r="C16" t="n">
-        <v>16.53263133951629</v>
+        <v>28.51878906066559</v>
       </c>
       <c r="D16" t="n">
-        <v>26.03889435973815</v>
+        <v>38.43836786437537</v>
       </c>
     </row>
     <row r="17">
@@ -6277,13 +6277,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0.9444412914854317</v>
+        <v>2.833323874456295</v>
       </c>
       <c r="C17" t="n">
-        <v>16.99994324673777</v>
+        <v>29.7499006817911</v>
       </c>
       <c r="D17" t="n">
-        <v>24.0832529328785</v>
+        <v>35.8887690764464</v>
       </c>
     </row>
     <row r="18">
@@ -6291,13 +6291,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1.070104997629023</v>
+        <v>3.21031499288707</v>
       </c>
       <c r="C18" t="n">
-        <v>17.12167996206437</v>
+        <v>31.56809743005619</v>
       </c>
       <c r="D18" t="n">
-        <v>20.86704745376595</v>
+        <v>30.49799243242716</v>
       </c>
     </row>
     <row r="19">
@@ -6305,13 +6305,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>0.6018113427032947</v>
+        <v>3.009056713516474</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>33.7014351913845</v>
       </c>
       <c r="D19" t="n">
-        <v>15.64709491028566</v>
+        <v>24.67426505083508</v>
       </c>
     </row>
     <row r="20">
@@ -6319,13 +6319,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>0.672497177409065</v>
+        <v>3.362485887045325</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>35.64235040268044</v>
       </c>
       <c r="D20" t="n">
-        <v>10.75995483854504</v>
+        <v>15.46743508040849</v>
       </c>
     </row>
     <row r="21">
@@ -6333,13 +6333,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.27142879644605</v>
+        <v>18.63289769781038</v>
       </c>
       <c r="C21" t="n">
-        <v>76.35000236268353</v>
+        <v>127.768441356414</v>
       </c>
       <c r="D21" t="n">
-        <v>5.453571597334538</v>
+        <v>5.323685056517252</v>
       </c>
     </row>
   </sheetData>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.432590884674349</v>
+        <v>2.231512531753</v>
       </c>
       <c r="C2" t="n">
-        <v>12.55949838042945</v>
+        <v>6.696501090667494</v>
       </c>
       <c r="D2" t="n">
-        <v>19.00172681569702</v>
+        <v>25.80818364924015</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>17.3131207643925</v>
+        <v>9.675123625352317</v>
       </c>
       <c r="C3" t="n">
-        <v>31.06740610089032</v>
+        <v>34.28262983229862</v>
       </c>
       <c r="D3" t="n">
-        <v>67.61787312999907</v>
+        <v>99.67684441217865</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>29.31596819651401</v>
+        <v>10.14636252339078</v>
       </c>
       <c r="C4" t="n">
-        <v>63.78807533573226</v>
+        <v>73.8578615381918</v>
       </c>
       <c r="D4" t="n">
-        <v>84.89761447244717</v>
+        <v>96.85628325787756</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>29.62423697564751</v>
+        <v>9.522952731194062</v>
       </c>
       <c r="C5" t="n">
-        <v>105.8569462104124</v>
+        <v>47.19752088166541</v>
       </c>
       <c r="D5" t="n">
-        <v>58.31581363226055</v>
+        <v>45.9703362513569</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>26.52584122104457</v>
+        <v>6.078000036992004</v>
       </c>
       <c r="C6" t="n">
-        <v>115.6027556704704</v>
+        <v>30.51075515258238</v>
       </c>
       <c r="D6" t="n">
-        <v>42.14348370020284</v>
+        <v>25.76105975943631</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>16.58859095865835</v>
+        <v>5.090361846519712</v>
       </c>
       <c r="C7" t="n">
-        <v>90.30900781825558</v>
+        <v>20.54110721595601</v>
       </c>
       <c r="D7" t="n">
-        <v>36.35117224514665</v>
+        <v>27.30829414132927</v>
       </c>
     </row>
     <row r="8">
@@ -6462,13 +6462,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>8.17795837637593</v>
+        <v>5.841398840268521</v>
       </c>
       <c r="C8" t="n">
-        <v>49.48499303256047</v>
+        <v>23.19869825135213</v>
       </c>
       <c r="D8" t="n">
-        <v>33.79666471869644</v>
+        <v>29.12354564648163</v>
       </c>
     </row>
     <row r="9">
@@ -6476,13 +6476,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.657812019574366</v>
+        <v>5.768749510154256</v>
       </c>
       <c r="C9" t="n">
-        <v>28.6218725696115</v>
+        <v>26.29218526743382</v>
       </c>
       <c r="D9" t="n">
-        <v>32.9484347022272</v>
+        <v>33.39218466454675</v>
       </c>
     </row>
     <row r="10">
@@ -6490,13 +6490,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4.982369599052563</v>
+        <v>5.409429850399925</v>
       </c>
       <c r="C10" t="n">
-        <v>26.76244241776806</v>
+        <v>26.47773558353648</v>
       </c>
       <c r="D10" t="n">
-        <v>33.88011327355743</v>
+        <v>36.72718161587318</v>
       </c>
     </row>
     <row r="11">
@@ -6504,7 +6504,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.442408361716816</v>
+        <v>4.620104696185489</v>
       </c>
       <c r="C11" t="n">
         <v>26.47675383583222</v>
@@ -6518,13 +6518,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.471459882216721</v>
+        <v>3.688426124855267</v>
       </c>
       <c r="C12" t="n">
-        <v>24.5171854181556</v>
+        <v>27.12078032981814</v>
       </c>
       <c r="D12" t="n">
-        <v>34.28066633689012</v>
+        <v>34.93156506480576</v>
       </c>
     </row>
     <row r="13">
@@ -6535,10 +6535,10 @@
         <v>2.861794557879452</v>
       </c>
       <c r="C13" t="n">
-        <v>23.15451960466103</v>
+        <v>25.75615102091507</v>
       </c>
       <c r="D13" t="n">
-        <v>31.47974013667398</v>
+        <v>34.86186097780424</v>
       </c>
     </row>
     <row r="14">
@@ -6546,13 +6546,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.84372218857551</v>
+        <v>2.458296251434013</v>
       </c>
       <c r="C14" t="n">
-        <v>21.51009220004762</v>
+        <v>24.27567548291088</v>
       </c>
       <c r="D14" t="n">
-        <v>30.42141611149592</v>
+        <v>34.10886048864694</v>
       </c>
     </row>
     <row r="15">
@@ -6560,13 +6560,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.433351648200343</v>
+        <v>2.150027472300515</v>
       </c>
       <c r="C15" t="n">
-        <v>19.35024725070463</v>
+        <v>24.00864010735575</v>
       </c>
       <c r="D15" t="n">
-        <v>29.02537087605695</v>
+        <v>32.6087499965578</v>
       </c>
     </row>
     <row r="16">
@@ -6574,13 +6574,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.239947350463722</v>
+        <v>2.066578917439536</v>
       </c>
       <c r="C16" t="n">
-        <v>17.3592629064921</v>
+        <v>25.21226279276234</v>
       </c>
       <c r="D16" t="n">
-        <v>26.03889435973815</v>
+        <v>30.58536797810513</v>
       </c>
     </row>
     <row r="17">
@@ -6588,13 +6588,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0.9444412914854317</v>
+        <v>2.361103228713579</v>
       </c>
       <c r="C17" t="n">
-        <v>17.47216389248049</v>
+        <v>26.9165768073348</v>
       </c>
       <c r="D17" t="n">
-        <v>24.0832529328785</v>
+        <v>25.97213551584937</v>
       </c>
     </row>
     <row r="18">
@@ -6602,13 +6602,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>0.5350524988145117</v>
+        <v>2.140209995258047</v>
       </c>
       <c r="C18" t="n">
-        <v>17.65673246087889</v>
+        <v>28.89283493598363</v>
       </c>
       <c r="D18" t="n">
-        <v>20.86704745376595</v>
+        <v>21.40209995258047</v>
       </c>
     </row>
     <row r="19">
@@ -6616,13 +6616,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>0.6018113427032947</v>
+        <v>2.407245370813179</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>30.69237847786803</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>13.23984953947248</v>
       </c>
     </row>
     <row r="20">
@@ -6630,13 +6630,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>0</v>
+        <v>14.12244072559037</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>96.83959354690535</v>
       </c>
       <c r="D20" t="n">
-        <v>10.75995483854504</v>
+        <v>4.03498306445439</v>
       </c>
     </row>
     <row r="21">
@@ -6644,13 +6644,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.477884807051963</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>85.99567528109758</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>6.543149206170468</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
